--- a/input/reg_income.xlsx
+++ b/input/reg_income.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Patryk\git\SimPathsFork\input\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Patryk\git\SimPaths_HU\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F51F219-A60E-4A73-8CED-CFA74D2E4ED6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E9BB024-F1E5-4368-BA66-DFDA85B3FAA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="852" activeTab="4" xr2:uid="{8DDB884B-4CBA-4D96-8159-4841B9678181}"/>
+    <workbookView xWindow="-83" yWindow="0" windowWidth="14566" windowHeight="17363" tabRatio="852" activeTab="4" xr2:uid="{8DDB884B-4CBA-4D96-8159-4841B9678181}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="7" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="38">
   <si>
     <t>Constant</t>
   </si>
@@ -149,6 +149,12 @@
   <si>
     <t>COEFFICIENT</t>
   </si>
+  <si>
+    <t>Les_c3_Student_L1</t>
+  </si>
+  <si>
+    <t>Les_c3_NotEmployed_L1</t>
+  </si>
 </sst>
 </file>
 
@@ -211,7 +217,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyAlignment="1">
@@ -225,6 +231,7 @@
     <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -544,14 +551,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA6ABAD6-EDFF-4112-B11C-EFA0B1D442EA}">
   <dimension ref="A1:F13"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="53.140625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="53.1328125" style="1" customWidth="1"/>
     <col min="2" max="2" width="31" style="1" customWidth="1"/>
-    <col min="3" max="16384" width="9.140625" style="1"/>
+    <col min="3" max="16384" width="9.1328125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A1" s="5" t="s">
         <v>12</v>
       </c>
@@ -563,7 +570,7 @@
       <c r="E1" s="6"/>
       <c r="F1" s="6"/>
     </row>
-    <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>18</v>
       </c>
@@ -573,7 +580,7 @@
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -581,7 +588,7 @@
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A4" s="3" t="s">
         <v>16</v>
       </c>
@@ -593,7 +600,7 @@
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -605,7 +612,7 @@
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -617,7 +624,7 @@
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>23</v>
       </c>
@@ -629,7 +636,7 @@
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>25</v>
       </c>
@@ -641,7 +648,7 @@
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A9"/>
       <c r="B9"/>
       <c r="C9" s="2"/>
@@ -649,7 +656,7 @@
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A10" s="3" t="s">
         <v>27</v>
       </c>
@@ -657,14 +664,14 @@
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A11"/>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A12"/>
       <c r="B12"/>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A13"/>
       <c r="B13"/>
     </row>
@@ -680,17 +687,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E58AB64-AB0B-453E-B671-AB6F0851D77A}">
   <dimension ref="A1:L11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="20.140625" style="4" customWidth="1"/>
-    <col min="2" max="16384" width="9.140625" style="4"/>
+    <col min="1" max="1" width="20.1328125" style="4" customWidth="1"/>
+    <col min="2" max="16384" width="9.1328125" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="7" t="s">
         <v>35</v>
       </c>
       <c r="C1" t="s">
@@ -724,384 +731,384 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A2" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>-0.10240189715765066</v>
+      <c r="B2" s="7">
+        <v>-7.1433508314934793E-2</v>
       </c>
       <c r="C2">
-        <v>8.2808546024554942E-3</v>
+        <v>6.0919174846594676E-3</v>
       </c>
       <c r="D2">
-        <v>7.1044116632562669E-4</v>
+        <v>-5.3959207781726411E-4</v>
       </c>
       <c r="E2">
-        <v>-1.9815560885740013E-5</v>
+        <v>1.1911810048719682E-5</v>
       </c>
       <c r="F2">
-        <v>-3.3874794625969758E-4</v>
+        <v>-8.8638448957555961E-5</v>
       </c>
       <c r="G2">
-        <v>-1.4948454914505381E-4</v>
+        <v>-1.4698674764988958E-4</v>
       </c>
       <c r="H2">
-        <v>3.9653378881065147E-4</v>
+        <v>2.050993823188383E-4</v>
       </c>
       <c r="I2">
-        <v>4.0672032452544402E-4</v>
+        <v>3.3904690768547731E-4</v>
       </c>
       <c r="J2">
-        <v>4.0079847432287433E-4</v>
+        <v>9.452570199991895E-5</v>
       </c>
       <c r="K2">
-        <v>-9.0897527910057405E-5</v>
+        <v>-8.0411813398847476E-5</v>
       </c>
       <c r="L2">
-        <v>-7.6738220850745692E-3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+        <v>4.3716778981481774E-3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A3" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>-0.51110889672472348</v>
+      <c r="B3" s="7">
+        <v>-0.67049384303294957</v>
       </c>
       <c r="C3">
-        <v>7.1044116632562669E-4</v>
+        <v>-5.3959207781726411E-4</v>
       </c>
       <c r="D3">
-        <v>0.11296167243471517</v>
+        <v>7.9274933544330684E-2</v>
       </c>
       <c r="E3">
-        <v>-2.6314802745372812E-3</v>
+        <v>-1.8448105357181551E-3</v>
       </c>
       <c r="F3">
-        <v>-3.3793125995343343E-4</v>
+        <v>-2.221359638218956E-4</v>
       </c>
       <c r="G3">
-        <v>-7.1255764510259889E-6</v>
+        <v>4.5346939163172506E-6</v>
       </c>
       <c r="H3">
-        <v>-1.1694305561432028E-2</v>
+        <v>-1.6978056227078708E-2</v>
       </c>
       <c r="I3">
-        <v>1.5320216601766856E-3</v>
+        <v>6.6255928735658998E-6</v>
       </c>
       <c r="J3">
-        <v>-1.8344729137192983E-3</v>
+        <v>-2.0876415275182802E-3</v>
       </c>
       <c r="K3">
-        <v>1.9087645315524204E-4</v>
+        <v>-6.1870430253865849E-5</v>
       </c>
       <c r="L3">
-        <v>-1.1972160160514802</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+        <v>-0.83660664734140444</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A4" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="B4">
-        <v>1.0064057075673519E-2</v>
+      <c r="B4" s="7">
+        <v>1.3692507072557822E-2</v>
       </c>
       <c r="C4">
-        <v>-1.9815560885740013E-5</v>
+        <v>1.1911810048719682E-5</v>
       </c>
       <c r="D4">
-        <v>-2.6314802745372812E-3</v>
+        <v>-1.8448105357181551E-3</v>
       </c>
       <c r="E4">
-        <v>6.1563055889288037E-5</v>
+        <v>4.3116354084073313E-5</v>
       </c>
       <c r="F4">
-        <v>5.7803811403514191E-6</v>
+        <v>4.6699713741934351E-6</v>
       </c>
       <c r="G4">
-        <v>-3.9168598087169215E-6</v>
+        <v>-2.3968524011040151E-6</v>
       </c>
       <c r="H4">
-        <v>2.4343931186612128E-4</v>
+        <v>3.6824093019872939E-4</v>
       </c>
       <c r="I4">
-        <v>-2.7889976363309338E-5</v>
+        <v>3.6403582219330863E-6</v>
       </c>
       <c r="J4">
-        <v>4.5334740685833153E-5</v>
+        <v>4.9446043371814685E-5</v>
       </c>
       <c r="K4">
-        <v>-2.9309652223316954E-6</v>
+        <v>1.8020597742714368E-6</v>
       </c>
       <c r="L4">
-        <v>2.7768129738076047E-2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+        <v>1.9389131545675922E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A5" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="B5">
-        <v>2.8579097623150338E-2</v>
+      <c r="B5" s="7">
+        <v>3.0156752093573394E-2</v>
       </c>
       <c r="C5">
-        <v>-3.3874794625969758E-4</v>
+        <v>-8.8638448957555961E-5</v>
       </c>
       <c r="D5">
-        <v>-3.3793125995343343E-4</v>
+        <v>-2.221359638218956E-4</v>
       </c>
       <c r="E5">
-        <v>5.7803811403514191E-6</v>
+        <v>4.6699713741934351E-6</v>
       </c>
       <c r="F5">
-        <v>4.7581032805811586E-3</v>
+        <v>3.2636371818738569E-3</v>
       </c>
       <c r="G5">
-        <v>-3.9855020448604985E-5</v>
+        <v>-5.1018107774518265E-5</v>
       </c>
       <c r="H5">
-        <v>-2.7873294932820071E-3</v>
+        <v>2.8303305777074642E-3</v>
       </c>
       <c r="I5">
-        <v>-3.3949738207323613E-4</v>
+        <v>-7.0075220312239544E-5</v>
       </c>
       <c r="J5">
-        <v>3.0459133453043796E-4</v>
+        <v>1.7785908801168718E-4</v>
       </c>
       <c r="K5">
-        <v>-1.1069256263282435E-4</v>
+        <v>-9.2231112297763013E-6</v>
       </c>
       <c r="L5">
-        <v>-1.5162753706863055E-2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+        <v>-1.2127387544961893E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A6" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="B6">
-        <v>4.9162215657146124E-2</v>
+      <c r="B6" s="7">
+        <v>8.0056636216084123E-2</v>
       </c>
       <c r="C6">
-        <v>-1.4948454914505381E-4</v>
+        <v>-1.4698674764988958E-4</v>
       </c>
       <c r="D6">
-        <v>-7.1255764510259889E-6</v>
+        <v>4.5346939163172506E-6</v>
       </c>
       <c r="E6">
-        <v>-3.9168598087169215E-6</v>
+        <v>-2.3968524011040151E-6</v>
       </c>
       <c r="F6">
-        <v>-3.9855020448604985E-5</v>
+        <v>-5.1018107774518265E-5</v>
       </c>
       <c r="G6">
-        <v>1.0977523244606073E-3</v>
+        <v>7.7643996126355299E-4</v>
       </c>
       <c r="H6">
-        <v>-1.4754508638281996E-4</v>
+        <v>-9.3713410084904965E-4</v>
       </c>
       <c r="I6">
-        <v>2.0657359942247329E-5</v>
+        <v>9.8332485211196979E-5</v>
       </c>
       <c r="J6">
-        <v>1.0193573814618571E-4</v>
+        <v>-1.1263273577808482E-5</v>
       </c>
       <c r="K6">
-        <v>-4.8900669527058519E-5</v>
+        <v>-2.2278130373918888E-5</v>
       </c>
       <c r="L6">
-        <v>2.2464860974854076E-3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+        <v>1.1896386061562817E-3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A7" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B7">
-        <v>6.988549881960104</v>
+      <c r="B7" s="7">
+        <v>4.6733997471688005</v>
       </c>
       <c r="C7">
-        <v>3.9653378881065147E-4</v>
+        <v>2.050993823188383E-4</v>
       </c>
       <c r="D7">
-        <v>-1.1694305561432028E-2</v>
+        <v>-1.6978056227078708E-2</v>
       </c>
       <c r="E7">
-        <v>2.4343931186612128E-4</v>
+        <v>3.6824093019872939E-4</v>
       </c>
       <c r="F7">
-        <v>-2.7873294932820071E-3</v>
+        <v>2.8303305777074642E-3</v>
       </c>
       <c r="G7">
-        <v>-1.4754508638281996E-4</v>
+        <v>-9.3713410084904965E-4</v>
       </c>
       <c r="H7">
-        <v>0.3728626196517949</v>
+        <v>0.22080881406144059</v>
       </c>
       <c r="I7">
-        <v>-8.9122145794995333E-4</v>
+        <v>1.2190093334851389E-3</v>
       </c>
       <c r="J7">
-        <v>1.49025781254708E-3</v>
+        <v>4.5260558913477952E-3</v>
       </c>
       <c r="K7">
-        <v>9.193103676388252E-4</v>
+        <v>8.2930134606174627E-4</v>
       </c>
       <c r="L7">
-        <v>0.12215751427796817</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+        <v>0.15421489068359645</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A8" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="B8">
-        <v>0.15547622749862661</v>
+      <c r="B8" s="7">
+        <v>0.21555847875657319</v>
       </c>
       <c r="C8">
-        <v>4.0672032452544402E-4</v>
+        <v>3.3904690768547731E-4</v>
       </c>
       <c r="D8">
-        <v>1.5320216601766856E-3</v>
+        <v>6.6255928735658998E-6</v>
       </c>
       <c r="E8">
-        <v>-2.7889976363309338E-5</v>
+        <v>3.6403582219330863E-6</v>
       </c>
       <c r="F8">
-        <v>-3.3949738207323613E-4</v>
+        <v>-7.0075220312239544E-5</v>
       </c>
       <c r="G8">
-        <v>2.0657359942247329E-5</v>
+        <v>9.8332485211196979E-5</v>
       </c>
       <c r="H8">
-        <v>-8.9122145794995333E-4</v>
+        <v>1.2190093334851389E-3</v>
       </c>
       <c r="I8">
-        <v>1.9195558961909439E-2</v>
+        <v>1.327630156985172E-2</v>
       </c>
       <c r="J8">
-        <v>1.1647781150583531E-2</v>
+        <v>7.8327181611551298E-3</v>
       </c>
       <c r="K8">
-        <v>1.1599860799089816E-4</v>
+        <v>5.8404345367384287E-5</v>
       </c>
       <c r="L8">
-        <v>-3.1701514781242918E-2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+        <v>-1.0391821890487251E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A9" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="B9">
-        <v>0.28809119553515905</v>
+      <c r="B9" s="7">
+        <v>0.22048535827922361</v>
       </c>
       <c r="C9">
-        <v>4.0079847432287433E-4</v>
+        <v>9.452570199991895E-5</v>
       </c>
       <c r="D9">
-        <v>-1.8344729137192983E-3</v>
+        <v>-2.0876415275182802E-3</v>
       </c>
       <c r="E9">
-        <v>4.5334740685833153E-5</v>
+        <v>4.9446043371814685E-5</v>
       </c>
       <c r="F9">
-        <v>3.0459133453043796E-4</v>
+        <v>1.7785908801168718E-4</v>
       </c>
       <c r="G9">
-        <v>1.0193573814618571E-4</v>
+        <v>-1.1263273577808482E-5</v>
       </c>
       <c r="H9">
-        <v>1.49025781254708E-3</v>
+        <v>4.5260558913477952E-3</v>
       </c>
       <c r="I9">
-        <v>1.1647781150583531E-2</v>
+        <v>7.8327181611551298E-3</v>
       </c>
       <c r="J9">
-        <v>1.491028213701066E-2</v>
+        <v>1.0523748738133189E-2</v>
       </c>
       <c r="K9">
-        <v>2.4938883144921733E-6</v>
+        <v>3.831769156524453E-5</v>
       </c>
       <c r="L9">
-        <v>5.0278391249019144E-3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+        <v>1.2282475895323464E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A10" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="B10">
-        <v>-4.2800586072581297E-2</v>
+      <c r="B10" s="7">
+        <v>-3.941476191921045E-2</v>
       </c>
       <c r="C10">
-        <v>-9.0897527910057405E-5</v>
+        <v>-8.0411813398847476E-5</v>
       </c>
       <c r="D10">
-        <v>1.9087645315524204E-4</v>
+        <v>-6.1870430253865849E-5</v>
       </c>
       <c r="E10">
-        <v>-2.9309652223316954E-6</v>
+        <v>1.8020597742714368E-6</v>
       </c>
       <c r="F10">
-        <v>-1.1069256263282435E-4</v>
+        <v>-9.2231112297763013E-6</v>
       </c>
       <c r="G10">
-        <v>-4.8900669527058519E-5</v>
+        <v>-2.2278130373918888E-5</v>
       </c>
       <c r="H10">
-        <v>9.193103676388252E-4</v>
+        <v>8.2930134606174627E-4</v>
       </c>
       <c r="I10">
-        <v>1.1599860799089816E-4</v>
+        <v>5.8404345367384287E-5</v>
       </c>
       <c r="J10">
-        <v>2.4938883144921733E-6</v>
+        <v>3.831769156524453E-5</v>
       </c>
       <c r="K10">
-        <v>3.3092930951310112E-4</v>
+        <v>1.4836914921091411E-4</v>
       </c>
       <c r="L10">
-        <v>-7.037192114923374E-3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+        <v>-1.6178032379947477E-3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A11" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B11">
-        <v>4.974271936332034</v>
+      <c r="B11" s="7">
+        <v>6.8095187118365725</v>
       </c>
       <c r="C11">
-        <v>-7.6738220850745692E-3</v>
+        <v>4.3716778981481774E-3</v>
       </c>
       <c r="D11">
-        <v>-1.1972160160514802</v>
+        <v>-0.83660664734140444</v>
       </c>
       <c r="E11">
-        <v>2.7768129738076047E-2</v>
+        <v>1.9389131545675922E-2</v>
       </c>
       <c r="F11">
-        <v>-1.5162753706863055E-2</v>
+        <v>-1.2127387544961893E-2</v>
       </c>
       <c r="G11">
-        <v>2.2464860974854076E-3</v>
+        <v>1.1896386061562817E-3</v>
       </c>
       <c r="H11">
-        <v>0.12215751427796817</v>
+        <v>0.15421489068359645</v>
       </c>
       <c r="I11">
-        <v>-3.1701514781242918E-2</v>
+        <v>-1.0391821890487251E-2</v>
       </c>
       <c r="J11">
-        <v>5.0278391249019144E-3</v>
+        <v>1.2282475895323464E-2</v>
       </c>
       <c r="K11">
-        <v>-7.037192114923374E-3</v>
+        <v>-1.6178032379947477E-3</v>
       </c>
       <c r="L11">
-        <v>12.910910737121768</v>
+        <v>8.9706734409772881</v>
       </c>
     </row>
   </sheetData>
@@ -1112,17 +1119,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B30AE7C4-97F7-4E3B-B4D2-E5D20CBCD6D2}">
   <dimension ref="A1:V21"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="39" style="4" customWidth="1"/>
-    <col min="2" max="16384" width="9.140625" style="4"/>
+    <col min="2" max="16384" width="9.1328125" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A1" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="7" t="s">
         <v>35</v>
       </c>
       <c r="C1" t="s">
@@ -1186,1364 +1193,1364 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A2" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>-4.3648512662320262E-2</v>
+      <c r="B2" s="7">
+        <v>-7.6200130854162482E-2</v>
       </c>
       <c r="C2">
-        <v>1.512342772203855E-3</v>
+        <v>1.0019263620517408E-3</v>
       </c>
       <c r="D2">
-        <v>2.8843925560692492E-5</v>
+        <v>2.0439942595506011E-5</v>
       </c>
       <c r="E2">
-        <v>-2.7174786653144162E-7</v>
+        <v>-1.8373150533484425E-7</v>
       </c>
       <c r="F2">
-        <v>-1.550045858224153E-4</v>
+        <v>-1.3519523746586149E-4</v>
       </c>
       <c r="G2">
-        <v>5.8685121683372713E-5</v>
+        <v>9.0234949119103749E-6</v>
       </c>
       <c r="H2">
-        <v>-3.7534101889557939E-4</v>
+        <v>-1.501033039406661E-4</v>
       </c>
       <c r="I2">
-        <v>1.4270565002178362E-5</v>
+        <v>-4.6487138081426058E-6</v>
       </c>
       <c r="J2">
-        <v>8.2845034391447302E-5</v>
+        <v>5.3220615243854014E-5</v>
       </c>
       <c r="K2">
-        <v>9.5886826367482414E-5</v>
+        <v>8.3409411279669854E-5</v>
       </c>
       <c r="L2">
-        <v>1.8108176205045728E-4</v>
+        <v>1.1649302345571012E-4</v>
       </c>
       <c r="M2">
-        <v>4.8965286095745456E-4</v>
+        <v>4.4712129864333112E-4</v>
       </c>
       <c r="N2">
-        <v>-7.1258715870670962E-6</v>
+        <v>1.3776151972405473E-5</v>
       </c>
       <c r="O2">
-        <v>-3.4474179288916255E-5</v>
+        <v>-1.9243580918563753E-5</v>
       </c>
       <c r="P2">
-        <v>1.2402570323351595E-5</v>
+        <v>5.1186259168677019E-5</v>
       </c>
       <c r="Q2">
-        <v>2.2212556422599223E-6</v>
+        <v>-6.140787039427654E-6</v>
       </c>
       <c r="R2">
-        <v>2.6907939063330107E-4</v>
+        <v>3.3481041432229419E-5</v>
       </c>
       <c r="S2">
-        <v>-3.4536995436787953E-5</v>
+        <v>-1.7504202512307271E-5</v>
       </c>
       <c r="T2">
-        <v>-2.1158412833762472E-5</v>
+        <v>-9.6350713912218442E-6</v>
       </c>
       <c r="U2">
-        <v>3.2905367248700103E-6</v>
+        <v>9.1807101588888923E-7</v>
       </c>
       <c r="V2">
-        <v>-1.2887301842413922E-3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+        <v>-9.1134439244929281E-4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A3" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>-2.3667979226252699E-2</v>
+      <c r="B3" s="7">
+        <v>-2.012971628744397E-2</v>
       </c>
       <c r="C3">
-        <v>2.8843925560692492E-5</v>
+        <v>2.0439942595506011E-5</v>
       </c>
       <c r="D3">
-        <v>7.785438639785748E-5</v>
+        <v>4.9456514197549484E-5</v>
       </c>
       <c r="E3">
-        <v>-7.4891506647166369E-7</v>
+        <v>-4.7629821734298719E-7</v>
       </c>
       <c r="F3">
-        <v>-9.2818850138887609E-6</v>
+        <v>-1.0392405883152085E-6</v>
       </c>
       <c r="G3">
-        <v>3.5360736876081705E-5</v>
+        <v>2.3497429992757447E-5</v>
       </c>
       <c r="H3">
-        <v>3.2503268773292237E-4</v>
+        <v>1.6768949382068207E-4</v>
       </c>
       <c r="I3">
-        <v>1.3761997408411674E-5</v>
+        <v>4.2406753944210273E-6</v>
       </c>
       <c r="J3">
-        <v>8.3106938023813789E-5</v>
+        <v>6.179341405444913E-5</v>
       </c>
       <c r="K3">
-        <v>-4.5646286713101926E-6</v>
+        <v>1.5606194137884573E-5</v>
       </c>
       <c r="L3">
-        <v>1.2879957769656222E-4</v>
+        <v>8.8067175873391082E-5</v>
       </c>
       <c r="M3">
-        <v>2.3524362885253761E-5</v>
+        <v>2.0040447910810253E-5</v>
       </c>
       <c r="N3">
-        <v>3.6979020959820325E-5</v>
+        <v>2.2431530768432961E-5</v>
       </c>
       <c r="O3">
-        <v>-4.0648543535980541E-6</v>
+        <v>-2.5709699252318203E-6</v>
       </c>
       <c r="P3">
-        <v>4.1774745489510899E-5</v>
+        <v>-2.0318779196285908E-5</v>
       </c>
       <c r="Q3">
-        <v>-1.8618630636062628E-5</v>
+        <v>-1.0640272748454493E-5</v>
       </c>
       <c r="R3">
-        <v>7.7862622419774515E-5</v>
+        <v>-1.2093647135070487E-5</v>
       </c>
       <c r="S3">
-        <v>-1.180677192513151E-6</v>
+        <v>-9.6889151516777383E-6</v>
       </c>
       <c r="T3">
-        <v>7.783394038064469E-6</v>
+        <v>-8.2193477312209441E-6</v>
       </c>
       <c r="U3">
-        <v>4.265086315686519E-6</v>
+        <v>6.1381446061721035E-7</v>
       </c>
       <c r="V3">
-        <v>-2.0174112551368611E-3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+        <v>-1.2490225474787219E-3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A4" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="B4">
-        <v>1.6482181228084743E-4</v>
+      <c r="B4" s="7">
+        <v>1.4540427440475469E-4</v>
       </c>
       <c r="C4">
-        <v>-2.7174786653144162E-7</v>
+        <v>-1.8373150533484425E-7</v>
       </c>
       <c r="D4">
-        <v>-7.4891506647166369E-7</v>
+        <v>-4.7629821734298719E-7</v>
       </c>
       <c r="E4">
-        <v>7.5744189132478203E-9</v>
+        <v>4.8519028717229415E-9</v>
       </c>
       <c r="F4">
-        <v>1.7721828837300793E-7</v>
+        <v>6.5463117959528647E-8</v>
       </c>
       <c r="G4">
-        <v>-3.7936055279147073E-7</v>
+        <v>-2.413390330726938E-7</v>
       </c>
       <c r="H4">
-        <v>-2.6412449557400509E-6</v>
+        <v>-1.2374383332218085E-6</v>
       </c>
       <c r="I4">
-        <v>-1.360103062185802E-8</v>
+        <v>5.5149917355223202E-8</v>
       </c>
       <c r="J4">
-        <v>-1.6032917690542159E-6</v>
+        <v>-1.1705271592303572E-6</v>
       </c>
       <c r="K4">
-        <v>3.3362063305863783E-7</v>
+        <v>6.2880072064145369E-8</v>
       </c>
       <c r="L4">
-        <v>-1.0711659155564057E-6</v>
+        <v>-7.4292881573353301E-7</v>
       </c>
       <c r="M4">
-        <v>-2.4810420748384026E-8</v>
+        <v>4.2360611942332793E-8</v>
       </c>
       <c r="N4">
-        <v>-2.2237180158060585E-7</v>
+        <v>-1.1619424757961462E-7</v>
       </c>
       <c r="O4">
-        <v>2.8761839958619851E-8</v>
+        <v>2.6885104899113038E-8</v>
       </c>
       <c r="P4">
-        <v>-4.1998940549364128E-7</v>
+        <v>1.1599537754993857E-7</v>
       </c>
       <c r="Q4">
-        <v>1.9221429673375618E-7</v>
+        <v>1.0337170516395234E-7</v>
       </c>
       <c r="R4">
-        <v>-6.7472405374665402E-7</v>
+        <v>6.6026336596895343E-8</v>
       </c>
       <c r="S4">
-        <v>8.2542880529303439E-8</v>
+        <v>1.3255191373696076E-7</v>
       </c>
       <c r="T4">
-        <v>3.9492116029696966E-8</v>
+        <v>1.2531789860559363E-7</v>
       </c>
       <c r="U4">
-        <v>-7.4632366165973545E-8</v>
+        <v>-1.841961348706978E-8</v>
       </c>
       <c r="V4">
-        <v>1.8322047212456053E-5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+        <v>1.1067997997374866E-5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A5" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B5">
-        <v>1.6555250943438699E-2</v>
+      <c r="B5" s="7">
+        <v>9.0034343022481977E-2</v>
       </c>
       <c r="C5">
-        <v>-1.550045858224153E-4</v>
+        <v>-1.3519523746586149E-4</v>
       </c>
       <c r="D5">
-        <v>-9.2818850138887609E-6</v>
+        <v>-1.0392405883152085E-6</v>
       </c>
       <c r="E5">
-        <v>1.7721828837300793E-7</v>
+        <v>6.5463117959528647E-8</v>
       </c>
       <c r="F5">
-        <v>2.9694873153147017E-3</v>
+        <v>1.9232610487988158E-3</v>
       </c>
       <c r="G5">
-        <v>2.4314693875462853E-3</v>
+        <v>1.5726700673280962E-3</v>
       </c>
       <c r="H5">
-        <v>-3.2629212834455796E-4</v>
+        <v>3.2618042216823426E-4</v>
       </c>
       <c r="I5">
-        <v>8.6460763357301587E-5</v>
+        <v>6.8868335669312135E-5</v>
       </c>
       <c r="J5">
-        <v>-1.5203168396467467E-4</v>
+        <v>-2.3080186652892608E-5</v>
       </c>
       <c r="K5">
-        <v>1.0051083081741177E-4</v>
+        <v>8.541558858321573E-5</v>
       </c>
       <c r="L5">
-        <v>1.0220553615922604E-4</v>
+        <v>6.9730838882652333E-5</v>
       </c>
       <c r="M5">
-        <v>3.6060936461811217E-5</v>
+        <v>1.8891818175762539E-5</v>
       </c>
       <c r="N5">
-        <v>4.9705165827533345E-5</v>
+        <v>3.7095591899758288E-5</v>
       </c>
       <c r="O5">
-        <v>1.1071687872663008E-5</v>
+        <v>1.7189822084381869E-5</v>
       </c>
       <c r="P5">
-        <v>9.0613960543462413E-4</v>
+        <v>1.662240947917649E-4</v>
       </c>
       <c r="Q5">
-        <v>1.4541868396171902E-5</v>
+        <v>1.2658843820220356E-5</v>
       </c>
       <c r="R5">
-        <v>3.6112106786997467E-4</v>
+        <v>1.4163968864685443E-4</v>
       </c>
       <c r="S5">
-        <v>-2.9005724964611371E-4</v>
+        <v>-2.3540059415884753E-4</v>
       </c>
       <c r="T5">
-        <v>-2.2898368096291788E-4</v>
+        <v>-1.8732762487271015E-4</v>
       </c>
       <c r="U5">
-        <v>-1.7954673059784214E-5</v>
+        <v>-2.2817143354046307E-6</v>
       </c>
       <c r="V5">
-        <v>-2.1875377063241717E-3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+        <v>-1.7261318982335001E-3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A6" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B6">
-        <v>5.9535020626463396E-2</v>
+      <c r="B6" s="7">
+        <v>7.8350291219620324E-2</v>
       </c>
       <c r="C6">
-        <v>5.8685121683372713E-5</v>
+        <v>9.0234949119103749E-6</v>
       </c>
       <c r="D6">
-        <v>3.5360736876081705E-5</v>
+        <v>2.3497429992757447E-5</v>
       </c>
       <c r="E6">
-        <v>-3.7936055279147073E-7</v>
+        <v>-2.413390330726938E-7</v>
       </c>
       <c r="F6">
-        <v>2.4314693875462853E-3</v>
+        <v>1.5726700673280962E-3</v>
       </c>
       <c r="G6">
-        <v>4.1521924728219733E-3</v>
+        <v>2.6602025424089424E-3</v>
       </c>
       <c r="H6">
-        <v>-1.6356143795023511E-4</v>
+        <v>3.3856758405224874E-4</v>
       </c>
       <c r="I6">
-        <v>-2.7054800886163659E-4</v>
+        <v>-1.1775970383402369E-4</v>
       </c>
       <c r="J6">
-        <v>7.6682650764123262E-5</v>
+        <v>1.231818716282329E-4</v>
       </c>
       <c r="K6">
-        <v>-1.8339143456168805E-4</v>
+        <v>-9.3191668775842061E-5</v>
       </c>
       <c r="L6">
-        <v>-1.100943285642982E-5</v>
+        <v>-1.9556601208192714E-6</v>
       </c>
       <c r="M6">
-        <v>9.769262314789426E-5</v>
+        <v>3.8328041133317472E-6</v>
       </c>
       <c r="N6">
-        <v>2.1372567429310364E-4</v>
+        <v>1.5014108839432491E-4</v>
       </c>
       <c r="O6">
-        <v>2.7399328908667175E-5</v>
+        <v>2.729921812495531E-5</v>
       </c>
       <c r="P6">
-        <v>1.0301538047408822E-3</v>
+        <v>3.9410731264859699E-4</v>
       </c>
       <c r="Q6">
-        <v>2.6617643300281093E-5</v>
+        <v>2.0369358998253919E-5</v>
       </c>
       <c r="R6">
-        <v>3.1053816982208561E-4</v>
+        <v>1.869173069896468E-4</v>
       </c>
       <c r="S6">
-        <v>-5.7476489544938366E-4</v>
+        <v>-3.8816736328825584E-4</v>
       </c>
       <c r="T6">
-        <v>-5.3409133995265673E-4</v>
+        <v>-3.832881521058395E-4</v>
       </c>
       <c r="U6">
-        <v>-7.6188025764043496E-6</v>
+        <v>-1.0365248146030389E-6</v>
       </c>
       <c r="V6">
-        <v>-3.5432578355001935E-3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+        <v>-2.4823836671913771E-3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A7" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="B7">
-        <v>0.263922591603653</v>
+      <c r="B7" s="7">
+        <v>0.26171896666474653</v>
       </c>
       <c r="C7">
-        <v>-3.7534101889557939E-4</v>
+        <v>-1.501033039406661E-4</v>
       </c>
       <c r="D7">
-        <v>3.2503268773292237E-4</v>
+        <v>1.6768949382068207E-4</v>
       </c>
       <c r="E7">
-        <v>-2.6412449557400509E-6</v>
+        <v>-1.2374383332218085E-6</v>
       </c>
       <c r="F7">
-        <v>-3.2629212834455796E-4</v>
+        <v>3.2618042216823426E-4</v>
       </c>
       <c r="G7">
-        <v>-1.6356143795023511E-4</v>
+        <v>3.3856758405224874E-4</v>
       </c>
       <c r="H7">
-        <v>2.4619102196889529E-2</v>
+        <v>1.455275792426145E-2</v>
       </c>
       <c r="I7">
-        <v>3.4286990710068318E-3</v>
+        <v>2.2560542814690143E-3</v>
       </c>
       <c r="J7">
-        <v>3.0751409198209977E-3</v>
+        <v>2.0297793868160438E-3</v>
       </c>
       <c r="K7">
-        <v>9.3104367300457123E-4</v>
+        <v>7.9243394529910824E-4</v>
       </c>
       <c r="L7">
-        <v>1.8844325145648676E-4</v>
+        <v>3.0029608754105223E-5</v>
       </c>
       <c r="M7">
-        <v>3.9167908209026246E-4</v>
+        <v>7.8653882924832304E-4</v>
       </c>
       <c r="N7">
-        <v>-8.262045012459491E-5</v>
+        <v>-8.7621857450400118E-5</v>
       </c>
       <c r="O7">
-        <v>4.0030570322108433E-4</v>
+        <v>3.0706206372059508E-4</v>
       </c>
       <c r="P7">
-        <v>-5.3807565560107067E-4</v>
+        <v>-3.8917249117162087E-4</v>
       </c>
       <c r="Q7">
-        <v>1.4587848290245289E-4</v>
+        <v>7.8849063188927618E-5</v>
       </c>
       <c r="R7">
-        <v>1.0135611887132582E-3</v>
+        <v>-3.4495967587960374E-4</v>
       </c>
       <c r="S7">
-        <v>-2.5890984242667864E-4</v>
+        <v>-2.0839176344674727E-4</v>
       </c>
       <c r="T7">
-        <v>-1.6346246494348439E-4</v>
+        <v>-2.5708239547763811E-4</v>
       </c>
       <c r="U7">
-        <v>-2.1245470463774957E-5</v>
+        <v>-2.9288476117113435E-5</v>
       </c>
       <c r="V7">
-        <v>-1.238533700910731E-2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+        <v>-7.3796558296811542E-3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A8" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="B8">
-        <v>0.16639773044221021</v>
+      <c r="B8" s="7">
+        <v>0.28034907297364431</v>
       </c>
       <c r="C8">
-        <v>1.4270565002178362E-5</v>
+        <v>-4.6487138081426058E-6</v>
       </c>
       <c r="D8">
-        <v>1.3761997408411674E-5</v>
+        <v>4.2406753944210273E-6</v>
       </c>
       <c r="E8">
-        <v>-1.360103062185802E-8</v>
+        <v>5.5149917355223202E-8</v>
       </c>
       <c r="F8">
-        <v>8.6460763357301587E-5</v>
+        <v>6.8868335669312135E-5</v>
       </c>
       <c r="G8">
-        <v>-2.7054800886163659E-4</v>
+        <v>-1.1775970383402369E-4</v>
       </c>
       <c r="H8">
-        <v>3.4286990710068318E-3</v>
+        <v>2.2560542814690143E-3</v>
       </c>
       <c r="I8">
-        <v>5.1414474271983431E-3</v>
+        <v>3.051123934716841E-3</v>
       </c>
       <c r="J8">
-        <v>3.1845721864226326E-3</v>
+        <v>1.9724959348714211E-3</v>
       </c>
       <c r="K8">
-        <v>1.8283577799184814E-6</v>
+        <v>8.6838261349557011E-5</v>
       </c>
       <c r="L8">
-        <v>1.6619300382601513E-4</v>
+        <v>8.8152849701631436E-5</v>
       </c>
       <c r="M8">
-        <v>-2.4306821687208855E-4</v>
+        <v>3.2097412707046734E-5</v>
       </c>
       <c r="N8">
-        <v>1.1209135461082933E-4</v>
+        <v>8.3388620188741368E-5</v>
       </c>
       <c r="O8">
-        <v>3.3358397714359199E-4</v>
+        <v>2.1675696181716733E-4</v>
       </c>
       <c r="P8">
-        <v>-2.1317742418158498E-4</v>
+        <v>-1.8337962790230481E-4</v>
       </c>
       <c r="Q8">
-        <v>1.5516486215474561E-4</v>
+        <v>8.4660560168911046E-5</v>
       </c>
       <c r="R8">
-        <v>5.0431878187459384E-4</v>
+        <v>-8.0228056018762876E-5</v>
       </c>
       <c r="S8">
-        <v>-1.5474670019208561E-4</v>
+        <v>-6.2458385657064922E-5</v>
       </c>
       <c r="T8">
-        <v>-2.5115325060588939E-4</v>
+        <v>-8.2940381995181677E-5</v>
       </c>
       <c r="U8">
-        <v>-3.2452648068804438E-5</v>
+        <v>-6.2805114046262213E-6</v>
       </c>
       <c r="V8">
-        <v>-4.2472353176065689E-3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+        <v>-2.9760603374614954E-3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A9" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="B9">
-        <v>-7.1415898247411316E-3</v>
+      <c r="B9" s="7">
+        <v>0.10953836344419209</v>
       </c>
       <c r="C9">
-        <v>8.2845034391447302E-5</v>
+        <v>5.3220615243854014E-5</v>
       </c>
       <c r="D9">
-        <v>8.3106938023813789E-5</v>
+        <v>6.179341405444913E-5</v>
       </c>
       <c r="E9">
-        <v>-1.6032917690542159E-6</v>
+        <v>-1.1705271592303572E-6</v>
       </c>
       <c r="F9">
-        <v>-1.5203168396467467E-4</v>
+        <v>-2.3080186652892608E-5</v>
       </c>
       <c r="G9">
-        <v>7.6682650764123262E-5</v>
+        <v>1.231818716282329E-4</v>
       </c>
       <c r="H9">
-        <v>3.0751409198209977E-3</v>
+        <v>2.0297793868160438E-3</v>
       </c>
       <c r="I9">
-        <v>3.1845721864226326E-3</v>
+        <v>1.9724959348714211E-3</v>
       </c>
       <c r="J9">
-        <v>7.37949095712662E-3</v>
+        <v>4.9052030797568143E-3</v>
       </c>
       <c r="K9">
-        <v>1.6940868555279402E-4</v>
+        <v>1.3666528444369582E-4</v>
       </c>
       <c r="L9">
-        <v>2.9761653502260337E-5</v>
+        <v>-1.8119519447380462E-5</v>
       </c>
       <c r="M9">
-        <v>-2.9340989873860395E-4</v>
+        <v>7.5877873120355765E-5</v>
       </c>
       <c r="N9">
-        <v>1.2235570914054142E-4</v>
+        <v>2.4221651217443737E-6</v>
       </c>
       <c r="O9">
-        <v>4.2573645244729894E-4</v>
+        <v>2.5743446012845033E-4</v>
       </c>
       <c r="P9">
-        <v>-3.6628419725134084E-4</v>
+        <v>-3.5336106602799899E-5</v>
       </c>
       <c r="Q9">
-        <v>1.5946988228466289E-4</v>
+        <v>1.0433508441596526E-4</v>
       </c>
       <c r="R9">
-        <v>4.7641804298572451E-4</v>
+        <v>5.746678372927326E-6</v>
       </c>
       <c r="S9">
-        <v>-6.2000117197029414E-5</v>
+        <v>-1.3149505768978408E-5</v>
       </c>
       <c r="T9">
-        <v>-2.1132731744895154E-4</v>
+        <v>-2.1889121172079511E-5</v>
       </c>
       <c r="U9">
-        <v>1.0432993781881112E-5</v>
+        <v>-3.5821513856973473E-6</v>
       </c>
       <c r="V9">
-        <v>-5.2776353262631269E-3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+        <v>-3.1010922969466103E-3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A10" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="B10">
-        <v>0.23500698437330511</v>
+      <c r="B10" s="7">
+        <v>0.47128913960443108</v>
       </c>
       <c r="C10">
-        <v>9.5886826367482414E-5</v>
+        <v>8.3409411279669854E-5</v>
       </c>
       <c r="D10">
-        <v>-4.5646286713101926E-6</v>
+        <v>1.5606194137884573E-5</v>
       </c>
       <c r="E10">
-        <v>3.3362063305863783E-7</v>
+        <v>6.2880072064145369E-8</v>
       </c>
       <c r="F10">
-        <v>1.0051083081741177E-4</v>
+        <v>8.541558858321573E-5</v>
       </c>
       <c r="G10">
-        <v>-1.8339143456168805E-4</v>
+        <v>-9.3191668775842061E-5</v>
       </c>
       <c r="H10">
-        <v>9.3104367300457123E-4</v>
+        <v>7.9243394529910824E-4</v>
       </c>
       <c r="I10">
-        <v>1.8283577799184814E-6</v>
+        <v>8.6838261349557011E-5</v>
       </c>
       <c r="J10">
-        <v>1.6940868555279402E-4</v>
+        <v>1.3666528444369582E-4</v>
       </c>
       <c r="K10">
-        <v>3.0363699926819424E-3</v>
+        <v>2.0845542458010329E-3</v>
       </c>
       <c r="L10">
-        <v>1.3105670050701081E-3</v>
+        <v>8.4884883712644079E-4</v>
       </c>
       <c r="M10">
-        <v>1.470251329307544E-3</v>
+        <v>1.2694817006289518E-3</v>
       </c>
       <c r="N10">
-        <v>-1.0202493291416681E-4</v>
+        <v>-6.6160844266576331E-5</v>
       </c>
       <c r="O10">
-        <v>7.506617821712544E-6</v>
+        <v>3.3402614822851941E-6</v>
       </c>
       <c r="P10">
-        <v>-7.4228273894361369E-4</v>
+        <v>-5.9151352873302622E-4</v>
       </c>
       <c r="Q10">
-        <v>3.5752665784221197E-5</v>
+        <v>1.292337452523666E-5</v>
       </c>
       <c r="R10">
-        <v>-1.1507756982667146E-3</v>
+        <v>-2.6988221335135865E-4</v>
       </c>
       <c r="S10">
-        <v>1.6727746041220507E-4</v>
+        <v>1.0342916393401712E-4</v>
       </c>
       <c r="T10">
-        <v>2.8478642112929309E-4</v>
+        <v>1.6438283524988697E-4</v>
       </c>
       <c r="U10">
-        <v>-6.5094130906932806E-5</v>
+        <v>-1.6331434904603721E-5</v>
       </c>
       <c r="V10">
-        <v>-1.145854390394311E-3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+        <v>-1.6843559474522033E-3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A11" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="B11">
-        <v>-4.5927131415252752E-2</v>
+      <c r="B11" s="7">
+        <v>0.11718800537777413</v>
       </c>
       <c r="C11">
-        <v>1.8108176205045728E-4</v>
+        <v>1.1649302345571012E-4</v>
       </c>
       <c r="D11">
-        <v>1.2879957769656222E-4</v>
+        <v>8.8067175873391082E-5</v>
       </c>
       <c r="E11">
-        <v>-1.0711659155564057E-6</v>
+        <v>-7.4292881573353301E-7</v>
       </c>
       <c r="F11">
-        <v>1.0220553615922604E-4</v>
+        <v>6.9730838882652333E-5</v>
       </c>
       <c r="G11">
-        <v>-1.100943285642982E-5</v>
+        <v>-1.9556601208192714E-6</v>
       </c>
       <c r="H11">
-        <v>1.8844325145648676E-4</v>
+        <v>3.0029608754105223E-5</v>
       </c>
       <c r="I11">
-        <v>1.6619300382601513E-4</v>
+        <v>8.8152849701631436E-5</v>
       </c>
       <c r="J11">
-        <v>2.9761653502260337E-5</v>
+        <v>-1.8119519447380462E-5</v>
       </c>
       <c r="K11">
-        <v>1.3105670050701081E-3</v>
+        <v>8.4884883712644079E-4</v>
       </c>
       <c r="L11">
-        <v>2.4447697360557522E-3</v>
+        <v>1.5402306285313436E-3</v>
       </c>
       <c r="M11">
-        <v>1.2735218420721851E-3</v>
+        <v>8.7206481558478447E-4</v>
       </c>
       <c r="N11">
-        <v>-1.1333914681204786E-5</v>
+        <v>-4.84209069887186E-6</v>
       </c>
       <c r="O11">
-        <v>2.2330849369483206E-6</v>
+        <v>-4.6684567762065907E-7</v>
       </c>
       <c r="P11">
-        <v>1.0684137516602573E-4</v>
+        <v>-2.8175253174019628E-4</v>
       </c>
       <c r="Q11">
-        <v>1.3992510526407252E-5</v>
+        <v>1.1297179089084807E-6</v>
       </c>
       <c r="R11">
-        <v>-8.1514751036977943E-4</v>
+        <v>-7.463651843954899E-5</v>
       </c>
       <c r="S11">
-        <v>1.0371174849722973E-4</v>
+        <v>6.4244863122926623E-5</v>
       </c>
       <c r="T11">
-        <v>1.261337275724481E-4</v>
+        <v>7.7847682314168953E-5</v>
       </c>
       <c r="U11">
-        <v>-2.8138975181209907E-5</v>
+        <v>-1.166997257368821E-5</v>
       </c>
       <c r="V11">
-        <v>-4.5797965668783296E-3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+        <v>-3.1199258434303056E-3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A12" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="B12">
-        <v>0.46200520315674559</v>
+      <c r="B12" s="7">
+        <v>0.9893644613640965</v>
       </c>
       <c r="C12">
-        <v>4.8965286095745456E-4</v>
+        <v>4.4712129864333112E-4</v>
       </c>
       <c r="D12">
-        <v>2.3524362885253761E-5</v>
+        <v>2.0040447910810253E-5</v>
       </c>
       <c r="E12">
-        <v>-2.4810420748384026E-8</v>
+        <v>4.2360611942332793E-8</v>
       </c>
       <c r="F12">
-        <v>3.6060936461811217E-5</v>
+        <v>1.8891818175762539E-5</v>
       </c>
       <c r="G12">
-        <v>9.769262314789426E-5</v>
+        <v>3.8328041133317472E-6</v>
       </c>
       <c r="H12">
-        <v>3.9167908209026246E-4</v>
+        <v>7.8653882924832304E-4</v>
       </c>
       <c r="I12">
-        <v>-2.4306821687208855E-4</v>
+        <v>3.2097412707046734E-5</v>
       </c>
       <c r="J12">
-        <v>-2.9340989873860395E-4</v>
+        <v>7.5877873120355765E-5</v>
       </c>
       <c r="K12">
-        <v>1.470251329307544E-3</v>
+        <v>1.2694817006289518E-3</v>
       </c>
       <c r="L12">
-        <v>1.2735218420721851E-3</v>
+        <v>8.7206481558478447E-4</v>
       </c>
       <c r="M12">
-        <v>1.0692544428054129E-2</v>
+        <v>9.4058869892767842E-3</v>
       </c>
       <c r="N12">
-        <v>-3.0811641743139491E-5</v>
+        <v>-6.5882487254454202E-6</v>
       </c>
       <c r="O12">
-        <v>-3.0268893081522122E-6</v>
+        <v>2.4792015389526014E-6</v>
       </c>
       <c r="P12">
-        <v>-2.7890888990913893E-3</v>
+        <v>-2.0277723038924804E-3</v>
       </c>
       <c r="Q12">
-        <v>3.192530733616863E-5</v>
+        <v>-6.8742233237918735E-6</v>
       </c>
       <c r="R12">
-        <v>-1.7434094803376694E-3</v>
+        <v>-8.6130836239424263E-4</v>
       </c>
       <c r="S12">
-        <v>-1.3627785267768841E-4</v>
+        <v>7.504647896210072E-5</v>
       </c>
       <c r="T12">
-        <v>-3.7803413501324426E-5</v>
+        <v>1.7690629576842733E-4</v>
       </c>
       <c r="U12">
-        <v>7.3616093812886477E-6</v>
+        <v>-2.2389904649799711E-5</v>
       </c>
       <c r="V12">
-        <v>-2.5205771843853854E-3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+        <v>-1.9387887671059607E-3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A13" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="B13">
-        <v>-0.10866045667910253</v>
+      <c r="B13" s="7">
+        <v>-8.2941991787264135E-2</v>
       </c>
       <c r="C13">
-        <v>-7.1258715870670962E-6</v>
+        <v>1.3776151972405473E-5</v>
       </c>
       <c r="D13">
-        <v>3.6979020959820325E-5</v>
+        <v>2.2431530768432961E-5</v>
       </c>
       <c r="E13">
-        <v>-2.2237180158060585E-7</v>
+        <v>-1.1619424757961462E-7</v>
       </c>
       <c r="F13">
-        <v>4.9705165827533345E-5</v>
+        <v>3.7095591899758288E-5</v>
       </c>
       <c r="G13">
-        <v>2.1372567429310364E-4</v>
+        <v>1.5014108839432491E-4</v>
       </c>
       <c r="H13">
-        <v>-8.262045012459491E-5</v>
+        <v>-8.7621857450400118E-5</v>
       </c>
       <c r="I13">
-        <v>1.1209135461082933E-4</v>
+        <v>8.3388620188741368E-5</v>
       </c>
       <c r="J13">
-        <v>1.2235570914054142E-4</v>
+        <v>2.4221651217443737E-6</v>
       </c>
       <c r="K13">
-        <v>-1.0202493291416681E-4</v>
+        <v>-6.6160844266576331E-5</v>
       </c>
       <c r="L13">
-        <v>-1.1333914681204786E-5</v>
+        <v>-4.84209069887186E-6</v>
       </c>
       <c r="M13">
-        <v>-3.0811641743139491E-5</v>
+        <v>-6.5882487254454202E-6</v>
       </c>
       <c r="N13">
-        <v>5.7004911443126664E-4</v>
+        <v>3.7831755697071052E-4</v>
       </c>
       <c r="O13">
-        <v>-1.7272892182135692E-5</v>
+        <v>-1.3931260921890379E-5</v>
       </c>
       <c r="P13">
-        <v>9.7183925307579074E-5</v>
+        <v>3.0675914185544079E-5</v>
       </c>
       <c r="Q13">
-        <v>-1.6208286306540601E-5</v>
+        <v>-9.512369293589723E-6</v>
       </c>
       <c r="R13">
-        <v>1.078053812205112E-4</v>
+        <v>1.0401928970376912E-5</v>
       </c>
       <c r="S13">
-        <v>2.9789849064579613E-5</v>
+        <v>-1.9570708849217392E-5</v>
       </c>
       <c r="T13">
-        <v>5.3205875615289222E-5</v>
+        <v>-1.4557249491753323E-5</v>
       </c>
       <c r="U13">
-        <v>-8.0015060703041998E-6</v>
+        <v>-5.2170992614186792E-6</v>
       </c>
       <c r="V13">
-        <v>-3.093967204153788E-3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+        <v>-1.9917435720328085E-3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A14" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="B14">
-        <v>2.5912993966848395E-2</v>
+      <c r="B14" s="7">
+        <v>2.3975932395520701E-2</v>
       </c>
       <c r="C14">
-        <v>-3.4474179288916255E-5</v>
+        <v>-1.9243580918563753E-5</v>
       </c>
       <c r="D14">
-        <v>-4.0648543535980541E-6</v>
+        <v>-2.5709699252318203E-6</v>
       </c>
       <c r="E14">
-        <v>2.8761839958619851E-8</v>
+        <v>2.6885104899113038E-8</v>
       </c>
       <c r="F14">
-        <v>1.1071687872663008E-5</v>
+        <v>1.7189822084381869E-5</v>
       </c>
       <c r="G14">
-        <v>2.7399328908667175E-5</v>
+        <v>2.729921812495531E-5</v>
       </c>
       <c r="H14">
-        <v>4.0030570322108433E-4</v>
+        <v>3.0706206372059508E-4</v>
       </c>
       <c r="I14">
-        <v>3.3358397714359199E-4</v>
+        <v>2.1675696181716733E-4</v>
       </c>
       <c r="J14">
-        <v>4.2573645244729894E-4</v>
+        <v>2.5743446012845033E-4</v>
       </c>
       <c r="K14">
-        <v>7.506617821712544E-6</v>
+        <v>3.3402614822851941E-6</v>
       </c>
       <c r="L14">
-        <v>2.2330849369483206E-6</v>
+        <v>-4.6684567762065907E-7</v>
       </c>
       <c r="M14">
-        <v>-3.0268893081522122E-6</v>
+        <v>2.4792015389526014E-6</v>
       </c>
       <c r="N14">
-        <v>-1.7272892182135692E-5</v>
+        <v>-1.3931260921890379E-5</v>
       </c>
       <c r="O14">
-        <v>1.2384578566498127E-4</v>
+        <v>8.1151201292349105E-5</v>
       </c>
       <c r="P14">
-        <v>-1.7126279587525181E-5</v>
+        <v>-1.0664658282397307E-5</v>
       </c>
       <c r="Q14">
-        <v>-4.637189899945121E-5</v>
+        <v>-3.0946593457702439E-5</v>
       </c>
       <c r="R14">
-        <v>9.4472456299593229E-5</v>
+        <v>-1.7307310165729E-5</v>
       </c>
       <c r="S14">
-        <v>-4.1379957500892428E-5</v>
+        <v>-1.8521718228332786E-5</v>
       </c>
       <c r="T14">
-        <v>-5.397381016423593E-5</v>
+        <v>-2.2635108108112918E-5</v>
       </c>
       <c r="U14">
-        <v>-4.4819129949591959E-6</v>
+        <v>-3.2307395265379293E-6</v>
       </c>
       <c r="V14">
-        <v>-2.1909813371359346E-4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+        <v>-1.6674304676853578E-4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A15" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B15">
-        <v>7.0692730265682799</v>
+      <c r="B15" s="7">
+        <v>3.3289135184300083</v>
       </c>
       <c r="C15">
-        <v>1.2402570323351595E-5</v>
+        <v>5.1186259168677019E-5</v>
       </c>
       <c r="D15">
-        <v>4.1774745489510899E-5</v>
+        <v>-2.0318779196285908E-5</v>
       </c>
       <c r="E15">
-        <v>-4.1998940549364128E-7</v>
+        <v>1.1599537754993857E-7</v>
       </c>
       <c r="F15">
-        <v>9.0613960543462413E-4</v>
+        <v>1.662240947917649E-4</v>
       </c>
       <c r="G15">
-        <v>1.0301538047408822E-3</v>
+        <v>3.9410731264859699E-4</v>
       </c>
       <c r="H15">
-        <v>-5.3807565560107067E-4</v>
+        <v>-3.8917249117162087E-4</v>
       </c>
       <c r="I15">
-        <v>-2.1317742418158498E-4</v>
+        <v>-1.8337962790230481E-4</v>
       </c>
       <c r="J15">
-        <v>-3.6628419725134084E-4</v>
+        <v>-3.5336106602799899E-5</v>
       </c>
       <c r="K15">
-        <v>-7.4228273894361369E-4</v>
+        <v>-5.9151352873302622E-4</v>
       </c>
       <c r="L15">
-        <v>1.0684137516602573E-4</v>
+        <v>-2.8175253174019628E-4</v>
       </c>
       <c r="M15">
-        <v>-2.7890888990913893E-3</v>
+        <v>-2.0277723038924804E-3</v>
       </c>
       <c r="N15">
-        <v>9.7183925307579074E-5</v>
+        <v>3.0675914185544079E-5</v>
       </c>
       <c r="O15">
-        <v>-1.7126279587525181E-5</v>
+        <v>-1.0664658282397307E-5</v>
       </c>
       <c r="P15">
-        <v>7.3315293489142425E-2</v>
+        <v>2.110886588171304E-2</v>
       </c>
       <c r="Q15">
-        <v>-1.2768263017220939E-4</v>
+        <v>1.0474556963167991E-5</v>
       </c>
       <c r="R15">
-        <v>-1.3112170827403732E-2</v>
+        <v>-1.1951708977584251E-3</v>
       </c>
       <c r="S15">
-        <v>-3.5153758640037083E-4</v>
+        <v>-1.302995373486724E-4</v>
       </c>
       <c r="T15">
-        <v>-1.5398136049638478E-4</v>
+        <v>-1.8441887241972934E-5</v>
       </c>
       <c r="U15">
-        <v>7.5773966119565541E-5</v>
+        <v>2.9286435189626066E-5</v>
       </c>
       <c r="V15">
-        <v>-3.6814566968321554E-3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+        <v>-5.1646375057862127E-4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A16" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B16">
-        <v>-5.754197291963495E-3</v>
+      <c r="B16" s="7">
+        <v>6.1391422278524238E-3</v>
       </c>
       <c r="C16">
-        <v>2.2212556422599223E-6</v>
+        <v>-6.140787039427654E-6</v>
       </c>
       <c r="D16">
-        <v>-1.8618630636062628E-5</v>
+        <v>-1.0640272748454493E-5</v>
       </c>
       <c r="E16">
-        <v>1.9221429673375618E-7</v>
+        <v>1.0337170516395234E-7</v>
       </c>
       <c r="F16">
-        <v>1.4541868396171902E-5</v>
+        <v>1.2658843820220356E-5</v>
       </c>
       <c r="G16">
-        <v>2.6617643300281093E-5</v>
+        <v>2.0369358998253919E-5</v>
       </c>
       <c r="H16">
-        <v>1.4587848290245289E-4</v>
+        <v>7.8849063188927618E-5</v>
       </c>
       <c r="I16">
-        <v>1.5516486215474561E-4</v>
+        <v>8.4660560168911046E-5</v>
       </c>
       <c r="J16">
-        <v>1.5946988228466289E-4</v>
+        <v>1.0433508441596526E-4</v>
       </c>
       <c r="K16">
-        <v>3.5752665784221197E-5</v>
+        <v>1.292337452523666E-5</v>
       </c>
       <c r="L16">
-        <v>1.3992510526407252E-5</v>
+        <v>1.1297179089084807E-6</v>
       </c>
       <c r="M16">
-        <v>3.192530733616863E-5</v>
+        <v>-6.8742233237918735E-6</v>
       </c>
       <c r="N16">
-        <v>-1.6208286306540601E-5</v>
+        <v>-9.512369293589723E-6</v>
       </c>
       <c r="O16">
-        <v>-4.637189899945121E-5</v>
+        <v>-3.0946593457702439E-5</v>
       </c>
       <c r="P16">
-        <v>-1.2768263017220939E-4</v>
+        <v>1.0474556963167991E-5</v>
       </c>
       <c r="Q16">
-        <v>9.821380462481452E-5</v>
+        <v>6.06652723242525E-5</v>
       </c>
       <c r="R16">
-        <v>-5.6370746236863106E-5</v>
+        <v>2.4492207754567031E-5</v>
       </c>
       <c r="S16">
-        <v>1.062247167410267E-5</v>
+        <v>1.4341051888368253E-5</v>
       </c>
       <c r="T16">
-        <v>8.8111897147937683E-6</v>
+        <v>1.2030844359734697E-5</v>
       </c>
       <c r="U16">
-        <v>-8.0850744012651422E-6</v>
+        <v>-1.4975870693212087E-6</v>
       </c>
       <c r="V16">
-        <v>2.6678074114173966E-4</v>
-      </c>
-    </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+        <v>1.1248659172277342E-4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A17" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="B17">
-        <v>4.5654982828799087</v>
+      <c r="B17" s="7">
+        <v>2.3672517942967479</v>
       </c>
       <c r="C17">
-        <v>2.6907939063330107E-4</v>
+        <v>3.3481041432229419E-5</v>
       </c>
       <c r="D17">
-        <v>7.7862622419774515E-5</v>
+        <v>-1.2093647135070487E-5</v>
       </c>
       <c r="E17">
-        <v>-6.7472405374665402E-7</v>
+        <v>6.6026336596895343E-8</v>
       </c>
       <c r="F17">
-        <v>3.6112106786997467E-4</v>
+        <v>1.4163968864685443E-4</v>
       </c>
       <c r="G17">
-        <v>3.1053816982208561E-4</v>
+        <v>1.869173069896468E-4</v>
       </c>
       <c r="H17">
-        <v>1.0135611887132582E-3</v>
+        <v>-3.4495967587960374E-4</v>
       </c>
       <c r="I17">
-        <v>5.0431878187459384E-4</v>
+        <v>-8.0228056018762876E-5</v>
       </c>
       <c r="J17">
-        <v>4.7641804298572451E-4</v>
+        <v>5.746678372927326E-6</v>
       </c>
       <c r="K17">
-        <v>-1.1507756982667146E-3</v>
+        <v>-2.6988221335135865E-4</v>
       </c>
       <c r="L17">
-        <v>-8.1514751036977943E-4</v>
+        <v>-7.463651843954899E-5</v>
       </c>
       <c r="M17">
-        <v>-1.7434094803376694E-3</v>
+        <v>-8.6130836239424263E-4</v>
       </c>
       <c r="N17">
-        <v>1.078053812205112E-4</v>
+        <v>1.0401928970376912E-5</v>
       </c>
       <c r="O17">
-        <v>9.4472456299593229E-5</v>
+        <v>-1.7307310165729E-5</v>
       </c>
       <c r="P17">
-        <v>-1.3112170827403732E-2</v>
+        <v>-1.1951708977584251E-3</v>
       </c>
       <c r="Q17">
-        <v>-5.6370746236863106E-5</v>
+        <v>2.4492207754567031E-5</v>
       </c>
       <c r="R17">
-        <v>6.3693031208577111E-2</v>
+        <v>1.3104475362297714E-2</v>
       </c>
       <c r="S17">
-        <v>-3.884454469777858E-4</v>
+        <v>-7.7164404514042334E-5</v>
       </c>
       <c r="T17">
-        <v>-1.8543824192077726E-4</v>
+        <v>-1.0731073923734495E-4</v>
       </c>
       <c r="U17">
-        <v>4.4754599708568868E-5</v>
+        <v>7.0339519457741326E-6</v>
       </c>
       <c r="V17">
-        <v>-4.4825449281234954E-3</v>
-      </c>
-    </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+        <v>-1.7308066114394785E-4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A18" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="B18">
-        <v>0.21966248655960974</v>
+      <c r="B18" s="7">
+        <v>0.18146203210633352</v>
       </c>
       <c r="C18">
-        <v>-3.4536995436787953E-5</v>
+        <v>-1.7504202512307271E-5</v>
       </c>
       <c r="D18">
-        <v>-1.180677192513151E-6</v>
+        <v>-9.6889151516777383E-6</v>
       </c>
       <c r="E18">
-        <v>8.2542880529303439E-8</v>
+        <v>1.3255191373696076E-7</v>
       </c>
       <c r="F18">
-        <v>-2.9005724964611371E-4</v>
+        <v>-2.3540059415884753E-4</v>
       </c>
       <c r="G18">
-        <v>-5.7476489544938366E-4</v>
+        <v>-3.8816736328825584E-4</v>
       </c>
       <c r="H18">
-        <v>-2.5890984242667864E-4</v>
+        <v>-2.0839176344674727E-4</v>
       </c>
       <c r="I18">
-        <v>-1.5474670019208561E-4</v>
+        <v>-6.2458385657064922E-5</v>
       </c>
       <c r="J18">
-        <v>-6.2000117197029414E-5</v>
+        <v>-1.3149505768978408E-5</v>
       </c>
       <c r="K18">
-        <v>1.6727746041220507E-4</v>
+        <v>1.0342916393401712E-4</v>
       </c>
       <c r="L18">
-        <v>1.0371174849722973E-4</v>
+        <v>6.4244863122926623E-5</v>
       </c>
       <c r="M18">
-        <v>-1.3627785267768841E-4</v>
+        <v>7.504647896210072E-5</v>
       </c>
       <c r="N18">
-        <v>2.9789849064579613E-5</v>
+        <v>-1.9570708849217392E-5</v>
       </c>
       <c r="O18">
-        <v>-4.1379957500892428E-5</v>
+        <v>-1.8521718228332786E-5</v>
       </c>
       <c r="P18">
-        <v>-3.5153758640037083E-4</v>
+        <v>-1.302995373486724E-4</v>
       </c>
       <c r="Q18">
-        <v>1.062247167410267E-5</v>
+        <v>1.4341051888368253E-5</v>
       </c>
       <c r="R18">
-        <v>-3.884454469777858E-4</v>
+        <v>-7.7164404514042334E-5</v>
       </c>
       <c r="S18">
-        <v>3.6529957357718619E-3</v>
+        <v>2.2353699398028537E-3</v>
       </c>
       <c r="T18">
-        <v>2.5431199816202052E-3</v>
+        <v>1.5077469156183636E-3</v>
       </c>
       <c r="U18">
-        <v>-3.9682390920836152E-5</v>
+        <v>-2.2442899494066043E-5</v>
       </c>
       <c r="V18">
-        <v>-1.6782429909114138E-3</v>
-      </c>
-    </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+        <v>-6.9804464697652735E-4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A19" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="B19">
-        <v>0.51054777236701676</v>
+      <c r="B19" s="7">
+        <v>0.44142752781695577</v>
       </c>
       <c r="C19">
-        <v>-2.1158412833762472E-5</v>
+        <v>-9.6350713912218442E-6</v>
       </c>
       <c r="D19">
-        <v>7.783394038064469E-6</v>
+        <v>-8.2193477312209441E-6</v>
       </c>
       <c r="E19">
-        <v>3.9492116029696966E-8</v>
+        <v>1.2531789860559363E-7</v>
       </c>
       <c r="F19">
-        <v>-2.2898368096291788E-4</v>
+        <v>-1.8732762487271015E-4</v>
       </c>
       <c r="G19">
-        <v>-5.3409133995265673E-4</v>
+        <v>-3.832881521058395E-4</v>
       </c>
       <c r="H19">
-        <v>-1.6346246494348439E-4</v>
+        <v>-2.5708239547763811E-4</v>
       </c>
       <c r="I19">
-        <v>-2.5115325060588939E-4</v>
+        <v>-8.2940381995181677E-5</v>
       </c>
       <c r="J19">
-        <v>-2.1132731744895154E-4</v>
+        <v>-2.1889121172079511E-5</v>
       </c>
       <c r="K19">
-        <v>2.8478642112929309E-4</v>
+        <v>1.6438283524988697E-4</v>
       </c>
       <c r="L19">
-        <v>1.261337275724481E-4</v>
+        <v>7.7847682314168953E-5</v>
       </c>
       <c r="M19">
-        <v>-3.7803413501324426E-5</v>
+        <v>1.7690629576842733E-4</v>
       </c>
       <c r="N19">
-        <v>5.3205875615289222E-5</v>
+        <v>-1.4557249491753323E-5</v>
       </c>
       <c r="O19">
-        <v>-5.397381016423593E-5</v>
+        <v>-2.2635108108112918E-5</v>
       </c>
       <c r="P19">
-        <v>-1.5398136049638478E-4</v>
+        <v>-1.8441887241972934E-5</v>
       </c>
       <c r="Q19">
-        <v>8.8111897147937683E-6</v>
+        <v>1.2030844359734697E-5</v>
       </c>
       <c r="R19">
-        <v>-1.8543824192077726E-4</v>
+        <v>-1.0731073923734495E-4</v>
       </c>
       <c r="S19">
-        <v>2.5431199816202052E-3</v>
+        <v>1.5077469156183636E-3</v>
       </c>
       <c r="T19">
-        <v>3.0821340251115572E-3</v>
+        <v>1.8650049027750643E-3</v>
       </c>
       <c r="U19">
-        <v>-3.093146687980388E-5</v>
+        <v>-1.9757345747068082E-5</v>
       </c>
       <c r="V19">
-        <v>-2.2329137880258139E-3</v>
-      </c>
-    </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+        <v>-8.3394758209854984E-4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A20" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="B20">
-        <v>3.4517328250294145E-3</v>
+      <c r="B20" s="7">
+        <v>-3.5124590603923291E-2</v>
       </c>
       <c r="C20">
-        <v>3.2905367248700103E-6</v>
+        <v>9.1807101588888923E-7</v>
       </c>
       <c r="D20">
-        <v>4.265086315686519E-6</v>
+        <v>6.1381446061721035E-7</v>
       </c>
       <c r="E20">
-        <v>-7.4632366165973545E-8</v>
+        <v>-1.841961348706978E-8</v>
       </c>
       <c r="F20">
-        <v>-1.7954673059784214E-5</v>
+        <v>-2.2817143354046307E-6</v>
       </c>
       <c r="G20">
-        <v>-7.6188025764043496E-6</v>
+        <v>-1.0365248146030389E-6</v>
       </c>
       <c r="H20">
-        <v>-2.1245470463774957E-5</v>
+        <v>-2.9288476117113435E-5</v>
       </c>
       <c r="I20">
-        <v>-3.2452648068804438E-5</v>
+        <v>-6.2805114046262213E-6</v>
       </c>
       <c r="J20">
-        <v>1.0432993781881112E-5</v>
+        <v>-3.5821513856973473E-6</v>
       </c>
       <c r="K20">
-        <v>-6.5094130906932806E-5</v>
+        <v>-1.6331434904603721E-5</v>
       </c>
       <c r="L20">
-        <v>-2.8138975181209907E-5</v>
+        <v>-1.166997257368821E-5</v>
       </c>
       <c r="M20">
-        <v>7.3616093812886477E-6</v>
+        <v>-2.2389904649799711E-5</v>
       </c>
       <c r="N20">
-        <v>-8.0015060703041998E-6</v>
+        <v>-5.2170992614186792E-6</v>
       </c>
       <c r="O20">
-        <v>-4.4819129949591959E-6</v>
+        <v>-3.2307395265379293E-6</v>
       </c>
       <c r="P20">
-        <v>7.5773966119565541E-5</v>
+        <v>2.9286435189626066E-5</v>
       </c>
       <c r="Q20">
-        <v>-8.0850744012651422E-6</v>
+        <v>-1.4975870693212087E-6</v>
       </c>
       <c r="R20">
-        <v>4.4754599708568868E-5</v>
+        <v>7.0339519457741326E-6</v>
       </c>
       <c r="S20">
-        <v>-3.9682390920836152E-5</v>
+        <v>-2.2442899494066043E-5</v>
       </c>
       <c r="T20">
-        <v>-3.093146687980388E-5</v>
+        <v>-1.9757345747068082E-5</v>
       </c>
       <c r="U20">
-        <v>6.5227200815642304E-5</v>
+        <v>2.1472428541903495E-5</v>
       </c>
       <c r="V20">
-        <v>-9.0186218501598779E-4</v>
-      </c>
-    </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+        <v>-2.5324972738849865E-4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A21" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B21">
-        <v>-1.5621795536642773</v>
+      <c r="B21" s="7">
+        <v>-1.1297035541990583</v>
       </c>
       <c r="C21">
-        <v>-1.2887301842413922E-3</v>
+        <v>-9.1134439244929281E-4</v>
       </c>
       <c r="D21">
-        <v>-2.0174112551368611E-3</v>
+        <v>-1.2490225474787219E-3</v>
       </c>
       <c r="E21">
-        <v>1.8322047212456053E-5</v>
+        <v>1.1067997997374866E-5</v>
       </c>
       <c r="F21">
-        <v>-2.1875377063241717E-3</v>
+        <v>-1.7261318982335001E-3</v>
       </c>
       <c r="G21">
-        <v>-3.5432578355001935E-3</v>
+        <v>-2.4823836671913771E-3</v>
       </c>
       <c r="H21">
-        <v>-1.238533700910731E-2</v>
+        <v>-7.3796558296811542E-3</v>
       </c>
       <c r="I21">
-        <v>-4.2472353176065689E-3</v>
+        <v>-2.9760603374614954E-3</v>
       </c>
       <c r="J21">
-        <v>-5.2776353262631269E-3</v>
+        <v>-3.1010922969466103E-3</v>
       </c>
       <c r="K21">
-        <v>-1.145854390394311E-3</v>
+        <v>-1.6843559474522033E-3</v>
       </c>
       <c r="L21">
-        <v>-4.5797965668783296E-3</v>
+        <v>-3.1199258434303056E-3</v>
       </c>
       <c r="M21">
-        <v>-2.5205771843853854E-3</v>
+        <v>-1.9387887671059607E-3</v>
       </c>
       <c r="N21">
-        <v>-3.093967204153788E-3</v>
+        <v>-1.9917435720328085E-3</v>
       </c>
       <c r="O21">
-        <v>-2.1909813371359346E-4</v>
+        <v>-1.6674304676853578E-4</v>
       </c>
       <c r="P21">
-        <v>-3.6814566968321554E-3</v>
+        <v>-5.1646375057862127E-4</v>
       </c>
       <c r="Q21">
-        <v>2.6678074114173966E-4</v>
+        <v>1.1248659172277342E-4</v>
       </c>
       <c r="R21">
-        <v>-4.4825449281234954E-3</v>
+        <v>-1.7308066114394785E-4</v>
       </c>
       <c r="S21">
-        <v>-1.6782429909114138E-3</v>
+        <v>-6.9804464697652735E-4</v>
       </c>
       <c r="T21">
-        <v>-2.2329137880258139E-3</v>
+        <v>-8.3394758209854984E-4</v>
       </c>
       <c r="U21">
-        <v>-9.0186218501598779E-4</v>
+        <v>-2.5324972738849865E-4</v>
       </c>
       <c r="V21">
-        <v>8.4634546467901847E-2</v>
+        <v>4.9181083377989987E-2</v>
       </c>
     </row>
   </sheetData>
@@ -2554,17 +2561,17 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{096FB178-A353-4186-9E40-A0F2A803816D}">
   <dimension ref="A1:L11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="20.42578125" style="4" customWidth="1"/>
-    <col min="2" max="16384" width="9.140625" style="4"/>
+    <col min="1" max="1" width="20.3984375" style="4" customWidth="1"/>
+    <col min="2" max="16384" width="9.1328125" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="7" t="s">
         <v>35</v>
       </c>
       <c r="C1" t="s">
@@ -2598,384 +2605,384 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A2" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>-2.929298938517964E-2</v>
+      <c r="B2" s="7">
+        <v>-5.051551827747696E-2</v>
       </c>
       <c r="C2">
-        <v>5.6923083046035283E-3</v>
+        <v>4.8620303535781848E-3</v>
       </c>
       <c r="D2">
-        <v>1.4545212011666687E-3</v>
+        <v>1.3441019401767649E-3</v>
       </c>
       <c r="E2">
-        <v>-3.2777424790135685E-5</v>
+        <v>-3.089622806568151E-5</v>
       </c>
       <c r="F2">
-        <v>-5.0107123081876478E-5</v>
+        <v>2.9699928231728462E-4</v>
       </c>
       <c r="G2">
-        <v>6.7073118763428955E-6</v>
+        <v>-8.5172430586373201E-5</v>
       </c>
       <c r="H2">
-        <v>2.5414543965075163E-3</v>
+        <v>7.6474606950385077E-4</v>
       </c>
       <c r="I2">
-        <v>-8.3587447263442141E-4</v>
+        <v>-6.030802445391992E-4</v>
       </c>
       <c r="J2">
-        <v>3.1246896645667661E-4</v>
+        <v>-8.5239545636379803E-5</v>
       </c>
       <c r="K2">
-        <v>3.6555378125204289E-5</v>
+        <v>5.464933408432654E-5</v>
       </c>
       <c r="L2">
-        <v>-1.9210002250647534E-2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+        <v>-1.8749599840915246E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A3" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>-1.3641849331215041</v>
+      <c r="B3" s="7">
+        <v>-1.2983719900740349</v>
       </c>
       <c r="C3">
-        <v>1.4545212011666687E-3</v>
+        <v>1.3441019401767649E-3</v>
       </c>
       <c r="D3">
-        <v>7.4533972601258713E-2</v>
+        <v>6.8588790485414552E-2</v>
       </c>
       <c r="E3">
-        <v>-1.713489586155699E-3</v>
+        <v>-1.5701007286897314E-3</v>
       </c>
       <c r="F3">
-        <v>1.2848452231662977E-3</v>
+        <v>1.1379776712124035E-3</v>
       </c>
       <c r="G3">
-        <v>-1.1339786394926124E-3</v>
+        <v>-6.4645805143555973E-4</v>
       </c>
       <c r="H3">
-        <v>-1.0229754256072976E-2</v>
+        <v>-8.6819839234821838E-3</v>
       </c>
       <c r="I3">
-        <v>8.4292332214421645E-4</v>
+        <v>-2.7516413141942097E-3</v>
       </c>
       <c r="J3">
-        <v>1.422940020884722E-3</v>
+        <v>-1.269332698069281E-3</v>
       </c>
       <c r="K3">
-        <v>4.5688887528499977E-4</v>
+        <v>-1.6376850248178698E-4</v>
       </c>
       <c r="L3">
-        <v>-0.81177729612622684</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+        <v>-0.73862124530475803</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A4" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="B4">
-        <v>3.0684363642761402E-2</v>
+      <c r="B4" s="7">
+        <v>2.9464976784623838E-2</v>
       </c>
       <c r="C4">
-        <v>-3.2777424790135685E-5</v>
+        <v>-3.089622806568151E-5</v>
       </c>
       <c r="D4">
-        <v>-1.713489586155699E-3</v>
+        <v>-1.5701007286897314E-3</v>
       </c>
       <c r="E4">
-        <v>3.9544847537662854E-5</v>
+        <v>3.6096808668567142E-5</v>
       </c>
       <c r="F4">
-        <v>-3.1060290543154061E-5</v>
+        <v>-2.6838090206401325E-5</v>
       </c>
       <c r="G4">
-        <v>2.4671542769201527E-5</v>
+        <v>1.4148759308860647E-5</v>
       </c>
       <c r="H4">
-        <v>2.0747619757660596E-4</v>
+        <v>1.808681688464861E-4</v>
       </c>
       <c r="I4">
-        <v>-1.8809937124143533E-5</v>
+        <v>6.2080751901998511E-5</v>
       </c>
       <c r="J4">
-        <v>-3.1529976936662402E-5</v>
+        <v>3.0423781452857193E-5</v>
       </c>
       <c r="K4">
-        <v>-1.013668117045511E-5</v>
+        <v>4.246536280128662E-6</v>
       </c>
       <c r="L4">
-        <v>1.8601164776237356E-2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+        <v>1.6842384590168541E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A5" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="B5">
-        <v>3.3803221382980364E-2</v>
+      <c r="B5" s="7">
+        <v>9.2798509400978169E-2</v>
       </c>
       <c r="C5">
-        <v>-5.0107123081876478E-5</v>
+        <v>2.9699928231728462E-4</v>
       </c>
       <c r="D5">
-        <v>1.2848452231662977E-3</v>
+        <v>1.1379776712124035E-3</v>
       </c>
       <c r="E5">
-        <v>-3.1060290543154061E-5</v>
+        <v>-2.6838090206401325E-5</v>
       </c>
       <c r="F5">
-        <v>3.8067004608979653E-3</v>
+        <v>3.1959048068916241E-3</v>
       </c>
       <c r="G5">
-        <v>-5.0174058537222864E-5</v>
+        <v>-5.3157395205786573E-5</v>
       </c>
       <c r="H5">
-        <v>-6.1751018283020404E-4</v>
+        <v>-6.93291338831864E-4</v>
       </c>
       <c r="I5">
-        <v>2.3829246096415658E-4</v>
+        <v>1.448669267637274E-4</v>
       </c>
       <c r="J5">
-        <v>4.6143348289821168E-4</v>
+        <v>6.3602950349776061E-4</v>
       </c>
       <c r="K5">
-        <v>2.7204539532226478E-5</v>
+        <v>-5.3825925335343472E-5</v>
       </c>
       <c r="L5">
-        <v>-3.1212288068700994E-2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+        <v>-2.6180826698662896E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A6" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="B6">
-        <v>2.1855505572578472E-2</v>
+      <c r="B6" s="7">
+        <v>3.0795246185701276E-2</v>
       </c>
       <c r="C6">
-        <v>6.7073118763428955E-6</v>
+        <v>-8.5172430586373201E-5</v>
       </c>
       <c r="D6">
-        <v>-1.1339786394926124E-3</v>
+        <v>-6.4645805143555973E-4</v>
       </c>
       <c r="E6">
-        <v>2.4671542769201527E-5</v>
+        <v>1.4148759308860647E-5</v>
       </c>
       <c r="F6">
-        <v>-5.0174058537222864E-5</v>
+        <v>-5.3157395205786573E-5</v>
       </c>
       <c r="G6">
-        <v>5.1888239069602536E-4</v>
+        <v>4.6257122910800454E-4</v>
       </c>
       <c r="H6">
-        <v>-4.5030181911319064E-4</v>
+        <v>-3.7518587896146621E-4</v>
       </c>
       <c r="I6">
-        <v>2.5135979195898921E-4</v>
+        <v>1.0262447814689495E-4</v>
       </c>
       <c r="J6">
-        <v>-1.1713908701162798E-4</v>
+        <v>4.5636050914181882E-5</v>
       </c>
       <c r="K6">
-        <v>-4.3200567694750549E-5</v>
+        <v>1.0442197265863793E-5</v>
       </c>
       <c r="L6">
-        <v>1.3331256623023688E-2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+        <v>7.1320714324916747E-3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A7" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B7">
-        <v>3.9109746918213784</v>
+      <c r="B7" s="7">
+        <v>2.3801091773278706</v>
       </c>
       <c r="C7">
-        <v>2.5414543965075163E-3</v>
+        <v>7.6474606950385077E-4</v>
       </c>
       <c r="D7">
-        <v>-1.0229754256072976E-2</v>
+        <v>-8.6819839234821838E-3</v>
       </c>
       <c r="E7">
-        <v>2.0747619757660596E-4</v>
+        <v>1.808681688464861E-4</v>
       </c>
       <c r="F7">
-        <v>-6.1751018283020404E-4</v>
+        <v>-6.93291338831864E-4</v>
       </c>
       <c r="G7">
-        <v>-4.5030181911319064E-4</v>
+        <v>-3.7518587896146621E-4</v>
       </c>
       <c r="H7">
-        <v>8.2411801474828128E-2</v>
+        <v>1.2855860237723546E-2</v>
       </c>
       <c r="I7">
-        <v>-3.0931410231148761E-3</v>
+        <v>6.6914605864439112E-4</v>
       </c>
       <c r="J7">
-        <v>3.0759512614375595E-3</v>
+        <v>1.3087951686447039E-3</v>
       </c>
       <c r="K7">
-        <v>8.4015487434231997E-4</v>
+        <v>-9.4902945073560216E-5</v>
       </c>
       <c r="L7">
-        <v>0.10200537721714986</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+        <v>0.10123286940337084</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A8" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="B8">
-        <v>-0.12773509156487015</v>
+      <c r="B8" s="7">
+        <v>-6.2524673324793209E-2</v>
       </c>
       <c r="C8">
-        <v>-8.3587447263442141E-4</v>
+        <v>-6.030802445391992E-4</v>
       </c>
       <c r="D8">
-        <v>8.4292332214421645E-4</v>
+        <v>-2.7516413141942097E-3</v>
       </c>
       <c r="E8">
-        <v>-1.8809937124143533E-5</v>
+        <v>6.2080751901998511E-5</v>
       </c>
       <c r="F8">
-        <v>2.3829246096415658E-4</v>
+        <v>1.448669267637274E-4</v>
       </c>
       <c r="G8">
-        <v>2.5135979195898921E-4</v>
+        <v>1.0262447814689495E-4</v>
       </c>
       <c r="H8">
-        <v>-3.0931410231148761E-3</v>
+        <v>6.6914605864439112E-4</v>
       </c>
       <c r="I8">
-        <v>1.3729614217520971E-2</v>
+        <v>1.0202791751467957E-2</v>
       </c>
       <c r="J8">
-        <v>7.7165904443240408E-3</v>
+        <v>5.2310493547185876E-3</v>
       </c>
       <c r="K8">
-        <v>4.8665864952462338E-5</v>
+        <v>3.3399538667438274E-5</v>
       </c>
       <c r="L8">
-        <v>-1.8463900466412421E-2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+        <v>2.3526824290151266E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A9" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="B9">
-        <v>-0.21335051578297848</v>
+      <c r="B9" s="7">
+        <v>-0.19973254849945279</v>
       </c>
       <c r="C9">
-        <v>3.1246896645667661E-4</v>
+        <v>-8.5239545636379803E-5</v>
       </c>
       <c r="D9">
-        <v>1.422940020884722E-3</v>
+        <v>-1.269332698069281E-3</v>
       </c>
       <c r="E9">
-        <v>-3.1529976936662402E-5</v>
+        <v>3.0423781452857193E-5</v>
       </c>
       <c r="F9">
-        <v>4.6143348289821168E-4</v>
+        <v>6.3602950349776061E-4</v>
       </c>
       <c r="G9">
-        <v>-1.1713908701162798E-4</v>
+        <v>4.5636050914181882E-5</v>
       </c>
       <c r="H9">
-        <v>3.0759512614375595E-3</v>
+        <v>1.3087951686447039E-3</v>
       </c>
       <c r="I9">
-        <v>7.7165904443240408E-3</v>
+        <v>5.2310493547185876E-3</v>
       </c>
       <c r="J9">
-        <v>9.9180575410929613E-3</v>
+        <v>7.326339415196996E-3</v>
       </c>
       <c r="K9">
-        <v>8.3388878006225879E-5</v>
+        <v>1.5481591509270949E-5</v>
       </c>
       <c r="L9">
-        <v>-2.7373911771300025E-2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+        <v>4.2858893011360356E-3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A10" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="B10">
-        <v>-8.0370529607905108E-3</v>
+      <c r="B10" s="7">
+        <v>-1.3919841860523082E-2</v>
       </c>
       <c r="C10">
-        <v>3.6555378125204289E-5</v>
+        <v>5.464933408432654E-5</v>
       </c>
       <c r="D10">
-        <v>4.5688887528499977E-4</v>
+        <v>-1.6376850248178698E-4</v>
       </c>
       <c r="E10">
-        <v>-1.013668117045511E-5</v>
+        <v>4.246536280128662E-6</v>
       </c>
       <c r="F10">
-        <v>2.7204539532226478E-5</v>
+        <v>-5.3825925335343472E-5</v>
       </c>
       <c r="G10">
-        <v>-4.3200567694750549E-5</v>
+        <v>1.0442197265863793E-5</v>
       </c>
       <c r="H10">
-        <v>8.4015487434231997E-4</v>
+        <v>-9.4902945073560216E-5</v>
       </c>
       <c r="I10">
-        <v>4.8665864952462338E-5</v>
+        <v>3.3399538667438274E-5</v>
       </c>
       <c r="J10">
-        <v>8.3388878006225879E-5</v>
+        <v>1.5481591509270949E-5</v>
       </c>
       <c r="K10">
-        <v>2.0673572907017917E-4</v>
+        <v>1.3163671687633236E-4</v>
       </c>
       <c r="L10">
-        <v>-8.3352062084125836E-3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+        <v>-1.1656308250264716E-4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A11" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B11">
-        <v>12.267583145184187</v>
+      <c r="B11" s="7">
+        <v>11.616030505838898</v>
       </c>
       <c r="C11">
-        <v>-1.9210002250647534E-2</v>
+        <v>-1.8749599840915246E-2</v>
       </c>
       <c r="D11">
-        <v>-0.81177729612622684</v>
+        <v>-0.73862124530475803</v>
       </c>
       <c r="E11">
-        <v>1.8601164776237356E-2</v>
+        <v>1.6842384590168541E-2</v>
       </c>
       <c r="F11">
-        <v>-3.1212288068700994E-2</v>
+        <v>-2.6180826698662896E-2</v>
       </c>
       <c r="G11">
-        <v>1.3331256623023688E-2</v>
+        <v>7.1320714324916747E-3</v>
       </c>
       <c r="H11">
-        <v>0.10200537721714986</v>
+        <v>0.10123286940337084</v>
       </c>
       <c r="I11">
-        <v>-1.8463900466412421E-2</v>
+        <v>2.3526824290151266E-2</v>
       </c>
       <c r="J11">
-        <v>-2.7373911771300025E-2</v>
+        <v>4.2858893011360356E-3</v>
       </c>
       <c r="K11">
-        <v>-8.3352062084125836E-3</v>
+        <v>-1.1656308250264716E-4</v>
       </c>
       <c r="L11">
-        <v>9.0078508998462326</v>
+        <v>8.0810162433882837</v>
       </c>
     </row>
   </sheetData>
@@ -2986,17 +2993,17 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6625456-5B9C-404B-BC52-0A6D9CC89C32}">
   <dimension ref="A1:V21"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="30.7109375" style="4" customWidth="1"/>
-    <col min="2" max="16384" width="9.140625" style="4"/>
+    <col min="1" max="1" width="30.73046875" style="4" customWidth="1"/>
+    <col min="2" max="16384" width="9.1328125" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A1" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="7" t="s">
         <v>35</v>
       </c>
       <c r="C1" t="s">
@@ -3015,10 +3022,10 @@
         <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="I1" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="J1" t="s">
         <v>33</v>
@@ -3060,1364 +3067,1364 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A2" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>-0.10855908036449249</v>
+      <c r="B2" s="7">
+        <v>-9.5778030584876342E-2</v>
       </c>
       <c r="C2">
-        <v>1.2606449776186581E-3</v>
+        <v>1.0933656597565229E-3</v>
       </c>
       <c r="D2">
-        <v>2.2880059369569734E-5</v>
+        <v>2.6673849876415723E-5</v>
       </c>
       <c r="E2">
-        <v>-2.4055291562325241E-7</v>
+        <v>-2.6406242664304455E-7</v>
       </c>
       <c r="F2">
-        <v>-2.1038862152517463E-4</v>
+        <v>-1.3792421918539779E-4</v>
       </c>
       <c r="G2">
-        <v>-5.7103453234259285E-5</v>
+        <v>-2.2405619053391854E-5</v>
       </c>
       <c r="H2">
-        <v>1.6139352305338372E-4</v>
+        <v>1.5234651284352598E-4</v>
       </c>
       <c r="I2">
-        <v>-6.1993391980819752E-5</v>
+        <v>-5.5016902228932992E-5</v>
       </c>
       <c r="J2">
-        <v>2.4873240479934811E-5</v>
+        <v>5.9775860840883849E-5</v>
       </c>
       <c r="K2">
-        <v>2.7358246041236706E-5</v>
+        <v>1.1224461825848475E-4</v>
       </c>
       <c r="L2">
-        <v>1.7117461178215026E-4</v>
+        <v>2.1627398624758678E-4</v>
       </c>
       <c r="M2">
-        <v>4.4624120421127858E-4</v>
+        <v>5.2293721240511412E-4</v>
       </c>
       <c r="N2">
-        <v>1.3610803758431651E-5</v>
+        <v>5.2320754619103479E-6</v>
       </c>
       <c r="O2">
-        <v>-2.117381428911456E-5</v>
+        <v>-2.1335184281993645E-5</v>
       </c>
       <c r="P2">
-        <v>-2.200886716486228E-4</v>
+        <v>8.1238504430835559E-5</v>
       </c>
       <c r="Q2">
-        <v>-2.798043515445642E-5</v>
+        <v>-2.5528981076261636E-5</v>
       </c>
       <c r="R2">
-        <v>7.2642527386082849E-4</v>
+        <v>-1.1088999350553725E-5</v>
       </c>
       <c r="S2">
-        <v>-1.1209844410064573E-4</v>
+        <v>-1.0906912166162158E-4</v>
       </c>
       <c r="T2">
-        <v>-1.1311760860704164E-4</v>
+        <v>-8.535940952759751E-5</v>
       </c>
       <c r="U2">
-        <v>2.1006550147106387E-5</v>
+        <v>5.4471686966269434E-6</v>
       </c>
       <c r="V2">
-        <v>-1.0846802946997023E-3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+        <v>-9.5153740686186518E-4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A3" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>4.1827988035928916E-3</v>
+      <c r="B3" s="7">
+        <v>6.1101552479797261E-3</v>
       </c>
       <c r="C3">
-        <v>2.2880059369569734E-5</v>
+        <v>2.6673849876415723E-5</v>
       </c>
       <c r="D3">
-        <v>5.7840331439279303E-5</v>
+        <v>4.70908756531213E-5</v>
       </c>
       <c r="E3">
-        <v>-5.6040625045909565E-7</v>
+        <v>-4.5693590688621895E-7</v>
       </c>
       <c r="F3">
-        <v>1.111603796596E-5</v>
+        <v>1.2985612666595088E-5</v>
       </c>
       <c r="G3">
-        <v>9.8296534187665804E-5</v>
+        <v>7.2752820475279362E-5</v>
       </c>
       <c r="H3">
-        <v>2.6103773944813975E-4</v>
+        <v>1.8691572800771998E-4</v>
       </c>
       <c r="I3">
-        <v>3.8581135254598417E-8</v>
+        <v>-2.858605441458746E-5</v>
       </c>
       <c r="J3">
-        <v>6.8121609888719314E-5</v>
+        <v>5.0280935373854421E-5</v>
       </c>
       <c r="K3">
-        <v>-6.3583486827656398E-6</v>
+        <v>2.1461872247115752E-5</v>
       </c>
       <c r="L3">
-        <v>8.0119020981381586E-5</v>
+        <v>6.3532503585001337E-5</v>
       </c>
       <c r="M3">
-        <v>-6.3186916004863121E-5</v>
+        <v>5.8969599836278816E-6</v>
       </c>
       <c r="N3">
-        <v>3.901566475309671E-5</v>
+        <v>2.8248912255336448E-5</v>
       </c>
       <c r="O3">
-        <v>6.7929980591587686E-7</v>
+        <v>-2.9482055088629445E-6</v>
       </c>
       <c r="P3">
-        <v>-9.5575235176110877E-5</v>
+        <v>-1.5229054684824227E-6</v>
       </c>
       <c r="Q3">
-        <v>-1.5812824943026179E-5</v>
+        <v>-1.0225854059047679E-5</v>
       </c>
       <c r="R3">
-        <v>3.085625208279659E-5</v>
+        <v>2.8458091006104214E-6</v>
       </c>
       <c r="S3">
-        <v>-5.7718389333629577E-5</v>
+        <v>-5.7452679569498484E-5</v>
       </c>
       <c r="T3">
-        <v>-4.0033974316033318E-5</v>
+        <v>-4.2557971765152646E-5</v>
       </c>
       <c r="U3">
-        <v>6.0928987697527089E-6</v>
+        <v>3.3185740126174515E-6</v>
       </c>
       <c r="V3">
-        <v>-1.5554030069631526E-3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+        <v>-1.2210088503361056E-3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A4" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="B4">
-        <v>4.6199064961397277E-6</v>
+      <c r="B4" s="7">
+        <v>2.008650639520531E-5</v>
       </c>
       <c r="C4">
-        <v>-2.4055291562325241E-7</v>
+        <v>-2.6406242664304455E-7</v>
       </c>
       <c r="D4">
-        <v>-5.6040625045909565E-7</v>
+        <v>-4.5693590688621895E-7</v>
       </c>
       <c r="E4">
-        <v>5.7200882142952138E-9</v>
+        <v>4.7309510119624482E-9</v>
       </c>
       <c r="F4">
-        <v>-1.2945891635037839E-7</v>
+        <v>-8.3066197312966231E-8</v>
       </c>
       <c r="G4">
-        <v>-1.0601607887519155E-6</v>
+        <v>-7.5291627544278487E-7</v>
       </c>
       <c r="H4">
-        <v>-2.1641121170444082E-6</v>
+        <v>-1.3532054328172981E-6</v>
       </c>
       <c r="I4">
-        <v>6.6681496380008771E-8</v>
+        <v>3.4260528937842757E-7</v>
       </c>
       <c r="J4">
-        <v>-1.3648758795172116E-6</v>
+        <v>-1.1878915816948706E-6</v>
       </c>
       <c r="K4">
-        <v>2.9720026483357486E-7</v>
+        <v>7.9399028395428759E-8</v>
       </c>
       <c r="L4">
-        <v>-6.2651019301314032E-7</v>
+        <v>-5.2093636775746478E-7</v>
       </c>
       <c r="M4">
-        <v>7.0570519632137243E-7</v>
+        <v>2.0094747205043859E-7</v>
       </c>
       <c r="N4">
-        <v>-2.8177951628939422E-7</v>
+        <v>-1.7062668162688349E-7</v>
       </c>
       <c r="O4">
-        <v>-4.7753238929791065E-9</v>
+        <v>3.6921182304510027E-8</v>
       </c>
       <c r="P4">
-        <v>8.8811402505663132E-7</v>
+        <v>-9.8840091125623949E-8</v>
       </c>
       <c r="Q4">
-        <v>1.4628975131691226E-7</v>
+        <v>8.9203793226011035E-8</v>
       </c>
       <c r="R4">
-        <v>-3.7980330224432121E-7</v>
+        <v>-5.8055555997111252E-9</v>
       </c>
       <c r="S4">
-        <v>5.8798950203362081E-7</v>
+        <v>5.9242926978984871E-7</v>
       </c>
       <c r="T4">
-        <v>4.2258028806795031E-7</v>
+        <v>4.3681072621852343E-7</v>
       </c>
       <c r="U4">
-        <v>-7.9483588855033187E-8</v>
+        <v>-4.3000635655077416E-8</v>
       </c>
       <c r="V4">
-        <v>1.4316082145922566E-5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+        <v>1.0835919980753418E-5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A5" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B5">
-        <v>-8.9061018529301067E-2</v>
+      <c r="B5" s="7">
+        <v>-0.11562459622351498</v>
       </c>
       <c r="C5">
-        <v>-2.1038862152517463E-4</v>
+        <v>-1.3792421918539779E-4</v>
       </c>
       <c r="D5">
-        <v>1.111603796596E-5</v>
+        <v>1.2985612666595088E-5</v>
       </c>
       <c r="E5">
-        <v>-1.2945891635037839E-7</v>
+        <v>-8.3066197312966231E-8</v>
       </c>
       <c r="F5">
-        <v>2.3182994668029958E-3</v>
+        <v>1.7777035912931941E-3</v>
       </c>
       <c r="G5">
-        <v>1.9174025975604476E-3</v>
+        <v>1.5055977135622566E-3</v>
       </c>
       <c r="H5">
-        <v>2.376766377063655E-4</v>
+        <v>4.7117775691008526E-4</v>
       </c>
       <c r="I5">
-        <v>-8.8126690512463292E-5</v>
+        <v>-1.0159944445712628E-4</v>
       </c>
       <c r="J5">
-        <v>1.8501909294216939E-4</v>
+        <v>-3.502654265500726E-5</v>
       </c>
       <c r="K5">
-        <v>1.0186575258229274E-4</v>
+        <v>6.3382734733691704E-5</v>
       </c>
       <c r="L5">
-        <v>-5.9357667532088532E-5</v>
+        <v>-4.6147216474287474E-5</v>
       </c>
       <c r="M5">
-        <v>-2.1592872173164558E-4</v>
+        <v>-2.6342949411859622E-5</v>
       </c>
       <c r="N5">
-        <v>4.2321179937438474E-5</v>
+        <v>7.0607879865360078E-5</v>
       </c>
       <c r="O5">
-        <v>-3.2024139848052725E-7</v>
+        <v>1.2283905191700673E-5</v>
       </c>
       <c r="P5">
-        <v>3.011762261389524E-4</v>
+        <v>1.5555586453100379E-5</v>
       </c>
       <c r="Q5">
-        <v>-9.902959351280458E-7</v>
+        <v>2.4638401045160809E-6</v>
       </c>
       <c r="R5">
-        <v>3.2831034901675826E-6</v>
+        <v>5.1676723383607204E-5</v>
       </c>
       <c r="S5">
-        <v>-8.0899670399283341E-5</v>
+        <v>-1.980955543431492E-4</v>
       </c>
       <c r="T5">
-        <v>-2.4422270597085479E-4</v>
+        <v>-2.971516575533688E-4</v>
       </c>
       <c r="U5">
-        <v>3.238205747657587E-5</v>
+        <v>1.5103122809794487E-5</v>
       </c>
       <c r="V5">
-        <v>-2.5080921180868796E-3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+        <v>-2.0702554684727168E-3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A6" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B6">
-        <v>-0.2187553692338664</v>
+      <c r="B6" s="7">
+        <v>-0.312049720588844</v>
       </c>
       <c r="C6">
-        <v>-5.7103453234259285E-5</v>
+        <v>-2.2405619053391854E-5</v>
       </c>
       <c r="D6">
-        <v>9.8296534187665804E-5</v>
+        <v>7.2752820475279362E-5</v>
       </c>
       <c r="E6">
-        <v>-1.0601607887519155E-6</v>
+        <v>-7.5291627544278487E-7</v>
       </c>
       <c r="F6">
-        <v>1.9174025975604476E-3</v>
+        <v>1.5055977135622566E-3</v>
       </c>
       <c r="G6">
-        <v>3.4432930374479181E-3</v>
+        <v>2.8436214370796487E-3</v>
       </c>
       <c r="H6">
-        <v>1.8170914897457221E-4</v>
+        <v>5.225321427310926E-4</v>
       </c>
       <c r="I6">
-        <v>-1.2818825666439915E-4</v>
+        <v>-2.0090885391268944E-4</v>
       </c>
       <c r="J6">
-        <v>5.5977319728869488E-4</v>
+        <v>3.3684500532875112E-4</v>
       </c>
       <c r="K6">
-        <v>-2.2488404129822163E-4</v>
+        <v>-1.1589980095340086E-4</v>
       </c>
       <c r="L6">
-        <v>-1.7042203633770557E-4</v>
+        <v>-1.0960558267432467E-4</v>
       </c>
       <c r="M6">
-        <v>-9.7739559726481577E-4</v>
+        <v>-3.8985568119236091E-4</v>
       </c>
       <c r="N6">
-        <v>1.9855146220120661E-4</v>
+        <v>2.0022174474063469E-4</v>
       </c>
       <c r="O6">
-        <v>2.7990404308771143E-5</v>
+        <v>2.5240830257051365E-5</v>
       </c>
       <c r="P6">
-        <v>4.9278643322279991E-4</v>
+        <v>3.9197100660613021E-4</v>
       </c>
       <c r="Q6">
-        <v>1.8950160294582078E-5</v>
+        <v>2.0283775716065217E-5</v>
       </c>
       <c r="R6">
-        <v>-3.3412393712240786E-4</v>
+        <v>-1.0715855676419594E-5</v>
       </c>
       <c r="S6">
-        <v>-4.3120415413403033E-4</v>
+        <v>-5.5206689033472645E-4</v>
       </c>
       <c r="T6">
-        <v>-4.7768750130597944E-4</v>
+        <v>-6.1494216492038447E-4</v>
       </c>
       <c r="U6">
-        <v>4.9268623531035117E-5</v>
+        <v>2.3665857040760163E-5</v>
       </c>
       <c r="V6">
-        <v>-5.1612812539170768E-3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+        <v>-3.8522072573399209E-3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A7" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="B7">
-        <v>-0.10154498861753357</v>
+      <c r="B7" s="7">
+        <v>0.14078681528491385</v>
       </c>
       <c r="C7">
-        <v>1.6139352305338372E-4</v>
+        <v>1.5234651284352598E-4</v>
       </c>
       <c r="D7">
-        <v>2.6103773944813975E-4</v>
+        <v>1.8691572800771998E-4</v>
       </c>
       <c r="E7">
-        <v>-2.1641121170444082E-6</v>
+        <v>-1.3532054328172981E-6</v>
       </c>
       <c r="F7">
-        <v>2.376766377063655E-4</v>
+        <v>4.7117775691008526E-4</v>
       </c>
       <c r="G7">
-        <v>1.8170914897457221E-4</v>
+        <v>5.225321427310926E-4</v>
       </c>
       <c r="H7">
-        <v>2.3817431072502376E-2</v>
+        <v>1.7930500616712246E-2</v>
       </c>
       <c r="I7">
-        <v>1.9092821056882702E-3</v>
+        <v>1.6005061432805999E-3</v>
       </c>
       <c r="J7">
-        <v>1.8396347167119308E-3</v>
+        <v>1.5074241870246191E-3</v>
       </c>
       <c r="K7">
-        <v>7.0232565571555321E-4</v>
+        <v>1.1024911982147755E-3</v>
       </c>
       <c r="L7">
-        <v>3.6553245122088792E-5</v>
+        <v>-1.014815884051234E-4</v>
       </c>
       <c r="M7">
-        <v>-5.0158784781796769E-4</v>
+        <v>1.165423391595788E-3</v>
       </c>
       <c r="N7">
-        <v>-3.8994018877465834E-5</v>
+        <v>1.0815626755262175E-5</v>
       </c>
       <c r="O7">
-        <v>8.8829449987423394E-5</v>
+        <v>2.0049315963047761E-4</v>
       </c>
       <c r="P7">
-        <v>-3.6563780524553648E-3</v>
+        <v>-9.4512603460843257E-4</v>
       </c>
       <c r="Q7">
-        <v>1.8915017476894155E-4</v>
+        <v>5.5521774644662502E-5</v>
       </c>
       <c r="R7">
-        <v>4.1549422700806818E-3</v>
+        <v>-9.612946707088536E-5</v>
       </c>
       <c r="S7">
-        <v>-2.5316546362665147E-4</v>
+        <v>-5.455034895268402E-4</v>
       </c>
       <c r="T7">
-        <v>-6.0800792939509456E-4</v>
+        <v>-5.1445012677452107E-4</v>
       </c>
       <c r="U7">
-        <v>4.8570386811534793E-6</v>
+        <v>1.637552771625644E-6</v>
       </c>
       <c r="V7">
-        <v>-9.5479299439533722E-3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+        <v>-8.0809729364833133E-3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A8" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="B8">
-        <v>2.9205414940590761E-2</v>
+      <c r="B8" s="7">
+        <v>0.12984391365926448</v>
       </c>
       <c r="C8">
-        <v>-6.1993391980819752E-5</v>
+        <v>-5.5016902228932992E-5</v>
       </c>
       <c r="D8">
-        <v>3.8581135254598417E-8</v>
+        <v>-2.858605441458746E-5</v>
       </c>
       <c r="E8">
-        <v>6.6681496380008771E-8</v>
+        <v>3.4260528937842757E-7</v>
       </c>
       <c r="F8">
-        <v>-8.8126690512463292E-5</v>
+        <v>-1.0159944445712628E-4</v>
       </c>
       <c r="G8">
-        <v>-1.2818825666439915E-4</v>
+        <v>-2.0090885391268944E-4</v>
       </c>
       <c r="H8">
-        <v>1.9092821056882702E-3</v>
+        <v>1.6005061432805999E-3</v>
       </c>
       <c r="I8">
-        <v>3.2525079233730464E-3</v>
+        <v>2.5609786179915817E-3</v>
       </c>
       <c r="J8">
-        <v>2.0077713906486556E-3</v>
+        <v>1.853615263371214E-3</v>
       </c>
       <c r="K8">
-        <v>-2.5246692221499124E-5</v>
+        <v>5.2842161845442423E-5</v>
       </c>
       <c r="L8">
-        <v>-1.2963860284042196E-5</v>
+        <v>-2.6225853438826988E-5</v>
       </c>
       <c r="M8">
-        <v>-4.2686360737312465E-4</v>
+        <v>2.2185865365416499E-4</v>
       </c>
       <c r="N8">
-        <v>1.0963604405887954E-4</v>
+        <v>8.1694055323807758E-5</v>
       </c>
       <c r="O8">
-        <v>1.8662145141860068E-4</v>
+        <v>1.9982921265771216E-4</v>
       </c>
       <c r="P8">
-        <v>9.8016225582774931E-4</v>
+        <v>-2.2530418248565328E-6</v>
       </c>
       <c r="Q8">
-        <v>1.1200181344711013E-4</v>
+        <v>7.2800521387807177E-5</v>
       </c>
       <c r="R8">
-        <v>-1.0091291944106717E-3</v>
+        <v>-9.0850431978946062E-5</v>
       </c>
       <c r="S8">
-        <v>1.7186741626007808E-4</v>
+        <v>1.4775817517303927E-4</v>
       </c>
       <c r="T8">
-        <v>1.7237269746029921E-4</v>
+        <v>1.4939015894451088E-4</v>
       </c>
       <c r="U8">
-        <v>-2.448932239456546E-5</v>
+        <v>-2.9782859362962797E-5</v>
       </c>
       <c r="V8">
-        <v>-2.5875493120586499E-3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+        <v>-1.5190247740773191E-3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A9" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="B9">
-        <v>6.2970126368330853E-2</v>
+      <c r="B9" s="7">
+        <v>5.9583423494434233E-2</v>
       </c>
       <c r="C9">
-        <v>2.4873240479934811E-5</v>
+        <v>5.9775860840883849E-5</v>
       </c>
       <c r="D9">
-        <v>6.8121609888719314E-5</v>
+        <v>5.0280935373854421E-5</v>
       </c>
       <c r="E9">
-        <v>-1.3648758795172116E-6</v>
+        <v>-1.1878915816948706E-6</v>
       </c>
       <c r="F9">
-        <v>1.8501909294216939E-4</v>
+        <v>-3.502654265500726E-5</v>
       </c>
       <c r="G9">
-        <v>5.5977319728869488E-4</v>
+        <v>3.3684500532875112E-4</v>
       </c>
       <c r="H9">
-        <v>1.8396347167119308E-3</v>
+        <v>1.5074241870246191E-3</v>
       </c>
       <c r="I9">
-        <v>2.0077713906486556E-3</v>
+        <v>1.853615263371214E-3</v>
       </c>
       <c r="J9">
-        <v>5.6731799829462777E-3</v>
+        <v>5.4145948825377026E-3</v>
       </c>
       <c r="K9">
-        <v>-2.0415850051141559E-4</v>
+        <v>-1.6476974281446699E-4</v>
       </c>
       <c r="L9">
-        <v>-2.9818584464802499E-4</v>
+        <v>-2.399467156763263E-4</v>
       </c>
       <c r="M9">
-        <v>-3.9873789044445659E-4</v>
+        <v>-7.457814872403835E-5</v>
       </c>
       <c r="N9">
-        <v>1.3126328178336266E-4</v>
+        <v>-1.9968893494167904E-5</v>
       </c>
       <c r="O9">
-        <v>1.977449980222623E-4</v>
+        <v>2.3207915018946817E-4</v>
       </c>
       <c r="P9">
-        <v>1.0784930123547594E-3</v>
+        <v>4.9992269232495548E-4</v>
       </c>
       <c r="Q9">
-        <v>2.0065929194573146E-4</v>
+        <v>1.3752434816368829E-4</v>
       </c>
       <c r="R9">
-        <v>-9.0736690478952081E-4</v>
+        <v>-1.5933881736847734E-4</v>
       </c>
       <c r="S9">
-        <v>-2.7720396047130162E-4</v>
+        <v>-1.6192257533607663E-4</v>
       </c>
       <c r="T9">
-        <v>-1.7574111899570227E-4</v>
+        <v>1.5419757416658929E-5</v>
       </c>
       <c r="U9">
-        <v>1.4333161147453075E-5</v>
+        <v>-1.9757148350270674E-5</v>
       </c>
       <c r="V9">
-        <v>-3.8128303692830301E-3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+        <v>-2.1966311904637117E-3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A10" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="B10">
-        <v>0.28584230365221258</v>
+      <c r="B10" s="7">
+        <v>0.25513923752639073</v>
       </c>
       <c r="C10">
-        <v>2.7358246041236706E-5</v>
+        <v>1.1224461825848475E-4</v>
       </c>
       <c r="D10">
-        <v>-6.3583486827656398E-6</v>
+        <v>2.1461872247115752E-5</v>
       </c>
       <c r="E10">
-        <v>2.9720026483357486E-7</v>
+        <v>7.9399028395428759E-8</v>
       </c>
       <c r="F10">
-        <v>1.0186575258229274E-4</v>
+        <v>6.3382734733691704E-5</v>
       </c>
       <c r="G10">
-        <v>-2.2488404129822163E-4</v>
+        <v>-1.1589980095340086E-4</v>
       </c>
       <c r="H10">
-        <v>7.0232565571555321E-4</v>
+        <v>1.1024911982147755E-3</v>
       </c>
       <c r="I10">
-        <v>-2.5246692221499124E-5</v>
+        <v>5.2842161845442423E-5</v>
       </c>
       <c r="J10">
-        <v>-2.0415850051141559E-4</v>
+        <v>-1.6476974281446699E-4</v>
       </c>
       <c r="K10">
-        <v>2.1907014531663315E-3</v>
+        <v>2.1516590699826353E-3</v>
       </c>
       <c r="L10">
-        <v>1.2300249055152406E-3</v>
+        <v>1.0225666929404597E-3</v>
       </c>
       <c r="M10">
-        <v>1.2509142968329038E-3</v>
+        <v>1.5514187143775794E-3</v>
       </c>
       <c r="N10">
-        <v>-9.2859834444393072E-5</v>
+        <v>-5.0245757397391967E-5</v>
       </c>
       <c r="O10">
-        <v>-2.1784753065706043E-5</v>
+        <v>5.3177644649590988E-6</v>
       </c>
       <c r="P10">
-        <v>4.5259111033694489E-4</v>
+        <v>-2.9713856881155771E-4</v>
       </c>
       <c r="Q10">
-        <v>1.4361560217792708E-5</v>
+        <v>-5.1439351831237518E-6</v>
       </c>
       <c r="R10">
-        <v>-1.6298329820565475E-3</v>
+        <v>1.0177823117025163E-4</v>
       </c>
       <c r="S10">
-        <v>1.6665939183647472E-4</v>
+        <v>1.9592154293996984E-4</v>
       </c>
       <c r="T10">
-        <v>1.8622711288142661E-4</v>
+        <v>1.4669200317054924E-4</v>
       </c>
       <c r="U10">
-        <v>-4.2445677561562877E-5</v>
+        <v>-2.8455401759327017E-6</v>
       </c>
       <c r="V10">
-        <v>-7.7611063389352556E-4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+        <v>-2.3814153979160239E-3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A11" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="B11">
-        <v>0.26015499392371</v>
+      <c r="B11" s="7">
+        <v>0.27833075411789471</v>
       </c>
       <c r="C11">
-        <v>1.7117461178215026E-4</v>
+        <v>2.1627398624758678E-4</v>
       </c>
       <c r="D11">
-        <v>8.0119020981381586E-5</v>
+        <v>6.3532503585001337E-5</v>
       </c>
       <c r="E11">
-        <v>-6.2651019301314032E-7</v>
+        <v>-5.2093636775746478E-7</v>
       </c>
       <c r="F11">
-        <v>-5.9357667532088532E-5</v>
+        <v>-4.6147216474287474E-5</v>
       </c>
       <c r="G11">
-        <v>-1.7042203633770557E-4</v>
+        <v>-1.0960558267432467E-4</v>
       </c>
       <c r="H11">
-        <v>3.6553245122088792E-5</v>
+        <v>-1.014815884051234E-4</v>
       </c>
       <c r="I11">
-        <v>-1.2963860284042196E-5</v>
+        <v>-2.6225853438826988E-5</v>
       </c>
       <c r="J11">
-        <v>-2.9818584464802499E-4</v>
+        <v>-2.399467156763263E-4</v>
       </c>
       <c r="K11">
-        <v>1.2300249055152406E-3</v>
+        <v>1.0225666929404597E-3</v>
       </c>
       <c r="L11">
-        <v>2.2004310281159819E-3</v>
+        <v>1.8012256597529869E-3</v>
       </c>
       <c r="M11">
-        <v>1.3029665460797908E-3</v>
+        <v>1.1780854888664963E-3</v>
       </c>
       <c r="N11">
-        <v>-2.4790902797421528E-5</v>
+        <v>2.2023427041863896E-5</v>
       </c>
       <c r="O11">
-        <v>2.3309459795421291E-6</v>
+        <v>-4.7292446692477407E-6</v>
       </c>
       <c r="P11">
-        <v>-5.3716751062301421E-4</v>
+        <v>-3.0735460203462888E-4</v>
       </c>
       <c r="Q11">
-        <v>1.9320313520788051E-5</v>
+        <v>1.1470437658787111E-5</v>
       </c>
       <c r="R11">
-        <v>-1.1486488092782585E-3</v>
+        <v>-1.1122281214913593E-4</v>
       </c>
       <c r="S11">
-        <v>1.8132577312509777E-4</v>
+        <v>5.1517420325050429E-5</v>
       </c>
       <c r="T11">
-        <v>1.9705502294746751E-4</v>
+        <v>5.8482901722426654E-5</v>
       </c>
       <c r="U11">
-        <v>-4.2271955458544452E-5</v>
+        <v>-1.6256958596493011E-5</v>
       </c>
       <c r="V11">
-        <v>-2.8170258826519033E-3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+        <v>-2.5707642124739136E-3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A12" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="B12">
-        <v>0.31640380801393647</v>
+      <c r="B12" s="7">
+        <v>0.50183521712027657</v>
       </c>
       <c r="C12">
-        <v>4.4624120421127858E-4</v>
+        <v>5.2293721240511412E-4</v>
       </c>
       <c r="D12">
-        <v>-6.3186916004863121E-5</v>
+        <v>5.8969599836278816E-6</v>
       </c>
       <c r="E12">
-        <v>7.0570519632137243E-7</v>
+        <v>2.0094747205043859E-7</v>
       </c>
       <c r="F12">
-        <v>-2.1592872173164558E-4</v>
+        <v>-2.6342949411859622E-5</v>
       </c>
       <c r="G12">
-        <v>-9.7739559726481577E-4</v>
+        <v>-3.8985568119236091E-4</v>
       </c>
       <c r="H12">
-        <v>-5.0158784781796769E-4</v>
+        <v>1.165423391595788E-3</v>
       </c>
       <c r="I12">
-        <v>-4.2686360737312465E-4</v>
+        <v>2.2185865365416499E-4</v>
       </c>
       <c r="J12">
-        <v>-3.9873789044445659E-4</v>
+        <v>-7.457814872403835E-5</v>
       </c>
       <c r="K12">
-        <v>1.2509142968329038E-3</v>
+        <v>1.5514187143775794E-3</v>
       </c>
       <c r="L12">
-        <v>1.3029665460797908E-3</v>
+        <v>1.1780854888664963E-3</v>
       </c>
       <c r="M12">
-        <v>8.9094254813412831E-3</v>
+        <v>4.7767529008998118E-3</v>
       </c>
       <c r="N12">
-        <v>3.6530442526367592E-5</v>
+        <v>-6.2416141598607683E-5</v>
       </c>
       <c r="O12">
-        <v>-8.4572145195030033E-5</v>
+        <v>-1.4081846645422365E-5</v>
       </c>
       <c r="P12">
-        <v>-3.8960681802594726E-3</v>
+        <v>-1.2557372657098379E-3</v>
       </c>
       <c r="Q12">
-        <v>5.6956803764659513E-5</v>
+        <v>-3.1374387528426824E-6</v>
       </c>
       <c r="R12">
-        <v>5.3261515412745437E-3</v>
+        <v>2.6529231983541063E-5</v>
       </c>
       <c r="S12">
-        <v>-6.3434959356604764E-4</v>
+        <v>1.6498778384609254E-4</v>
       </c>
       <c r="T12">
-        <v>-5.0014072772406172E-4</v>
+        <v>1.972424416282969E-4</v>
       </c>
       <c r="U12">
-        <v>1.268489349953425E-5</v>
+        <v>-2.5599927099522555E-5</v>
       </c>
       <c r="V12">
-        <v>4.6075597104513739E-4</v>
-      </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+        <v>-1.5189346188460278E-3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A13" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="B13">
-        <v>4.1874826053584578E-2</v>
+      <c r="B13" s="7">
+        <v>4.8504321017053396E-2</v>
       </c>
       <c r="C13">
-        <v>1.3610803758431651E-5</v>
+        <v>5.2320754619103479E-6</v>
       </c>
       <c r="D13">
-        <v>3.901566475309671E-5</v>
+        <v>2.8248912255336448E-5</v>
       </c>
       <c r="E13">
-        <v>-2.8177951628939422E-7</v>
+        <v>-1.7062668162688349E-7</v>
       </c>
       <c r="F13">
-        <v>4.2321179937438474E-5</v>
+        <v>7.0607879865360078E-5</v>
       </c>
       <c r="G13">
-        <v>1.9855146220120661E-4</v>
+        <v>2.0022174474063469E-4</v>
       </c>
       <c r="H13">
-        <v>-3.8994018877465834E-5</v>
+        <v>1.0815626755262175E-5</v>
       </c>
       <c r="I13">
-        <v>1.0963604405887954E-4</v>
+        <v>8.1694055323807758E-5</v>
       </c>
       <c r="J13">
-        <v>1.3126328178336266E-4</v>
+        <v>-1.9968893494167904E-5</v>
       </c>
       <c r="K13">
-        <v>-9.2859834444393072E-5</v>
+        <v>-5.0245757397391967E-5</v>
       </c>
       <c r="L13">
-        <v>-2.4790902797421528E-5</v>
+        <v>2.2023427041863896E-5</v>
       </c>
       <c r="M13">
-        <v>3.6530442526367592E-5</v>
+        <v>-6.2416141598607683E-5</v>
       </c>
       <c r="N13">
-        <v>4.6226746690636165E-4</v>
+        <v>3.847717792807357E-4</v>
       </c>
       <c r="O13">
-        <v>-1.3622851301689982E-5</v>
+        <v>-1.5784368950126042E-5</v>
       </c>
       <c r="P13">
-        <v>-2.3462867546855323E-4</v>
+        <v>-2.0127259804035699E-5</v>
       </c>
       <c r="Q13">
-        <v>-1.13553843385635E-5</v>
+        <v>-6.3313492362720942E-6</v>
       </c>
       <c r="R13">
-        <v>3.1065626536824677E-4</v>
+        <v>1.5807855293909108E-5</v>
       </c>
       <c r="S13">
-        <v>-1.7196646710945568E-4</v>
+        <v>-9.3282035375342499E-5</v>
       </c>
       <c r="T13">
-        <v>-1.375990364212926E-4</v>
+        <v>-8.5758712174573235E-5</v>
       </c>
       <c r="U13">
-        <v>1.0124442769630124E-5</v>
+        <v>-2.6163806895204787E-7</v>
       </c>
       <c r="V13">
-        <v>-2.8362085055283386E-3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+        <v>-2.2042654986475061E-3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A14" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="B14">
-        <v>1.8157206954486912E-2</v>
+      <c r="B14" s="7">
+        <v>1.2350662793498153E-2</v>
       </c>
       <c r="C14">
-        <v>-2.117381428911456E-5</v>
+        <v>-2.1335184281993645E-5</v>
       </c>
       <c r="D14">
-        <v>6.7929980591587686E-7</v>
+        <v>-2.9482055088629445E-6</v>
       </c>
       <c r="E14">
-        <v>-4.7753238929791065E-9</v>
+        <v>3.6921182304510027E-8</v>
       </c>
       <c r="F14">
-        <v>-3.2024139848052725E-7</v>
+        <v>1.2283905191700673E-5</v>
       </c>
       <c r="G14">
-        <v>2.7990404308771143E-5</v>
+        <v>2.5240830257051365E-5</v>
       </c>
       <c r="H14">
-        <v>8.8829449987423394E-5</v>
+        <v>2.0049315963047761E-4</v>
       </c>
       <c r="I14">
-        <v>1.8662145141860068E-4</v>
+        <v>1.9982921265771216E-4</v>
       </c>
       <c r="J14">
-        <v>1.977449980222623E-4</v>
+        <v>2.3207915018946817E-4</v>
       </c>
       <c r="K14">
-        <v>-2.1784753065706043E-5</v>
+        <v>5.3177644649590988E-6</v>
       </c>
       <c r="L14">
-        <v>2.3309459795421291E-6</v>
+        <v>-4.7292446692477407E-6</v>
       </c>
       <c r="M14">
-        <v>-8.4572145195030033E-5</v>
+        <v>-1.4081846645422365E-5</v>
       </c>
       <c r="N14">
-        <v>-1.3622851301689982E-5</v>
+        <v>-1.5784368950126042E-5</v>
       </c>
       <c r="O14">
-        <v>8.2265806641359474E-5</v>
+        <v>7.2082702326003268E-5</v>
       </c>
       <c r="P14">
-        <v>5.5106264977625098E-5</v>
+        <v>1.7757204700556621E-5</v>
       </c>
       <c r="Q14">
-        <v>-3.9039105312738114E-5</v>
+        <v>-2.3284930557373199E-5</v>
       </c>
       <c r="R14">
-        <v>-8.213476375598048E-5</v>
+        <v>-1.3785058401838085E-5</v>
       </c>
       <c r="S14">
-        <v>1.7757521411295216E-5</v>
+        <v>8.7345181349986797E-6</v>
       </c>
       <c r="T14">
-        <v>1.8423144210963913E-5</v>
+        <v>1.1372422166109199E-5</v>
       </c>
       <c r="U14">
-        <v>-4.7431895265010319E-6</v>
+        <v>-4.2457828382149717E-6</v>
       </c>
       <c r="V14">
-        <v>-1.7690766349992359E-4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+        <v>-1.6091015196135865E-4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A15" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B15">
-        <v>2.4456347677581118</v>
+      <c r="B15" s="7">
+        <v>1.5194782682779264</v>
       </c>
       <c r="C15">
-        <v>-2.200886716486228E-4</v>
+        <v>8.1238504430835559E-5</v>
       </c>
       <c r="D15">
-        <v>-9.5575235176110877E-5</v>
+        <v>-1.5229054684824227E-6</v>
       </c>
       <c r="E15">
-        <v>8.8811402505663132E-7</v>
+        <v>-9.8840091125623949E-8</v>
       </c>
       <c r="F15">
-        <v>3.011762261389524E-4</v>
+        <v>1.5555586453100379E-5</v>
       </c>
       <c r="G15">
-        <v>4.9278643322279991E-4</v>
+        <v>3.9197100660613021E-4</v>
       </c>
       <c r="H15">
-        <v>-3.6563780524553648E-3</v>
+        <v>-9.4512603460843257E-4</v>
       </c>
       <c r="I15">
-        <v>9.8016225582774931E-4</v>
+        <v>-2.2530418248565328E-6</v>
       </c>
       <c r="J15">
-        <v>1.0784930123547594E-3</v>
+        <v>4.9992269232495548E-4</v>
       </c>
       <c r="K15">
-        <v>4.5259111033694489E-4</v>
+        <v>-2.9713856881155771E-4</v>
       </c>
       <c r="L15">
-        <v>-5.3716751062301421E-4</v>
+        <v>-3.0735460203462888E-4</v>
       </c>
       <c r="M15">
-        <v>-3.8960681802594726E-3</v>
+        <v>-1.2557372657098379E-3</v>
       </c>
       <c r="N15">
-        <v>-2.3462867546855323E-4</v>
+        <v>-2.0127259804035699E-5</v>
       </c>
       <c r="O15">
-        <v>5.5106264977625098E-5</v>
+        <v>1.7757204700556621E-5</v>
       </c>
       <c r="P15">
-        <v>3.3285948359543779E-2</v>
+        <v>5.7310053918096003E-3</v>
       </c>
       <c r="Q15">
-        <v>5.1819914385675277E-5</v>
+        <v>-9.0039820778297778E-6</v>
       </c>
       <c r="R15">
-        <v>-2.3885888104803035E-2</v>
+        <v>-3.0826270981183469E-3</v>
       </c>
       <c r="S15">
-        <v>2.3119863536191637E-3</v>
+        <v>2.6269620253293485E-4</v>
       </c>
       <c r="T15">
-        <v>2.5979553500621935E-3</v>
+        <v>3.5867959151030101E-4</v>
       </c>
       <c r="U15">
-        <v>-9.7364192908278556E-5</v>
+        <v>-2.1875595937009358E-5</v>
       </c>
       <c r="V15">
-        <v>6.7447412652506646E-4</v>
-      </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+        <v>-1.5774693137675352E-6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A16" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B16">
-        <v>4.4576633525037646E-3</v>
+      <c r="B16" s="7">
+        <v>1.886703240580263E-2</v>
       </c>
       <c r="C16">
-        <v>-2.798043515445642E-5</v>
+        <v>-2.5528981076261636E-5</v>
       </c>
       <c r="D16">
-        <v>-1.5812824943026179E-5</v>
+        <v>-1.0225854059047679E-5</v>
       </c>
       <c r="E16">
-        <v>1.4628975131691226E-7</v>
+        <v>8.9203793226011035E-8</v>
       </c>
       <c r="F16">
-        <v>-9.902959351280458E-7</v>
+        <v>2.4638401045160809E-6</v>
       </c>
       <c r="G16">
-        <v>1.8950160294582078E-5</v>
+        <v>2.0283775716065217E-5</v>
       </c>
       <c r="H16">
-        <v>1.8915017476894155E-4</v>
+        <v>5.5521774644662502E-5</v>
       </c>
       <c r="I16">
-        <v>1.1200181344711013E-4</v>
+        <v>7.2800521387807177E-5</v>
       </c>
       <c r="J16">
-        <v>2.0065929194573146E-4</v>
+        <v>1.3752434816368829E-4</v>
       </c>
       <c r="K16">
-        <v>1.4361560217792708E-5</v>
+        <v>-5.1439351831237518E-6</v>
       </c>
       <c r="L16">
-        <v>1.9320313520788051E-5</v>
+        <v>1.1470437658787111E-5</v>
       </c>
       <c r="M16">
-        <v>5.6956803764659513E-5</v>
+        <v>-3.1374387528426824E-6</v>
       </c>
       <c r="N16">
-        <v>-1.13553843385635E-5</v>
+        <v>-6.3313492362720942E-6</v>
       </c>
       <c r="O16">
-        <v>-3.9039105312738114E-5</v>
+        <v>-2.3284930557373199E-5</v>
       </c>
       <c r="P16">
-        <v>5.1819914385675277E-5</v>
+        <v>-9.0039820778297778E-6</v>
       </c>
       <c r="Q16">
-        <v>8.7530792186131848E-5</v>
+        <v>5.5308526947329832E-5</v>
       </c>
       <c r="R16">
-        <v>-8.3840845934863022E-5</v>
+        <v>-1.3600433822306222E-5</v>
       </c>
       <c r="S16">
-        <v>-2.0011785946081351E-5</v>
+        <v>-1.7901257616996139E-5</v>
       </c>
       <c r="T16">
-        <v>-1.3226576168481793E-5</v>
+        <v>-8.6362985071152291E-6</v>
       </c>
       <c r="U16">
-        <v>-5.8626226481336741E-6</v>
+        <v>-1.7280521860250845E-6</v>
       </c>
       <c r="V16">
-        <v>2.5799308182290233E-4</v>
-      </c>
-    </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+        <v>1.5056789549973626E-4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A17" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="B17">
-        <v>1.2782713803483765</v>
+      <c r="B17" s="7">
+        <v>1.0332562831438197</v>
       </c>
       <c r="C17">
-        <v>7.2642527386082849E-4</v>
+        <v>-1.1088999350553725E-5</v>
       </c>
       <c r="D17">
-        <v>3.085625208279659E-5</v>
+        <v>2.8458091006104214E-6</v>
       </c>
       <c r="E17">
-        <v>-3.7980330224432121E-7</v>
+        <v>-5.8055555997111252E-9</v>
       </c>
       <c r="F17">
-        <v>3.2831034901675826E-6</v>
+        <v>5.1676723383607204E-5</v>
       </c>
       <c r="G17">
-        <v>-3.3412393712240786E-4</v>
+        <v>-1.0715855676419594E-5</v>
       </c>
       <c r="H17">
-        <v>4.1549422700806818E-3</v>
+        <v>-9.612946707088536E-5</v>
       </c>
       <c r="I17">
-        <v>-1.0091291944106717E-3</v>
+        <v>-9.0850431978946062E-5</v>
       </c>
       <c r="J17">
-        <v>-9.0736690478952081E-4</v>
+        <v>-1.5933881736847734E-4</v>
       </c>
       <c r="K17">
-        <v>-1.6298329820565475E-3</v>
+        <v>1.0177823117025163E-4</v>
       </c>
       <c r="L17">
-        <v>-1.1486488092782585E-3</v>
+        <v>-1.1122281214913593E-4</v>
       </c>
       <c r="M17">
-        <v>5.3261515412745437E-3</v>
+        <v>2.6529231983541063E-5</v>
       </c>
       <c r="N17">
-        <v>3.1065626536824677E-4</v>
+        <v>1.5807855293909108E-5</v>
       </c>
       <c r="O17">
-        <v>-8.213476375598048E-5</v>
+        <v>-1.3785058401838085E-5</v>
       </c>
       <c r="P17">
-        <v>-2.3885888104803035E-2</v>
+        <v>-3.0826270981183469E-3</v>
       </c>
       <c r="Q17">
-        <v>-8.3840845934863022E-5</v>
+        <v>-1.3600433822306222E-5</v>
       </c>
       <c r="R17">
-        <v>4.6890225509785936E-2</v>
+        <v>4.6964632349129672E-3</v>
       </c>
       <c r="S17">
-        <v>-3.1243475959661189E-3</v>
+        <v>1.0083326599939269E-4</v>
       </c>
       <c r="T17">
-        <v>-3.1771881599505177E-3</v>
+        <v>1.514563307848547E-4</v>
       </c>
       <c r="U17">
-        <v>3.2433770793514953E-4</v>
+        <v>2.7558157079330916E-5</v>
       </c>
       <c r="V17">
-        <v>-3.8670933731651883E-3</v>
-      </c>
-    </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+        <v>-8.4265620388735969E-4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A18" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="B18">
-        <v>6.2033253090084716E-3</v>
+      <c r="B18" s="7">
+        <v>-0.13045334914227164</v>
       </c>
       <c r="C18">
-        <v>-1.1209844410064573E-4</v>
+        <v>-1.0906912166162158E-4</v>
       </c>
       <c r="D18">
-        <v>-5.7718389333629577E-5</v>
+        <v>-5.7452679569498484E-5</v>
       </c>
       <c r="E18">
-        <v>5.8798950203362081E-7</v>
+        <v>5.9242926978984871E-7</v>
       </c>
       <c r="F18">
-        <v>-8.0899670399283341E-5</v>
+        <v>-1.980955543431492E-4</v>
       </c>
       <c r="G18">
-        <v>-4.3120415413403033E-4</v>
+        <v>-5.5206689033472645E-4</v>
       </c>
       <c r="H18">
-        <v>-2.5316546362665147E-4</v>
+        <v>-5.455034895268402E-4</v>
       </c>
       <c r="I18">
-        <v>1.7186741626007808E-4</v>
+        <v>1.4775817517303927E-4</v>
       </c>
       <c r="J18">
-        <v>-2.7720396047130162E-4</v>
+        <v>-1.6192257533607663E-4</v>
       </c>
       <c r="K18">
-        <v>1.6665939183647472E-4</v>
+        <v>1.9592154293996984E-4</v>
       </c>
       <c r="L18">
-        <v>1.8132577312509777E-4</v>
+        <v>5.1517420325050429E-5</v>
       </c>
       <c r="M18">
-        <v>-6.3434959356604764E-4</v>
+        <v>1.6498778384609254E-4</v>
       </c>
       <c r="N18">
-        <v>-1.7196646710945568E-4</v>
+        <v>-9.3282035375342499E-5</v>
       </c>
       <c r="O18">
-        <v>1.7757521411295216E-5</v>
+        <v>8.7345181349986797E-6</v>
       </c>
       <c r="P18">
-        <v>2.3119863536191637E-3</v>
+        <v>2.6269620253293485E-4</v>
       </c>
       <c r="Q18">
-        <v>-2.0011785946081351E-5</v>
+        <v>-1.7901257616996139E-5</v>
       </c>
       <c r="R18">
-        <v>-3.1243475959661189E-3</v>
+        <v>1.0083326599939269E-4</v>
       </c>
       <c r="S18">
-        <v>3.292810930976965E-3</v>
+        <v>2.5763018666673373E-3</v>
       </c>
       <c r="T18">
-        <v>2.3489266677833532E-3</v>
+        <v>1.8764321660145111E-3</v>
       </c>
       <c r="U18">
-        <v>-5.9039583244664237E-5</v>
+        <v>-5.9076076701580175E-5</v>
       </c>
       <c r="V18">
-        <v>7.1460989758666954E-4</v>
-      </c>
-    </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+        <v>8.9278814988223351E-4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A19" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="B19">
-        <v>-0.10213128610126428</v>
+      <c r="B19" s="7">
+        <v>-0.29612608058567269</v>
       </c>
       <c r="C19">
-        <v>-1.1311760860704164E-4</v>
+        <v>-8.535940952759751E-5</v>
       </c>
       <c r="D19">
-        <v>-4.0033974316033318E-5</v>
+        <v>-4.2557971765152646E-5</v>
       </c>
       <c r="E19">
-        <v>4.2258028806795031E-7</v>
+        <v>4.3681072621852343E-7</v>
       </c>
       <c r="F19">
-        <v>-2.4422270597085479E-4</v>
+        <v>-2.971516575533688E-4</v>
       </c>
       <c r="G19">
-        <v>-4.7768750130597944E-4</v>
+        <v>-6.1494216492038447E-4</v>
       </c>
       <c r="H19">
-        <v>-6.0800792939509456E-4</v>
+        <v>-5.1445012677452107E-4</v>
       </c>
       <c r="I19">
-        <v>1.7237269746029921E-4</v>
+        <v>1.4939015894451088E-4</v>
       </c>
       <c r="J19">
-        <v>-1.7574111899570227E-4</v>
+        <v>1.5419757416658929E-5</v>
       </c>
       <c r="K19">
-        <v>1.8622711288142661E-4</v>
+        <v>1.4669200317054924E-4</v>
       </c>
       <c r="L19">
-        <v>1.9705502294746751E-4</v>
+        <v>5.8482901722426654E-5</v>
       </c>
       <c r="M19">
-        <v>-5.0014072772406172E-4</v>
+        <v>1.972424416282969E-4</v>
       </c>
       <c r="N19">
-        <v>-1.375990364212926E-4</v>
+        <v>-8.5758712174573235E-5</v>
       </c>
       <c r="O19">
-        <v>1.8423144210963913E-5</v>
+        <v>1.1372422166109199E-5</v>
       </c>
       <c r="P19">
-        <v>2.5979553500621935E-3</v>
+        <v>3.5867959151030101E-4</v>
       </c>
       <c r="Q19">
-        <v>-1.3226576168481793E-5</v>
+        <v>-8.6362985071152291E-6</v>
       </c>
       <c r="R19">
-        <v>-3.1771881599505177E-3</v>
+        <v>1.514563307848547E-4</v>
       </c>
       <c r="S19">
-        <v>2.3489266677833532E-3</v>
+        <v>1.8764321660145111E-3</v>
       </c>
       <c r="T19">
-        <v>2.70466738384519E-3</v>
+        <v>2.1789204781280137E-3</v>
       </c>
       <c r="U19">
-        <v>-4.1670694429800541E-5</v>
+        <v>-5.8549843590020692E-5</v>
       </c>
       <c r="V19">
-        <v>-1.0111492519086697E-4</v>
-      </c>
-    </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+        <v>4.9004306775123345E-4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A20" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="B20">
-        <v>2.6166201866409727E-3</v>
+      <c r="B20" s="7">
+        <v>-1.6603958964387273E-3</v>
       </c>
       <c r="C20">
-        <v>2.1006550147106387E-5</v>
+        <v>5.4471686966269434E-6</v>
       </c>
       <c r="D20">
-        <v>6.0928987697527089E-6</v>
+        <v>3.3185740126174515E-6</v>
       </c>
       <c r="E20">
-        <v>-7.9483588855033187E-8</v>
+        <v>-4.3000635655077416E-8</v>
       </c>
       <c r="F20">
-        <v>3.238205747657587E-5</v>
+        <v>1.5103122809794487E-5</v>
       </c>
       <c r="G20">
-        <v>4.9268623531035117E-5</v>
+        <v>2.3665857040760163E-5</v>
       </c>
       <c r="H20">
-        <v>4.8570386811534793E-6</v>
+        <v>1.637552771625644E-6</v>
       </c>
       <c r="I20">
-        <v>-2.448932239456546E-5</v>
+        <v>-2.9782859362962797E-5</v>
       </c>
       <c r="J20">
-        <v>1.4333161147453075E-5</v>
+        <v>-1.9757148350270674E-5</v>
       </c>
       <c r="K20">
-        <v>-4.2445677561562877E-5</v>
+        <v>-2.8455401759327017E-6</v>
       </c>
       <c r="L20">
-        <v>-4.2271955458544452E-5</v>
+        <v>-1.6256958596493011E-5</v>
       </c>
       <c r="M20">
-        <v>1.268489349953425E-5</v>
+        <v>-2.5599927099522555E-5</v>
       </c>
       <c r="N20">
-        <v>1.0124442769630124E-5</v>
+        <v>-2.6163806895204787E-7</v>
       </c>
       <c r="O20">
-        <v>-4.7431895265010319E-6</v>
+        <v>-4.2457828382149717E-6</v>
       </c>
       <c r="P20">
-        <v>-9.7364192908278556E-5</v>
+        <v>-2.1875595937009358E-5</v>
       </c>
       <c r="Q20">
-        <v>-5.8626226481336741E-6</v>
+        <v>-1.7280521860250845E-6</v>
       </c>
       <c r="R20">
-        <v>3.2433770793514953E-4</v>
+        <v>2.7558157079330916E-5</v>
       </c>
       <c r="S20">
-        <v>-5.9039583244664237E-5</v>
+        <v>-5.9076076701580175E-5</v>
       </c>
       <c r="T20">
-        <v>-4.1670694429800541E-5</v>
+        <v>-5.8549843590020692E-5</v>
       </c>
       <c r="U20">
-        <v>4.6852588895343871E-5</v>
+        <v>2.6292455796104688E-5</v>
       </c>
       <c r="V20">
-        <v>-8.1341058828034391E-4</v>
-      </c>
-    </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+        <v>-3.8470152233795375E-4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A21" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B21">
-        <v>-3.3911705870058162</v>
+      <c r="B21" s="7">
+        <v>-3.0388070601859978</v>
       </c>
       <c r="C21">
-        <v>-1.0846802946997023E-3</v>
+        <v>-9.5153740686186518E-4</v>
       </c>
       <c r="D21">
-        <v>-1.5554030069631526E-3</v>
+        <v>-1.2210088503361056E-3</v>
       </c>
       <c r="E21">
-        <v>1.4316082145922566E-5</v>
+        <v>1.0835919980753418E-5</v>
       </c>
       <c r="F21">
-        <v>-2.5080921180868796E-3</v>
+        <v>-2.0702554684727168E-3</v>
       </c>
       <c r="G21">
-        <v>-5.1612812539170768E-3</v>
+        <v>-3.8522072573399209E-3</v>
       </c>
       <c r="H21">
-        <v>-9.5479299439533722E-3</v>
+        <v>-8.0809729364833133E-3</v>
       </c>
       <c r="I21">
-        <v>-2.5875493120586499E-3</v>
+        <v>-1.5190247740773191E-3</v>
       </c>
       <c r="J21">
-        <v>-3.8128303692830301E-3</v>
+        <v>-2.1966311904637117E-3</v>
       </c>
       <c r="K21">
-        <v>-7.7611063389352556E-4</v>
+        <v>-2.3814153979160239E-3</v>
       </c>
       <c r="L21">
-        <v>-2.8170258826519033E-3</v>
+        <v>-2.5707642124739136E-3</v>
       </c>
       <c r="M21">
-        <v>4.6075597104513739E-4</v>
+        <v>-1.5189346188460278E-3</v>
       </c>
       <c r="N21">
-        <v>-2.8362085055283386E-3</v>
+        <v>-2.2042654986475061E-3</v>
       </c>
       <c r="O21">
-        <v>-1.7690766349992359E-4</v>
+        <v>-1.6091015196135865E-4</v>
       </c>
       <c r="P21">
-        <v>6.7447412652506646E-4</v>
+        <v>-1.5774693137675352E-6</v>
       </c>
       <c r="Q21">
-        <v>2.5799308182290233E-4</v>
+        <v>1.5056789549973626E-4</v>
       </c>
       <c r="R21">
-        <v>-3.8670933731651883E-3</v>
+        <v>-8.4265620388735969E-4</v>
       </c>
       <c r="S21">
-        <v>7.1460989758666954E-4</v>
+        <v>8.9278814988223351E-4</v>
       </c>
       <c r="T21">
-        <v>-1.0111492519086697E-4</v>
+        <v>4.9004306775123345E-4</v>
       </c>
       <c r="U21">
-        <v>-8.1341058828034391E-4</v>
+        <v>-3.8470152233795375E-4</v>
       </c>
       <c r="V21">
-        <v>6.7411629530540002E-2</v>
+        <v>4.9994674055324144E-2</v>
       </c>
     </row>
   </sheetData>

--- a/input/reg_income.xlsx
+++ b/input/reg_income.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Patryk\git\SimPaths_HU\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E9BB024-F1E5-4368-BA66-DFDA85B3FAA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE040AC0-E7F0-426C-8D98-D7F3C07A2CA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-83" yWindow="0" windowWidth="14566" windowHeight="17363" tabRatio="852" activeTab="4" xr2:uid="{8DDB884B-4CBA-4D96-8159-4841B9678181}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" tabRatio="852" activeTab="4" xr2:uid="{8DDB884B-4CBA-4D96-8159-4841B9678181}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="7" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="36">
   <si>
     <t>Constant</t>
   </si>
@@ -149,12 +149,6 @@
   <si>
     <t>COEFFICIENT</t>
   </si>
-  <si>
-    <t>Les_c3_Student_L1</t>
-  </si>
-  <si>
-    <t>Les_c3_NotEmployed_L1</t>
-  </si>
 </sst>
 </file>
 
@@ -225,13 +219,13 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="4"/>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -559,16 +553,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="6">
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="7">
         <v>45623</v>
       </c>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
     </row>
     <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
@@ -694,10 +688,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="5" t="s">
         <v>35</v>
       </c>
       <c r="C1" t="s">
@@ -732,10 +726,10 @@
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="7">
+      <c r="B2" s="5">
         <v>-7.1433508314934793E-2</v>
       </c>
       <c r="C2">
@@ -770,10 +764,10 @@
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="7">
+      <c r="B3" s="5">
         <v>-0.67049384303294957</v>
       </c>
       <c r="C3">
@@ -808,10 +802,10 @@
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="7">
+      <c r="B4" s="5">
         <v>1.3692507072557822E-2</v>
       </c>
       <c r="C4">
@@ -846,10 +840,10 @@
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="5">
         <v>3.0156752093573394E-2</v>
       </c>
       <c r="C5">
@@ -884,10 +878,10 @@
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B6" s="5">
         <v>8.0056636216084123E-2</v>
       </c>
       <c r="C6">
@@ -922,10 +916,10 @@
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="7">
+      <c r="B7" s="5">
         <v>4.6733997471688005</v>
       </c>
       <c r="C7">
@@ -960,10 +954,10 @@
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="B8" s="7">
+      <c r="B8" s="5">
         <v>0.21555847875657319</v>
       </c>
       <c r="C8">
@@ -998,10 +992,10 @@
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="B9" s="7">
+      <c r="B9" s="5">
         <v>0.22048535827922361</v>
       </c>
       <c r="C9">
@@ -1036,10 +1030,10 @@
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B10" s="7">
+      <c r="B10" s="5">
         <v>-3.941476191921045E-2</v>
       </c>
       <c r="C10">
@@ -1074,10 +1068,10 @@
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A11" s="7" t="s">
+      <c r="A11" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B11" s="7">
+      <c r="B11" s="5">
         <v>6.8095187118365725</v>
       </c>
       <c r="C11">
@@ -1126,10 +1120,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="5" t="s">
         <v>35</v>
       </c>
       <c r="C1" t="s">
@@ -1194,10 +1188,10 @@
       </c>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="7">
+      <c r="B2" s="5">
         <v>-7.6200130854162482E-2</v>
       </c>
       <c r="C2">
@@ -1262,10 +1256,10 @@
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="7">
+      <c r="B3" s="5">
         <v>-2.012971628744397E-2</v>
       </c>
       <c r="C3">
@@ -1330,10 +1324,10 @@
       </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="7">
+      <c r="B4" s="5">
         <v>1.4540427440475469E-4</v>
       </c>
       <c r="C4">
@@ -1398,10 +1392,10 @@
       </c>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="5">
         <v>9.0034343022481977E-2</v>
       </c>
       <c r="C5">
@@ -1466,10 +1460,10 @@
       </c>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B6" s="5">
         <v>7.8350291219620324E-2</v>
       </c>
       <c r="C6">
@@ -1534,10 +1528,10 @@
       </c>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="B7" s="7">
+      <c r="B7" s="5">
         <v>0.26171896666474653</v>
       </c>
       <c r="C7">
@@ -1602,10 +1596,10 @@
       </c>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="B8" s="7">
+      <c r="B8" s="5">
         <v>0.28034907297364431</v>
       </c>
       <c r="C8">
@@ -1670,10 +1664,10 @@
       </c>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="B9" s="7">
+      <c r="B9" s="5">
         <v>0.10953836344419209</v>
       </c>
       <c r="C9">
@@ -1738,10 +1732,10 @@
       </c>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="7">
+      <c r="B10" s="5">
         <v>0.47128913960443108</v>
       </c>
       <c r="C10">
@@ -1806,10 +1800,10 @@
       </c>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="A11" s="7" t="s">
+      <c r="A11" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B11" s="7">
+      <c r="B11" s="5">
         <v>0.11718800537777413</v>
       </c>
       <c r="C11">
@@ -1874,10 +1868,10 @@
       </c>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="A12" s="7" t="s">
+      <c r="A12" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="7">
+      <c r="B12" s="5">
         <v>0.9893644613640965</v>
       </c>
       <c r="C12">
@@ -1942,10 +1936,10 @@
       </c>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="A13" s="7" t="s">
+      <c r="A13" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B13" s="7">
+      <c r="B13" s="5">
         <v>-8.2941991787264135E-2</v>
       </c>
       <c r="C13">
@@ -2010,10 +2004,10 @@
       </c>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="A14" s="7" t="s">
+      <c r="A14" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B14" s="7">
+      <c r="B14" s="5">
         <v>2.3975932395520701E-2</v>
       </c>
       <c r="C14">
@@ -2078,10 +2072,10 @@
       </c>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="A15" s="7" t="s">
+      <c r="A15" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="7">
+      <c r="B15" s="5">
         <v>3.3289135184300083</v>
       </c>
       <c r="C15">
@@ -2146,10 +2140,10 @@
       </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="A16" s="7" t="s">
+      <c r="A16" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B16" s="7">
+      <c r="B16" s="5">
         <v>6.1391422278524238E-3</v>
       </c>
       <c r="C16">
@@ -2214,10 +2208,10 @@
       </c>
     </row>
     <row r="17" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="A17" s="7" t="s">
+      <c r="A17" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B17" s="7">
+      <c r="B17" s="5">
         <v>2.3672517942967479</v>
       </c>
       <c r="C17">
@@ -2282,10 +2276,10 @@
       </c>
     </row>
     <row r="18" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="A18" s="7" t="s">
+      <c r="A18" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="B18" s="7">
+      <c r="B18" s="5">
         <v>0.18146203210633352</v>
       </c>
       <c r="C18">
@@ -2350,10 +2344,10 @@
       </c>
     </row>
     <row r="19" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="A19" s="7" t="s">
+      <c r="A19" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="B19" s="7">
+      <c r="B19" s="5">
         <v>0.44142752781695577</v>
       </c>
       <c r="C19">
@@ -2418,10 +2412,10 @@
       </c>
     </row>
     <row r="20" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="A20" s="7" t="s">
+      <c r="A20" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B20" s="7">
+      <c r="B20" s="5">
         <v>-3.5124590603923291E-2</v>
       </c>
       <c r="C20">
@@ -2486,10 +2480,10 @@
       </c>
     </row>
     <row r="21" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="A21" s="7" t="s">
+      <c r="A21" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B21" s="7">
+      <c r="B21" s="5">
         <v>-1.1297035541990583</v>
       </c>
       <c r="C21">
@@ -2568,10 +2562,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="5" t="s">
         <v>35</v>
       </c>
       <c r="C1" t="s">
@@ -2606,10 +2600,10 @@
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="7">
+      <c r="B2" s="5">
         <v>-5.051551827747696E-2</v>
       </c>
       <c r="C2">
@@ -2644,10 +2638,10 @@
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="7">
+      <c r="B3" s="5">
         <v>-1.2983719900740349</v>
       </c>
       <c r="C3">
@@ -2682,10 +2676,10 @@
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="7">
+      <c r="B4" s="5">
         <v>2.9464976784623838E-2</v>
       </c>
       <c r="C4">
@@ -2720,10 +2714,10 @@
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="5">
         <v>9.2798509400978169E-2</v>
       </c>
       <c r="C5">
@@ -2758,10 +2752,10 @@
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B6" s="5">
         <v>3.0795246185701276E-2</v>
       </c>
       <c r="C6">
@@ -2796,10 +2790,10 @@
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="7">
+      <c r="B7" s="5">
         <v>2.3801091773278706</v>
       </c>
       <c r="C7">
@@ -2834,10 +2828,10 @@
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="B8" s="7">
+      <c r="B8" s="5">
         <v>-6.2524673324793209E-2</v>
       </c>
       <c r="C8">
@@ -2872,10 +2866,10 @@
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="B9" s="7">
+      <c r="B9" s="5">
         <v>-0.19973254849945279</v>
       </c>
       <c r="C9">
@@ -2910,10 +2904,10 @@
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B10" s="7">
+      <c r="B10" s="5">
         <v>-1.3919841860523082E-2</v>
       </c>
       <c r="C10">
@@ -2948,10 +2942,10 @@
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A11" s="7" t="s">
+      <c r="A11" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B11" s="7">
+      <c r="B11" s="5">
         <v>11.616030505838898</v>
       </c>
       <c r="C11">
@@ -2995,15 +2989,14 @@
   <dimension ref="A1:V21"/>
   <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="30.73046875" style="4" customWidth="1"/>
-    <col min="2" max="16384" width="9.1328125" style="4"/>
+    <col min="1" max="1" width="30.73046875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="A1" s="7" t="s">
+      <c r="A1" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" t="s">
         <v>35</v>
       </c>
       <c r="C1" t="s">
@@ -3022,10 +3015,10 @@
         <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="I1" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="J1" t="s">
         <v>33</v>
@@ -3068,10 +3061,10 @@
       </c>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="A2" s="7" t="s">
+      <c r="A2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="7">
+      <c r="B2">
         <v>-9.5778030584876342E-2</v>
       </c>
       <c r="C2">
@@ -3136,10 +3129,10 @@
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="A3" s="7" t="s">
+      <c r="A3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="7">
+      <c r="B3">
         <v>6.1101552479797261E-3</v>
       </c>
       <c r="C3">
@@ -3204,10 +3197,10 @@
       </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="A4" s="7" t="s">
+      <c r="A4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="7">
+      <c r="B4">
         <v>2.008650639520531E-5</v>
       </c>
       <c r="C4">
@@ -3272,10 +3265,10 @@
       </c>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="A5" s="7" t="s">
+      <c r="A5" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5">
         <v>-0.11562459622351498</v>
       </c>
       <c r="C5">
@@ -3340,10 +3333,10 @@
       </c>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="A6" s="7" t="s">
+      <c r="A6" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B6">
         <v>-0.312049720588844</v>
       </c>
       <c r="C6">
@@ -3408,10 +3401,10 @@
       </c>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="A7" s="7" t="s">
+      <c r="A7" t="s">
         <v>31</v>
       </c>
-      <c r="B7" s="7">
+      <c r="B7">
         <v>0.14078681528491385</v>
       </c>
       <c r="C7">
@@ -3476,10 +3469,10 @@
       </c>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="A8" s="7" t="s">
+      <c r="A8" t="s">
         <v>32</v>
       </c>
-      <c r="B8" s="7">
+      <c r="B8">
         <v>0.12984391365926448</v>
       </c>
       <c r="C8">
@@ -3544,10 +3537,10 @@
       </c>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="A9" s="7" t="s">
+      <c r="A9" t="s">
         <v>33</v>
       </c>
-      <c r="B9" s="7">
+      <c r="B9">
         <v>5.9583423494434233E-2</v>
       </c>
       <c r="C9">
@@ -3612,10 +3605,10 @@
       </c>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="A10" s="7" t="s">
+      <c r="A10" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="7">
+      <c r="B10">
         <v>0.25513923752639073</v>
       </c>
       <c r="C10">
@@ -3680,10 +3673,10 @@
       </c>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="A11" s="7" t="s">
+      <c r="A11" t="s">
         <v>8</v>
       </c>
-      <c r="B11" s="7">
+      <c r="B11">
         <v>0.27833075411789471</v>
       </c>
       <c r="C11">
@@ -3748,10 +3741,10 @@
       </c>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="A12" s="7" t="s">
+      <c r="A12" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="7">
+      <c r="B12">
         <v>0.50183521712027657</v>
       </c>
       <c r="C12">
@@ -3816,10 +3809,10 @@
       </c>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="A13" s="7" t="s">
+      <c r="A13" t="s">
         <v>4</v>
       </c>
-      <c r="B13" s="7">
+      <c r="B13">
         <v>4.8504321017053396E-2</v>
       </c>
       <c r="C13">
@@ -3884,10 +3877,10 @@
       </c>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="A14" s="7" t="s">
+      <c r="A14" t="s">
         <v>10</v>
       </c>
-      <c r="B14" s="7">
+      <c r="B14">
         <v>1.2350662793498153E-2</v>
       </c>
       <c r="C14">
@@ -3952,10 +3945,10 @@
       </c>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="A15" s="7" t="s">
+      <c r="A15" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="7">
+      <c r="B15">
         <v>1.5194782682779264</v>
       </c>
       <c r="C15">
@@ -4020,10 +4013,10 @@
       </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="A16" s="7" t="s">
+      <c r="A16" t="s">
         <v>11</v>
       </c>
-      <c r="B16" s="7">
+      <c r="B16">
         <v>1.886703240580263E-2</v>
       </c>
       <c r="C16">
@@ -4088,10 +4081,10 @@
       </c>
     </row>
     <row r="17" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="A17" s="7" t="s">
+      <c r="A17" t="s">
         <v>14</v>
       </c>
-      <c r="B17" s="7">
+      <c r="B17">
         <v>1.0332562831438197</v>
       </c>
       <c r="C17">
@@ -4156,10 +4149,10 @@
       </c>
     </row>
     <row r="18" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="A18" s="7" t="s">
+      <c r="A18" t="s">
         <v>29</v>
       </c>
-      <c r="B18" s="7">
+      <c r="B18">
         <v>-0.13045334914227164</v>
       </c>
       <c r="C18">
@@ -4224,10 +4217,10 @@
       </c>
     </row>
     <row r="19" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="A19" s="7" t="s">
+      <c r="A19" t="s">
         <v>30</v>
       </c>
-      <c r="B19" s="7">
+      <c r="B19">
         <v>-0.29612608058567269</v>
       </c>
       <c r="C19">
@@ -4292,10 +4285,10 @@
       </c>
     </row>
     <row r="20" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="A20" s="7" t="s">
+      <c r="A20" t="s">
         <v>15</v>
       </c>
-      <c r="B20" s="7">
+      <c r="B20">
         <v>-1.6603958964387273E-3</v>
       </c>
       <c r="C20">
@@ -4360,10 +4353,10 @@
       </c>
     </row>
     <row r="21" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="A21" s="7" t="s">
+      <c r="A21" t="s">
         <v>0</v>
       </c>
-      <c r="B21" s="7">
+      <c r="B21">
         <v>-3.0388070601859978</v>
       </c>
       <c r="C21">

--- a/input/reg_income.xlsx
+++ b/input/reg_income.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Patryk\git\SimPaths_HU\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{540C88CD-7E85-471E-A0BE-1350A34D4C13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{957CDB07-C0D9-4BCC-9649-602BBEDA83A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-83" yWindow="0" windowWidth="14566" windowHeight="17363" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" tabRatio="776" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="1" r:id="rId1"/>
-    <sheet name="PL_I3a_selection" sheetId="2" r:id="rId2"/>
-    <sheet name="PL_I3b_selection" sheetId="3" r:id="rId3"/>
-    <sheet name="PL_I3a_amount" sheetId="4" r:id="rId4"/>
-    <sheet name="PL_I3b_amount" sheetId="5" r:id="rId5"/>
+    <sheet name="IT_I3a_selection" sheetId="2" r:id="rId2"/>
+    <sheet name="IT_I3b_selection" sheetId="3" r:id="rId3"/>
+    <sheet name="IT_I3a_amount" sheetId="4" r:id="rId4"/>
+    <sheet name="IT_I3b_amount" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
@@ -60,9 +60,6 @@
   </si>
   <si>
     <t>Categorical health variable modelled as continuous</t>
-  </si>
-  <si>
-    <t>Region Poludniowy is the omitted category.</t>
   </si>
   <si>
     <t>REGRESSOR</t>
@@ -131,46 +128,32 @@
     <t>Ypncp_L2</t>
   </si>
   <si>
-    <t>PL4</t>
+    <t>Regions: ITF = South, ITG = Islands, ITH = Northeast, ITI = Central. Northwest (ITC) is the omitted region.</t>
   </si>
   <si>
-    <t>PL5</t>
+    <t>ITF</t>
   </si>
   <si>
-    <t>PL6</t>
+    <t>ITG</t>
   </si>
   <si>
-    <t>PL10</t>
+    <t>ITH</t>
+  </si>
+  <si>
+    <t>ITI</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
@@ -183,21 +166,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="4">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -216,12 +185,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -557,7 +523,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
@@ -571,7 +537,7 @@
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="1" t="s">
         <v>0</v>
       </c>
     </row>
@@ -608,7 +574,7 @@
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B10" t="s">
@@ -617,7 +583,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B11" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -635,28 +601,28 @@
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" t="s">
         <v>13</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>14</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>15</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>16</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>17</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>18</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>19</v>
-      </c>
-      <c r="H1" t="s">
-        <v>20</v>
       </c>
       <c r="I1" t="s">
         <v>35</v>
@@ -671,716 +637,716 @@
         <v>38</v>
       </c>
       <c r="M1" t="s">
+        <v>20</v>
+      </c>
+      <c r="N1" t="s">
         <v>21</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>22</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>23</v>
-      </c>
-      <c r="P1" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2" s="4">
-        <v>-5.4195916477670178E-2</v>
+        <v>14</v>
+      </c>
+      <c r="B2">
+        <v>-3.7472243874744224E-2</v>
       </c>
       <c r="C2">
-        <v>8.1691920548476547E-3</v>
+        <v>4.2330266613677453E-3</v>
       </c>
       <c r="D2">
-        <v>2.5927086468314185E-4</v>
+        <v>1.4011929433466984E-3</v>
       </c>
       <c r="E2">
-        <v>-6.8166325106816638E-6</v>
+        <v>-3.0342612296865325E-5</v>
       </c>
       <c r="F2">
-        <v>4.0525755546789608E-4</v>
+        <v>-1.0081018369028926E-4</v>
       </c>
       <c r="G2">
-        <v>2.3087837583198617E-4</v>
+        <v>-7.0738901173439649E-5</v>
       </c>
       <c r="H2">
-        <v>-6.5016898835071335E-4</v>
+        <v>-4.7757775831659531E-4</v>
       </c>
       <c r="I2">
-        <v>4.9805907074982605E-4</v>
+        <v>8.2284140742923504E-4</v>
       </c>
       <c r="J2">
-        <v>1.3214142799248185E-4</v>
+        <v>8.6838176634904487E-4</v>
       </c>
       <c r="K2">
-        <v>-5.676904090733553E-4</v>
+        <v>6.3391707348764469E-4</v>
       </c>
       <c r="L2">
-        <v>-4.485077544803776E-4</v>
+        <v>5.6019852202740441E-4</v>
       </c>
       <c r="M2">
-        <v>2.7204180497073091E-5</v>
+        <v>-5.1773643727376817E-5</v>
       </c>
       <c r="N2">
-        <v>2.0443495185602789E-5</v>
+        <v>4.041009087219897E-4</v>
       </c>
       <c r="O2">
-        <v>4.0401144563914117E-4</v>
+        <v>4.306351377614681E-4</v>
       </c>
       <c r="P2">
-        <v>-8.6062735248320175E-3</v>
+        <v>-1.7070095679316097E-2</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" s="4">
-        <v>-1.2930789870906354</v>
+        <v>15</v>
+      </c>
+      <c r="B3">
+        <v>-0.64443853620467872</v>
       </c>
       <c r="C3">
-        <v>2.5927086468314185E-4</v>
+        <v>1.4011929433466984E-3</v>
       </c>
       <c r="D3">
-        <v>0.13557900273199791</v>
+        <v>3.6786930726820599E-2</v>
       </c>
       <c r="E3">
-        <v>-3.1928022328535461E-3</v>
+        <v>-8.4368840949642764E-4</v>
       </c>
       <c r="F3">
-        <v>-1.7720913230165336E-3</v>
+        <v>-2.2322209756015648E-4</v>
       </c>
       <c r="G3">
-        <v>8.2483561493512311E-4</v>
+        <v>-4.9455366625533867E-5</v>
       </c>
       <c r="H3">
-        <v>-3.0735952235135144E-2</v>
+        <v>-5.9941752295459491E-3</v>
       </c>
       <c r="I3">
-        <v>-8.8347110041592236E-4</v>
+        <v>8.1223688962803534E-4</v>
       </c>
       <c r="J3">
-        <v>-4.2364121916049768E-3</v>
+        <v>8.4021225092044405E-4</v>
       </c>
       <c r="K3">
-        <v>-1.2458261744344029E-3</v>
+        <v>-1.5596007682813773E-4</v>
       </c>
       <c r="L3">
-        <v>-4.903096949434374E-3</v>
+        <v>-4.5943210625193354E-4</v>
       </c>
       <c r="M3">
-        <v>1.9922906335933036E-4</v>
+        <v>4.8064846678790019E-5</v>
       </c>
       <c r="N3">
-        <v>-1.3302070002176869E-3</v>
+        <v>2.6640013656867856E-3</v>
       </c>
       <c r="O3">
-        <v>2.7847462886532171E-5</v>
+        <v>-4.9643862402694305E-4</v>
       </c>
       <c r="P3">
-        <v>-1.4116192330683661</v>
+        <v>-0.39400359802311691</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B4" s="4">
-        <v>2.8636951172297961E-2</v>
+        <v>16</v>
+      </c>
+      <c r="B4">
+        <v>1.5681035283139862E-2</v>
       </c>
       <c r="C4">
-        <v>-6.8166325106816638E-6</v>
+        <v>-3.0342612296865325E-5</v>
       </c>
       <c r="D4">
-        <v>-3.1928022328535461E-3</v>
+        <v>-8.4368840949642764E-4</v>
       </c>
       <c r="E4">
-        <v>7.5504267241909023E-5</v>
+        <v>1.9434431241970902E-5</v>
       </c>
       <c r="F4">
-        <v>3.7114904614166545E-5</v>
+        <v>5.9511204385834476E-6</v>
       </c>
       <c r="G4">
-        <v>-2.2888563418816364E-5</v>
+        <v>-2.0766477567771059E-7</v>
       </c>
       <c r="H4">
-        <v>6.7729699830049173E-4</v>
+        <v>1.3205020647803583E-4</v>
       </c>
       <c r="I4">
-        <v>3.8972871924849994E-5</v>
+        <v>-2.0102871049139533E-5</v>
       </c>
       <c r="J4">
-        <v>1.0419969467440927E-4</v>
+        <v>-2.1746552313193883E-5</v>
       </c>
       <c r="K4">
-        <v>4.0277390738826082E-5</v>
+        <v>3.3888438533994855E-6</v>
       </c>
       <c r="L4">
-        <v>1.3013587127392033E-4</v>
+        <v>9.8508104931609164E-6</v>
       </c>
       <c r="M4">
-        <v>-4.5241372333371067E-6</v>
+        <v>-1.1719006530320868E-6</v>
       </c>
       <c r="N4">
-        <v>3.6366219018603083E-5</v>
+        <v>-5.7629422641374169E-5</v>
       </c>
       <c r="O4">
-        <v>-9.9358884120270829E-7</v>
+        <v>1.3035253363248567E-5</v>
       </c>
       <c r="P4">
-        <v>3.3127252719317851E-2</v>
+        <v>8.9984676757957766E-3</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" s="4">
-        <v>-0.1973557992456175</v>
+        <v>17</v>
+      </c>
+      <c r="B5">
+        <v>5.5623440011398712E-2</v>
       </c>
       <c r="C5">
-        <v>4.0525755546789608E-4</v>
+        <v>-1.0081018369028926E-4</v>
       </c>
       <c r="D5">
-        <v>-1.7720913230165336E-3</v>
+        <v>-2.2322209756015648E-4</v>
       </c>
       <c r="E5">
-        <v>3.7114904614166545E-5</v>
+        <v>5.9511204385834476E-6</v>
       </c>
       <c r="F5">
-        <v>4.7445377445975113E-3</v>
+        <v>2.1820600691346737E-3</v>
       </c>
       <c r="G5">
-        <v>-7.9726076344024542E-5</v>
+        <v>6.9760481537111708E-5</v>
       </c>
       <c r="H5">
-        <v>2.9078458026708456E-3</v>
+        <v>-2.5598936431665863E-4</v>
       </c>
       <c r="I5">
-        <v>6.7660067941723977E-4</v>
+        <v>-4.8941988862661017E-4</v>
       </c>
       <c r="J5">
-        <v>9.6815510454524838E-4</v>
+        <v>-7.5725241908537505E-4</v>
       </c>
       <c r="K5">
-        <v>-3.1605842463547801E-4</v>
+        <v>-1.6468240401233767E-4</v>
       </c>
       <c r="L5">
-        <v>-7.502633651325244E-5</v>
+        <v>-2.1656381093853802E-4</v>
       </c>
       <c r="M5">
-        <v>6.1604915765201397E-5</v>
+        <v>3.2451841570317087E-5</v>
       </c>
       <c r="N5">
-        <v>1.104472807160182E-3</v>
+        <v>-1.4227092903089811E-4</v>
       </c>
       <c r="O5">
-        <v>-6.8895104880995622E-5</v>
+        <v>3.5513194682945323E-4</v>
       </c>
       <c r="P5">
-        <v>-2.2807651744780142E-3</v>
+        <v>-7.5952720633431503E-3</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>19</v>
-      </c>
-      <c r="B6" s="4">
-        <v>0.14155425159903157</v>
+        <v>18</v>
+      </c>
+      <c r="B6">
+        <v>8.1286278235480885E-3</v>
       </c>
       <c r="C6">
-        <v>2.3087837583198617E-4</v>
+        <v>-7.0738901173439649E-5</v>
       </c>
       <c r="D6">
-        <v>8.2483561493512311E-4</v>
+        <v>-4.9455366625533867E-5</v>
       </c>
       <c r="E6">
-        <v>-2.2888563418816364E-5</v>
+        <v>-2.0766477567771059E-7</v>
       </c>
       <c r="F6">
-        <v>-7.9726076344024542E-5</v>
+        <v>6.9760481537111708E-5</v>
       </c>
       <c r="G6">
-        <v>1.8565272735226923E-3</v>
+        <v>3.853947659705936E-4</v>
       </c>
       <c r="H6">
-        <v>-5.4713420063030524E-4</v>
+        <v>-2.8593193081677154E-4</v>
       </c>
       <c r="I6">
-        <v>-1.5769035154343698E-4</v>
+        <v>-1.2647319533019686E-4</v>
       </c>
       <c r="J6">
-        <v>-1.0186300341650158E-3</v>
+        <v>-1.3126358477256236E-4</v>
       </c>
       <c r="K6">
-        <v>-3.9520583004779778E-4</v>
+        <v>-2.1154919270178259E-4</v>
       </c>
       <c r="L6">
-        <v>-3.8110051216101964E-4</v>
+        <v>-1.5383791884923084E-4</v>
       </c>
       <c r="M6">
-        <v>-4.208581769266724E-6</v>
+        <v>1.7335614217387098E-5</v>
       </c>
       <c r="N6">
-        <v>-4.1964026666554098E-4</v>
+        <v>-2.3109710907291301E-4</v>
       </c>
       <c r="O6">
-        <v>6.3286787272887491E-4</v>
+        <v>-1.4514723566559721E-4</v>
       </c>
       <c r="P6">
-        <v>-6.8883707396388914E-3</v>
+        <v>5.7841735178241691E-4</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>20</v>
-      </c>
-      <c r="B7" s="4">
-        <v>6.1101146020187818</v>
+        <v>19</v>
+      </c>
+      <c r="B7">
+        <v>1.8473076056515576</v>
       </c>
       <c r="C7">
-        <v>-6.5016898835071335E-4</v>
+        <v>-4.7757775831659531E-4</v>
       </c>
       <c r="D7">
-        <v>-3.0735952235135144E-2</v>
+        <v>-5.9941752295459491E-3</v>
       </c>
       <c r="E7">
-        <v>6.7729699830049173E-4</v>
+        <v>1.3205020647803583E-4</v>
       </c>
       <c r="F7">
-        <v>2.9078458026708456E-3</v>
+        <v>-2.5598936431665863E-4</v>
       </c>
       <c r="G7">
-        <v>-5.4713420063030524E-4</v>
+        <v>-2.8593193081677154E-4</v>
       </c>
       <c r="H7">
-        <v>0.2274621502916479</v>
+        <v>2.1336010733630156E-2</v>
       </c>
       <c r="I7">
-        <v>-2.0335716009964241E-3</v>
+        <v>-4.6380456273564016E-5</v>
       </c>
       <c r="J7">
-        <v>1.0946242255156058E-2</v>
+        <v>9.4831930125117113E-4</v>
       </c>
       <c r="K7">
-        <v>-4.1757733507196944E-3</v>
+        <v>-3.8530068107109003E-4</v>
       </c>
       <c r="L7">
-        <v>-1.9380397356296363E-3</v>
+        <v>-3.8581798944832893E-4</v>
       </c>
       <c r="M7">
-        <v>-1.3703878397937222E-4</v>
+        <v>1.1481174957408535E-4</v>
       </c>
       <c r="N7">
-        <v>-1.1064409362404728E-2</v>
+        <v>-1.3853311573848032E-3</v>
       </c>
       <c r="O7">
-        <v>3.1059247500814929E-3</v>
+        <v>3.0993625777899804E-4</v>
       </c>
       <c r="P7">
-        <v>0.32304954040186973</v>
+        <v>6.3815705610682727E-2</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>35</v>
       </c>
-      <c r="B8" s="4">
-        <v>0.51843175874412695</v>
+      <c r="B8">
+        <v>-0.65033305637324124</v>
       </c>
       <c r="C8">
-        <v>4.9805907074982605E-4</v>
+        <v>8.2284140742923504E-4</v>
       </c>
       <c r="D8">
-        <v>-8.8347110041592236E-4</v>
+        <v>8.1223688962803534E-4</v>
       </c>
       <c r="E8">
-        <v>3.8972871924849994E-5</v>
+        <v>-2.0102871049139533E-5</v>
       </c>
       <c r="F8">
-        <v>6.7660067941723977E-4</v>
+        <v>-4.8941988862661017E-4</v>
       </c>
       <c r="G8">
-        <v>-1.5769035154343698E-4</v>
+        <v>-1.2647319533019686E-4</v>
       </c>
       <c r="H8">
-        <v>-2.0335716009964241E-3</v>
+        <v>-4.6380456273564016E-5</v>
       </c>
       <c r="I8">
-        <v>3.0137745580250588E-2</v>
+        <v>9.30874852793547E-3</v>
       </c>
       <c r="J8">
-        <v>1.6292725710756163E-2</v>
+        <v>5.5160620741562128E-3</v>
       </c>
       <c r="K8">
-        <v>1.6401852100039596E-2</v>
+        <v>5.4116376204371734E-3</v>
       </c>
       <c r="L8">
-        <v>1.6433576966933181E-2</v>
+        <v>5.4244623210341989E-3</v>
       </c>
       <c r="M8">
-        <v>-8.5512421666685798E-5</v>
+        <v>-1.0183668597221046E-4</v>
       </c>
       <c r="N8">
-        <v>9.1908488846958493E-4</v>
+        <v>7.2636700422437205E-4</v>
       </c>
       <c r="O8">
-        <v>6.5999672950090536E-4</v>
+        <v>3.2651295197115744E-5</v>
       </c>
       <c r="P8">
-        <v>-1.6257081916556806E-2</v>
+        <v>-1.0093389052505251E-2</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>36</v>
       </c>
-      <c r="B9" s="4">
-        <v>0.55667587218144632</v>
+      <c r="B9">
+        <v>-0.61796310467193283</v>
       </c>
       <c r="C9">
-        <v>1.3214142799248185E-4</v>
+        <v>8.6838176634904487E-4</v>
       </c>
       <c r="D9">
-        <v>-4.2364121916049768E-3</v>
+        <v>8.4021225092044405E-4</v>
       </c>
       <c r="E9">
-        <v>1.0419969467440927E-4</v>
+        <v>-2.1746552313193883E-5</v>
       </c>
       <c r="F9">
-        <v>9.6815510454524838E-4</v>
+        <v>-7.5725241908537505E-4</v>
       </c>
       <c r="G9">
-        <v>-1.0186300341650158E-3</v>
+        <v>-1.3126358477256236E-4</v>
       </c>
       <c r="H9">
-        <v>1.0946242255156058E-2</v>
+        <v>9.4831930125117113E-4</v>
       </c>
       <c r="I9">
-        <v>1.6292725710756163E-2</v>
+        <v>5.5160620741562128E-3</v>
       </c>
       <c r="J9">
-        <v>3.9372713955532261E-2</v>
+        <v>1.6549654247359127E-2</v>
       </c>
       <c r="K9">
-        <v>1.62018471024724E-2</v>
+        <v>5.3979228766483514E-3</v>
       </c>
       <c r="L9">
-        <v>1.6281201945770801E-2</v>
+        <v>5.4559871845347753E-3</v>
       </c>
       <c r="M9">
-        <v>1.9079129883465157E-4</v>
+        <v>-1.1738228691953725E-4</v>
       </c>
       <c r="N9">
-        <v>7.4690522880243963E-5</v>
+        <v>5.5680918313313205E-5</v>
       </c>
       <c r="O9">
-        <v>-5.0335122456411294E-4</v>
+        <v>3.0365211206371352E-4</v>
       </c>
       <c r="P9">
-        <v>1.8516219390862364E-2</v>
+        <v>-8.6803415317129456E-3</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="4">
-        <v>0.34094675805504671</v>
+      <c r="B10">
+        <v>-5.8431883082675481E-2</v>
       </c>
       <c r="C10">
-        <v>-5.676904090733553E-4</v>
+        <v>6.3391707348764469E-4</v>
       </c>
       <c r="D10">
-        <v>-1.2458261744344029E-3</v>
+        <v>-1.5596007682813773E-4</v>
       </c>
       <c r="E10">
-        <v>4.0277390738826082E-5</v>
+        <v>3.3888438533994855E-6</v>
       </c>
       <c r="F10">
-        <v>-3.1605842463547801E-4</v>
+        <v>-1.6468240401233767E-4</v>
       </c>
       <c r="G10">
-        <v>-3.9520583004779778E-4</v>
+        <v>-2.1154919270178259E-4</v>
       </c>
       <c r="H10">
-        <v>-4.1757733507196944E-3</v>
+        <v>-3.8530068107109003E-4</v>
       </c>
       <c r="I10">
-        <v>1.6401852100039596E-2</v>
+        <v>5.4116376204371734E-3</v>
       </c>
       <c r="J10">
-        <v>1.62018471024724E-2</v>
+        <v>5.3979228766483514E-3</v>
       </c>
       <c r="K10">
-        <v>2.9315101734371907E-2</v>
+        <v>1.041722994179275E-2</v>
       </c>
       <c r="L10">
-        <v>1.6529826786783143E-2</v>
+        <v>5.4686377849395822E-3</v>
       </c>
       <c r="M10">
-        <v>-1.4042547823460343E-4</v>
+        <v>-1.2196073483569929E-4</v>
       </c>
       <c r="N10">
-        <v>1.0601706424469939E-3</v>
+        <v>-1.6730764401593889E-4</v>
       </c>
       <c r="O10">
-        <v>2.0385673508418194E-3</v>
+        <v>-3.0657001769863719E-4</v>
       </c>
       <c r="P10">
-        <v>-3.7315949711386855E-3</v>
+        <v>-1.1022868369204436E-3</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="4">
-        <v>0.45413664592627845</v>
+      <c r="B11">
+        <v>-0.20937850542299155</v>
       </c>
       <c r="C11">
-        <v>-4.485077544803776E-4</v>
+        <v>5.6019852202740441E-4</v>
       </c>
       <c r="D11">
-        <v>-4.903096949434374E-3</v>
+        <v>-4.5943210625193354E-4</v>
       </c>
       <c r="E11">
-        <v>1.3013587127392033E-4</v>
+        <v>9.8508104931609164E-6</v>
       </c>
       <c r="F11">
-        <v>-7.502633651325244E-5</v>
+        <v>-2.1656381093853802E-4</v>
       </c>
       <c r="G11">
-        <v>-3.8110051216101964E-4</v>
+        <v>-1.5383791884923084E-4</v>
       </c>
       <c r="H11">
-        <v>-1.9380397356296363E-3</v>
+        <v>-3.8581798944832893E-4</v>
       </c>
       <c r="I11">
-        <v>1.6433576966933181E-2</v>
+        <v>5.4244623210341989E-3</v>
       </c>
       <c r="J11">
-        <v>1.6281201945770801E-2</v>
+        <v>5.4559871845347753E-3</v>
       </c>
       <c r="K11">
-        <v>1.6529826786783143E-2</v>
+        <v>5.4686377849395822E-3</v>
       </c>
       <c r="L11">
-        <v>2.0902631506899819E-2</v>
+        <v>8.805285678124726E-3</v>
       </c>
       <c r="M11">
-        <v>-6.8872418659500094E-5</v>
+        <v>-1.7776646269224264E-4</v>
       </c>
       <c r="N11">
-        <v>3.2688443227641355E-4</v>
+        <v>-2.1404012486560264E-4</v>
       </c>
       <c r="O11">
-        <v>1.795632266911477E-3</v>
+        <v>9.2661069274489749E-5</v>
       </c>
       <c r="P11">
-        <v>3.0758647960639689E-2</v>
+        <v>3.5004130210054482E-3</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>21</v>
-      </c>
-      <c r="B12" s="4">
-        <v>-1.3248714263209772E-2</v>
+        <v>20</v>
+      </c>
+      <c r="B12">
+        <v>8.8326801346771525E-2</v>
       </c>
       <c r="C12">
-        <v>2.7204180497073091E-5</v>
+        <v>-5.1773643727376817E-5</v>
       </c>
       <c r="D12">
-        <v>1.9922906335933036E-4</v>
+        <v>4.8064846678790019E-5</v>
       </c>
       <c r="E12">
-        <v>-4.5241372333371067E-6</v>
+        <v>-1.1719006530320868E-6</v>
       </c>
       <c r="F12">
-        <v>6.1604915765201397E-5</v>
+        <v>3.2451841570317087E-5</v>
       </c>
       <c r="G12">
-        <v>-4.208581769266724E-6</v>
+        <v>1.7335614217387098E-5</v>
       </c>
       <c r="H12">
-        <v>-1.3703878397937222E-4</v>
+        <v>1.1481174957408535E-4</v>
       </c>
       <c r="I12">
-        <v>-8.5512421666685798E-5</v>
+        <v>-1.0183668597221046E-4</v>
       </c>
       <c r="J12">
-        <v>1.9079129883465157E-4</v>
+        <v>-1.1738228691953725E-4</v>
       </c>
       <c r="K12">
-        <v>-1.4042547823460343E-4</v>
+        <v>-1.2196073483569929E-4</v>
       </c>
       <c r="L12">
-        <v>-6.8872418659500094E-5</v>
+        <v>-1.7776646269224264E-4</v>
       </c>
       <c r="M12">
-        <v>1.7085367722927027E-4</v>
+        <v>9.3571728841199852E-5</v>
       </c>
       <c r="N12">
-        <v>-7.4707731942032772E-4</v>
+        <v>-3.1613391964968542E-4</v>
       </c>
       <c r="O12">
-        <v>-8.3525857547424071E-4</v>
+        <v>-4.2409811982750049E-4</v>
       </c>
       <c r="P12">
-        <v>-5.0068612123493105E-3</v>
+        <v>-1.9355646229625486E-3</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>22</v>
-      </c>
-      <c r="B13" s="4">
-        <v>-0.57630880707849841</v>
+        <v>21</v>
+      </c>
+      <c r="B13">
+        <v>0.33728316212818055</v>
       </c>
       <c r="C13">
-        <v>2.0443495185602789E-5</v>
+        <v>4.041009087219897E-4</v>
       </c>
       <c r="D13">
-        <v>-1.3302070002176869E-3</v>
+        <v>2.6640013656867856E-3</v>
       </c>
       <c r="E13">
-        <v>3.6366219018603083E-5</v>
+        <v>-5.7629422641374169E-5</v>
       </c>
       <c r="F13">
-        <v>1.104472807160182E-3</v>
+        <v>-1.4227092903089811E-4</v>
       </c>
       <c r="G13">
-        <v>-4.1964026666554098E-4</v>
+        <v>-2.3109710907291301E-4</v>
       </c>
       <c r="H13">
-        <v>-1.1064409362404728E-2</v>
+        <v>-1.3853311573848032E-3</v>
       </c>
       <c r="I13">
-        <v>9.1908488846958493E-4</v>
+        <v>7.2636700422437205E-4</v>
       </c>
       <c r="J13">
-        <v>7.4690522880243963E-5</v>
+        <v>5.5680918313313205E-5</v>
       </c>
       <c r="K13">
-        <v>1.0601706424469939E-3</v>
+        <v>-1.6730764401593889E-4</v>
       </c>
       <c r="L13">
-        <v>3.2688443227641355E-4</v>
+        <v>-2.1404012486560264E-4</v>
       </c>
       <c r="M13">
-        <v>-7.4707731942032772E-4</v>
+        <v>-3.1613391964968542E-4</v>
       </c>
       <c r="N13">
-        <v>4.2563430290085205E-2</v>
+        <v>1.7411550674087419E-2</v>
       </c>
       <c r="O13">
-        <v>4.4683339396158709E-3</v>
+        <v>1.0116890577498762E-2</v>
       </c>
       <c r="P13">
-        <v>1.6275145995177286E-2</v>
+        <v>-2.5429406018125239E-2</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>23</v>
-      </c>
-      <c r="B14" s="4">
-        <v>-0.41593435651321148</v>
+        <v>22</v>
+      </c>
+      <c r="B14">
+        <v>0.13752423845873693</v>
       </c>
       <c r="C14">
-        <v>4.0401144563914117E-4</v>
+        <v>4.306351377614681E-4</v>
       </c>
       <c r="D14">
-        <v>2.7847462886532171E-5</v>
+        <v>-4.9643862402694305E-4</v>
       </c>
       <c r="E14">
-        <v>-9.9358884120270829E-7</v>
+        <v>1.3035253363248567E-5</v>
       </c>
       <c r="F14">
-        <v>-6.8895104880995622E-5</v>
+        <v>3.5513194682945323E-4</v>
       </c>
       <c r="G14">
-        <v>6.3286787272887491E-4</v>
+        <v>-1.4514723566559721E-4</v>
       </c>
       <c r="H14">
-        <v>3.1059247500814929E-3</v>
+        <v>3.0993625777899804E-4</v>
       </c>
       <c r="I14">
-        <v>6.5999672950090536E-4</v>
+        <v>3.2651295197115744E-5</v>
       </c>
       <c r="J14">
-        <v>-5.0335122456411294E-4</v>
+        <v>3.0365211206371352E-4</v>
       </c>
       <c r="K14">
-        <v>2.0385673508418194E-3</v>
+        <v>-3.0657001769863719E-4</v>
       </c>
       <c r="L14">
-        <v>1.795632266911477E-3</v>
+        <v>9.2661069274489749E-5</v>
       </c>
       <c r="M14">
-        <v>-8.3525857547424071E-4</v>
+        <v>-4.2409811982750049E-4</v>
       </c>
       <c r="N14">
-        <v>4.4683339396158709E-3</v>
+        <v>1.0116890577498762E-2</v>
       </c>
       <c r="O14">
-        <v>4.4355597936093172E-2</v>
+        <v>1.7437559923477355E-2</v>
       </c>
       <c r="P14">
-        <v>9.3334734430350012E-3</v>
+        <v>8.4979741133626111E-3</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>24</v>
-      </c>
-      <c r="B15" s="4">
-        <v>12.764979619392339</v>
+        <v>23</v>
+      </c>
+      <c r="B15">
+        <v>5.3650688333796213</v>
       </c>
       <c r="C15">
-        <v>-8.6062735248320175E-3</v>
+        <v>-1.7070095679316097E-2</v>
       </c>
       <c r="D15">
-        <v>-1.4116192330683661</v>
+        <v>-0.39400359802311691</v>
       </c>
       <c r="E15">
-        <v>3.3127252719317851E-2</v>
+        <v>8.9984676757957766E-3</v>
       </c>
       <c r="F15">
-        <v>-2.2807651744780142E-3</v>
+        <v>-7.5952720633431503E-3</v>
       </c>
       <c r="G15">
-        <v>-6.8883707396388914E-3</v>
+        <v>5.7841735178241691E-4</v>
       </c>
       <c r="H15">
-        <v>0.32304954040186973</v>
+        <v>6.3815705610682727E-2</v>
       </c>
       <c r="I15">
-        <v>-1.6257081916556806E-2</v>
+        <v>-1.0093389052505251E-2</v>
       </c>
       <c r="J15">
-        <v>1.8516219390862364E-2</v>
+        <v>-8.6803415317129456E-3</v>
       </c>
       <c r="K15">
-        <v>-3.7315949711386855E-3</v>
+        <v>-1.1022868369204436E-3</v>
       </c>
       <c r="L15">
-        <v>3.0758647960639689E-2</v>
+        <v>3.5004130210054482E-3</v>
       </c>
       <c r="M15">
-        <v>-5.0068612123493105E-3</v>
+        <v>-1.9355646229625486E-3</v>
       </c>
       <c r="N15">
-        <v>1.6275145995177286E-2</v>
+        <v>-2.5429406018125239E-2</v>
       </c>
       <c r="O15">
-        <v>9.3334734430350012E-3</v>
+        <v>8.4979741133626111E-3</v>
       </c>
       <c r="P15">
-        <v>14.904352184626887</v>
+        <v>4.3041789159285315</v>
       </c>
     </row>
   </sheetData>
@@ -1398,58 +1364,58 @@
   <sheetData>
     <row r="1" spans="1:26" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" t="s">
         <v>13</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>14</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>15</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>16</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I1" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" t="s">
+        <v>28</v>
+      </c>
+      <c r="K1" t="s">
+        <v>29</v>
+      </c>
+      <c r="L1" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1" t="s">
+        <v>31</v>
+      </c>
+      <c r="N1" t="s">
         <v>17</v>
       </c>
-      <c r="F1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G1" t="s">
-        <v>26</v>
-      </c>
-      <c r="H1" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" t="s">
-        <v>28</v>
-      </c>
-      <c r="J1" t="s">
-        <v>29</v>
-      </c>
-      <c r="K1" t="s">
-        <v>30</v>
-      </c>
-      <c r="L1" t="s">
-        <v>31</v>
-      </c>
-      <c r="M1" t="s">
+      <c r="O1" t="s">
+        <v>18</v>
+      </c>
+      <c r="P1" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q1" t="s">
         <v>32</v>
       </c>
-      <c r="N1" t="s">
-        <v>18</v>
-      </c>
-      <c r="O1" t="s">
-        <v>19</v>
-      </c>
-      <c r="P1" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>33</v>
-      </c>
-      <c r="R1" t="s">
-        <v>34</v>
       </c>
       <c r="S1" t="s">
         <v>35</v>
@@ -1464,1936 +1430,1936 @@
         <v>38</v>
       </c>
       <c r="W1" t="s">
+        <v>20</v>
+      </c>
+      <c r="X1" t="s">
         <v>21</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Y1" t="s">
         <v>22</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Z1" t="s">
         <v>23</v>
-      </c>
-      <c r="Z1" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2" s="4">
-        <v>-6.0311047926147936E-2</v>
+        <v>14</v>
+      </c>
+      <c r="B2">
+        <v>-3.0657707389751786E-2</v>
       </c>
       <c r="C2">
-        <v>1.3343070177331555E-3</v>
+        <v>4.5342279777112085E-4</v>
       </c>
       <c r="D2">
-        <v>1.2570491828734379E-5</v>
+        <v>4.7163787431326792E-6</v>
       </c>
       <c r="E2">
-        <v>-7.564428022270162E-8</v>
+        <v>-3.1149819369544808E-8</v>
       </c>
       <c r="F2">
-        <v>-3.2042047436069539E-4</v>
+        <v>-2.6109700253872212E-5</v>
       </c>
       <c r="G2">
-        <v>-3.2700163107205772E-4</v>
+        <v>-3.939842995071776E-5</v>
       </c>
       <c r="H2">
-        <v>-1.4602621609638067E-4</v>
+        <v>1.4609091762208219E-5</v>
       </c>
       <c r="I2">
-        <v>1.1539980195091426E-4</v>
+        <v>7.8122845579966935E-5</v>
       </c>
       <c r="J2">
-        <v>1.887448996251969E-5</v>
+        <v>-7.9115478582439389E-5</v>
       </c>
       <c r="K2">
-        <v>1.3590582542531791E-4</v>
+        <v>2.9820009923332686E-5</v>
       </c>
       <c r="L2">
-        <v>3.6241522555972974E-5</v>
+        <v>4.6929438273914845E-5</v>
       </c>
       <c r="M2">
-        <v>5.767836060510637E-4</v>
+        <v>1.9667008938907692E-4</v>
       </c>
       <c r="N2">
-        <v>2.8338898545950185E-5</v>
+        <v>-1.1288063187715515E-5</v>
       </c>
       <c r="O2">
-        <v>-1.6106877841293591E-5</v>
+        <v>-5.6422966327218777E-6</v>
       </c>
       <c r="P2">
-        <v>-6.1616736195303518E-6</v>
+        <v>-9.3537273746559663E-6</v>
       </c>
       <c r="Q2">
-        <v>-2.974110074611576E-5</v>
+        <v>-7.9105966988647611E-6</v>
       </c>
       <c r="R2">
-        <v>1.1317409883911767E-4</v>
+        <v>9.9113807268979255E-6</v>
       </c>
       <c r="S2">
-        <v>-3.1930597001795954E-5</v>
+        <v>-2.4760968515378431E-5</v>
       </c>
       <c r="T2">
-        <v>1.5787656139973656E-5</v>
+        <v>-2.0349882290950109E-5</v>
       </c>
       <c r="U2">
-        <v>-4.303234360877463E-5</v>
+        <v>1.930230554874688E-6</v>
       </c>
       <c r="V2">
-        <v>-4.03622165785195E-5</v>
+        <v>-5.3357055333429459E-6</v>
       </c>
       <c r="W2">
-        <v>-1.8489065971462965E-6</v>
+        <v>6.4241140035134486E-7</v>
       </c>
       <c r="X2">
-        <v>3.8758169007535272E-5</v>
+        <v>7.3211005194813629E-6</v>
       </c>
       <c r="Y2">
-        <v>1.8506060607368518E-5</v>
+        <v>6.0687961971312324E-6</v>
       </c>
       <c r="Z2">
-        <v>-7.3127166886379001E-4</v>
+        <v>-2.6750172737660915E-4</v>
       </c>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" s="4">
-        <v>-6.6407839768712652E-3</v>
+        <v>15</v>
+      </c>
+      <c r="B3">
+        <v>8.5801553521109132E-4</v>
       </c>
       <c r="C3">
-        <v>1.2570491828734379E-5</v>
+        <v>4.7163787431326792E-6</v>
       </c>
       <c r="D3">
-        <v>6.4945394696462656E-5</v>
+        <v>2.1598406981730183E-5</v>
       </c>
       <c r="E3">
-        <v>-6.400972096180439E-7</v>
+        <v>-2.0083580213353152E-7</v>
       </c>
       <c r="F3">
-        <v>-3.0026751803752011E-5</v>
+        <v>2.3958491663704937E-6</v>
       </c>
       <c r="G3">
-        <v>3.2085328801988947E-5</v>
+        <v>-3.5119559320735439E-6</v>
       </c>
       <c r="H3">
-        <v>2.3982663141522257E-4</v>
+        <v>8.1345273466333564E-5</v>
       </c>
       <c r="I3">
-        <v>2.824905813684158E-5</v>
+        <v>-3.5052675440831144E-6</v>
       </c>
       <c r="J3">
-        <v>1.2900836432948041E-4</v>
+        <v>1.6460168904879119E-5</v>
       </c>
       <c r="K3">
-        <v>4.8081521995091279E-5</v>
+        <v>3.3325472488515283E-6</v>
       </c>
       <c r="L3">
-        <v>1.4151240801527263E-4</v>
+        <v>3.5656654246877152E-5</v>
       </c>
       <c r="M3">
-        <v>3.3295278434521559E-6</v>
+        <v>1.4527837837640295E-5</v>
       </c>
       <c r="N3">
-        <v>2.0583332736663366E-5</v>
+        <v>2.2586019995947908E-7</v>
       </c>
       <c r="O3">
-        <v>4.7850681222955064E-6</v>
+        <v>-1.6360224643778689E-6</v>
       </c>
       <c r="P3">
-        <v>1.7990167347663785E-5</v>
+        <v>-7.2866488159888207E-6</v>
       </c>
       <c r="Q3">
-        <v>-1.0838488077256601E-5</v>
+        <v>-3.562346585378855E-6</v>
       </c>
       <c r="R3">
-        <v>-4.3551902623353085E-5</v>
+        <v>-6.5427626084489708E-6</v>
       </c>
       <c r="S3">
-        <v>1.9280583675494105E-5</v>
+        <v>-2.7724845509853414E-6</v>
       </c>
       <c r="T3">
-        <v>1.2070308675688482E-5</v>
+        <v>-1.4194491696989541E-6</v>
       </c>
       <c r="U3">
-        <v>9.1289300966917878E-6</v>
+        <v>1.4540266569357089E-6</v>
       </c>
       <c r="V3">
-        <v>1.5433213691023887E-5</v>
+        <v>-1.5238299107893068E-6</v>
       </c>
       <c r="W3">
-        <v>-3.3377470949820688E-6</v>
+        <v>-4.8675910751175543E-7</v>
       </c>
       <c r="X3">
-        <v>4.7456284863945449E-5</v>
+        <v>-2.9953078859712694E-6</v>
       </c>
       <c r="Y3">
-        <v>1.7790854707234191E-5</v>
+        <v>4.4958746874400215E-8</v>
       </c>
       <c r="Z3">
-        <v>-1.5703476312509779E-3</v>
+        <v>-5.1291744315841382E-4</v>
       </c>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B4" s="4">
-        <v>1.756968971653699E-5</v>
+        <v>16</v>
+      </c>
+      <c r="B4">
+        <v>7.4741626079639759E-5</v>
       </c>
       <c r="C4">
-        <v>-7.564428022270162E-8</v>
+        <v>-3.1149819369544808E-8</v>
       </c>
       <c r="D4">
-        <v>-6.400972096180439E-7</v>
+        <v>-2.0083580213353152E-7</v>
       </c>
       <c r="E4">
-        <v>6.6066756638699412E-9</v>
+        <v>1.9561962347074885E-9</v>
       </c>
       <c r="F4">
-        <v>2.6422719286221168E-7</v>
+        <v>-1.7821038950672977E-8</v>
       </c>
       <c r="G4">
-        <v>-5.0903460306619199E-7</v>
+        <v>-1.6574756159539386E-8</v>
       </c>
       <c r="H4">
-        <v>-1.9895927450758859E-6</v>
+        <v>-6.0525187298704269E-7</v>
       </c>
       <c r="I4">
-        <v>-3.040476631851745E-7</v>
+        <v>2.5087783129221573E-8</v>
       </c>
       <c r="J4">
-        <v>-1.8824850879085174E-6</v>
+        <v>-3.1151430558223389E-7</v>
       </c>
       <c r="K4">
-        <v>-1.8396240802711042E-7</v>
+        <v>3.4841219568333261E-8</v>
       </c>
       <c r="L4">
-        <v>-1.2642399934480773E-6</v>
+        <v>-2.9865803768461393E-7</v>
       </c>
       <c r="M4">
-        <v>2.2305133179276629E-7</v>
+        <v>-5.3429518114519352E-8</v>
       </c>
       <c r="N4">
-        <v>-7.1265447348865531E-8</v>
+        <v>2.5757752110308993E-8</v>
       </c>
       <c r="O4">
-        <v>-3.7662758621914361E-8</v>
+        <v>1.9179329431223549E-8</v>
       </c>
       <c r="P4">
-        <v>-2.3914809880062036E-7</v>
+        <v>2.2592922394968238E-8</v>
       </c>
       <c r="Q4">
-        <v>9.5820471223792519E-8</v>
+        <v>3.5552566295484652E-8</v>
       </c>
       <c r="R4">
-        <v>3.8938360788607817E-7</v>
+        <v>4.1936601399230843E-8</v>
       </c>
       <c r="S4">
-        <v>-1.8016041331657672E-7</v>
+        <v>3.2226335729336566E-8</v>
       </c>
       <c r="T4">
-        <v>-1.7012423833868518E-7</v>
+        <v>2.199054723841206E-8</v>
       </c>
       <c r="U4">
-        <v>-1.1490490676355463E-7</v>
+        <v>-7.7228336994951326E-9</v>
       </c>
       <c r="V4">
-        <v>-1.7527874688059326E-7</v>
+        <v>1.6931698647129571E-8</v>
       </c>
       <c r="W4">
-        <v>3.0340105741843263E-8</v>
+        <v>-1.2233309193638598E-9</v>
       </c>
       <c r="X4">
-        <v>-4.3748824523357364E-7</v>
+        <v>2.8424050159782826E-8</v>
       </c>
       <c r="Y4">
-        <v>-1.9351885592057598E-7</v>
+        <v>1.6509860258172627E-8</v>
       </c>
       <c r="Z4">
-        <v>1.4296387363460427E-5</v>
+        <v>4.4794366207618664E-6</v>
       </c>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>25</v>
-      </c>
-      <c r="B5" s="4">
-        <v>-0.11099651758769653</v>
+        <v>24</v>
+      </c>
+      <c r="B5">
+        <v>-0.34433117434504201</v>
       </c>
       <c r="C5">
-        <v>-3.2042047436069539E-4</v>
+        <v>-2.6109700253872212E-5</v>
       </c>
       <c r="D5">
-        <v>-3.0026751803752011E-5</v>
+        <v>2.3958491663704937E-6</v>
       </c>
       <c r="E5">
-        <v>2.6422719286221168E-7</v>
+        <v>-1.7821038950672977E-8</v>
       </c>
       <c r="F5">
-        <v>2.0524077273745564E-3</v>
+        <v>1.0437818238875126E-3</v>
       </c>
       <c r="G5">
-        <v>1.7323414894727946E-3</v>
+        <v>8.1120921368390793E-4</v>
       </c>
       <c r="H5">
-        <v>1.0062460226827364E-5</v>
+        <v>5.1435339700839952E-5</v>
       </c>
       <c r="I5">
-        <v>-1.2765492198652916E-4</v>
+        <v>-3.5319349447362714E-5</v>
       </c>
       <c r="J5">
-        <v>1.0183353506414827E-4</v>
+        <v>-1.1777852052196017E-5</v>
       </c>
       <c r="K5">
-        <v>2.1040434921762853E-4</v>
+        <v>5.2822750145486313E-5</v>
       </c>
       <c r="L5">
-        <v>1.2962097761670769E-4</v>
+        <v>3.7273946456482469E-5</v>
       </c>
       <c r="M5">
-        <v>2.6872124933042803E-5</v>
+        <v>3.4492006967320168E-5</v>
       </c>
       <c r="N5">
-        <v>1.7924379537528074E-5</v>
+        <v>2.8797280961390582E-6</v>
       </c>
       <c r="O5">
-        <v>-3.7507574787564714E-6</v>
+        <v>3.6962994519418209E-6</v>
       </c>
       <c r="P5">
-        <v>4.5893494467773993E-5</v>
+        <v>1.2124547755947625E-4</v>
       </c>
       <c r="Q5">
-        <v>6.6773799459460647E-5</v>
+        <v>3.9416742180503504E-6</v>
       </c>
       <c r="R5">
-        <v>5.1875941152168515E-5</v>
+        <v>3.2747887556468198E-5</v>
       </c>
       <c r="S5">
-        <v>-8.9427230875303138E-5</v>
+        <v>1.8538703766488876E-5</v>
       </c>
       <c r="T5">
-        <v>-1.4944370075172048E-4</v>
+        <v>1.7307204965050522E-5</v>
       </c>
       <c r="U5">
-        <v>1.225885141637839E-5</v>
+        <v>-1.437643463629817E-5</v>
       </c>
       <c r="V5">
-        <v>3.492604323026313E-6</v>
+        <v>-3.4271122623108496E-6</v>
       </c>
       <c r="W5">
-        <v>1.7220990881987147E-5</v>
+        <v>5.2239805422033144E-6</v>
       </c>
       <c r="X5">
-        <v>-1.2103884618969542E-4</v>
+        <v>5.4441691505076307E-6</v>
       </c>
       <c r="Y5">
-        <v>-1.0175761089266844E-4</v>
+        <v>-7.8852760226817448E-6</v>
       </c>
       <c r="Z5">
-        <v>-1.2966174938875807E-3</v>
+        <v>-1.0201047048666947E-3</v>
       </c>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>26</v>
-      </c>
-      <c r="B6" s="4">
-        <v>-1.1153490839974377E-2</v>
+        <v>25</v>
+      </c>
+      <c r="B6">
+        <v>-0.76070386310867522</v>
       </c>
       <c r="C6">
-        <v>-3.2700163107205772E-4</v>
+        <v>-3.939842995071776E-5</v>
       </c>
       <c r="D6">
-        <v>3.2085328801988947E-5</v>
+        <v>-3.5119559320735439E-6</v>
       </c>
       <c r="E6">
-        <v>-5.0903460306619199E-7</v>
+        <v>-1.6574756159539386E-8</v>
       </c>
       <c r="F6">
-        <v>1.7323414894727946E-3</v>
+        <v>8.1120921368390793E-4</v>
       </c>
       <c r="G6">
-        <v>3.8477276011083766E-3</v>
+        <v>1.1652983457035625E-3</v>
       </c>
       <c r="H6">
-        <v>-7.7853982558026926E-6</v>
+        <v>6.617917094168277E-5</v>
       </c>
       <c r="I6">
-        <v>-8.6965930811555456E-5</v>
+        <v>-3.4666916789438741E-5</v>
       </c>
       <c r="J6">
-        <v>3.8119956888355401E-4</v>
+        <v>4.2797264586790347E-5</v>
       </c>
       <c r="K6">
-        <v>8.7360787852286534E-5</v>
+        <v>5.5896402061482735E-5</v>
       </c>
       <c r="L6">
-        <v>-5.260542536790247E-5</v>
+        <v>4.2508433973970421E-5</v>
       </c>
       <c r="M6">
-        <v>2.3828626514347823E-5</v>
+        <v>5.9053499909431984E-5</v>
       </c>
       <c r="N6">
-        <v>1.3107041374988757E-4</v>
+        <v>2.5214192856986362E-5</v>
       </c>
       <c r="O6">
-        <v>1.5242450349293475E-5</v>
+        <v>9.9134665784640035E-6</v>
       </c>
       <c r="P6">
-        <v>3.5326185515899017E-4</v>
+        <v>3.0212510917043136E-4</v>
       </c>
       <c r="Q6">
-        <v>7.599701265936589E-5</v>
+        <v>9.9456229460841791E-6</v>
       </c>
       <c r="R6">
-        <v>8.2620771070478346E-5</v>
+        <v>9.9605645950698915E-5</v>
       </c>
       <c r="S6">
-        <v>-2.5749285919079404E-4</v>
+        <v>-1.0242658971515465E-5</v>
       </c>
       <c r="T6">
-        <v>-9.0989792033858833E-5</v>
+        <v>-8.3988302436985892E-6</v>
       </c>
       <c r="U6">
-        <v>-8.3710056878112974E-5</v>
+        <v>-3.333255961533103E-5</v>
       </c>
       <c r="V6">
-        <v>-1.2486684619019382E-4</v>
+        <v>-1.2428230972393267E-5</v>
       </c>
       <c r="W6">
-        <v>2.0251400453035254E-5</v>
+        <v>1.198603318790024E-5</v>
       </c>
       <c r="X6">
-        <v>-4.2580763047944019E-5</v>
+        <v>-1.4523466102543182E-6</v>
       </c>
       <c r="Y6">
-        <v>2.5806581809090234E-5</v>
+        <v>-1.9324393009367298E-5</v>
       </c>
       <c r="Z6">
-        <v>-2.9021676809827097E-3</v>
+        <v>-1.0606612310304104E-3</v>
       </c>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>27</v>
-      </c>
-      <c r="B7" s="4">
-        <v>0.56985303287543332</v>
+        <v>26</v>
+      </c>
+      <c r="B7">
+        <v>0.4204737835311993</v>
       </c>
       <c r="C7">
-        <v>-1.4602621609638067E-4</v>
+        <v>1.4609091762208219E-5</v>
       </c>
       <c r="D7">
-        <v>2.3982663141522257E-4</v>
+        <v>8.1345273466333564E-5</v>
       </c>
       <c r="E7">
-        <v>-1.9895927450758859E-6</v>
+        <v>-6.0525187298704269E-7</v>
       </c>
       <c r="F7">
-        <v>1.0062460226827364E-5</v>
+        <v>5.1435339700839952E-5</v>
       </c>
       <c r="G7">
-        <v>-7.7853982558026926E-6</v>
+        <v>6.617917094168277E-5</v>
       </c>
       <c r="H7">
-        <v>1.4170261905547772E-2</v>
+        <v>5.1631448970055425E-3</v>
       </c>
       <c r="I7">
-        <v>2.6139754447995086E-3</v>
+        <v>7.783845584002629E-4</v>
       </c>
       <c r="J7">
-        <v>2.4428434018274455E-3</v>
+        <v>6.7997067697083595E-4</v>
       </c>
       <c r="K7">
-        <v>7.7478156417348613E-4</v>
+        <v>1.9290301091471446E-4</v>
       </c>
       <c r="L7">
-        <v>1.8542320371499593E-5</v>
+        <v>2.0912506006810792E-5</v>
       </c>
       <c r="M7">
-        <v>4.7998057282696259E-4</v>
+        <v>2.9414484745343906E-4</v>
       </c>
       <c r="N7">
-        <v>-3.0518826448337332E-5</v>
+        <v>7.6955121308407734E-6</v>
       </c>
       <c r="O7">
-        <v>3.5933627439942167E-4</v>
+        <v>7.7692966621244094E-5</v>
       </c>
       <c r="P7">
-        <v>3.5269211232810682E-4</v>
+        <v>1.3157415212642991E-5</v>
       </c>
       <c r="Q7">
-        <v>3.5848321969282154E-6</v>
+        <v>2.2619823318768655E-5</v>
       </c>
       <c r="R7">
-        <v>-2.1835425973305757E-4</v>
+        <v>3.9129726335896536E-5</v>
       </c>
       <c r="S7">
-        <v>2.0584464399172817E-4</v>
+        <v>-1.5642980307411727E-5</v>
       </c>
       <c r="T7">
-        <v>-4.8157230896755986E-5</v>
+        <v>3.4430845437848968E-6</v>
       </c>
       <c r="U7">
-        <v>1.2341537077314611E-4</v>
+        <v>3.426924458995481E-5</v>
       </c>
       <c r="V7">
-        <v>2.7585135416178792E-4</v>
+        <v>4.6894016633811531E-6</v>
       </c>
       <c r="W7">
-        <v>-2.5757842459753981E-5</v>
+        <v>-3.2590277028666701E-6</v>
       </c>
       <c r="X7">
-        <v>5.2895724822177607E-4</v>
+        <v>-6.9115614778209261E-5</v>
       </c>
       <c r="Y7">
-        <v>-1.0039890202066457E-4</v>
+        <v>-9.2507556571743473E-6</v>
       </c>
       <c r="Z7">
-        <v>-9.1895501848544611E-3</v>
+        <v>-3.4918434793624773E-3</v>
       </c>
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>28</v>
-      </c>
-      <c r="B8" s="4">
-        <v>0.31216810932719424</v>
+        <v>27</v>
+      </c>
+      <c r="B8">
+        <v>-0.10605488316427726</v>
       </c>
       <c r="C8">
-        <v>1.1539980195091426E-4</v>
+        <v>7.8122845579966935E-5</v>
       </c>
       <c r="D8">
-        <v>2.824905813684158E-5</v>
+        <v>-3.5052675440831144E-6</v>
       </c>
       <c r="E8">
-        <v>-3.040476631851745E-7</v>
+        <v>2.5087783129221573E-8</v>
       </c>
       <c r="F8">
-        <v>-1.2765492198652916E-4</v>
+        <v>-3.5319349447362714E-5</v>
       </c>
       <c r="G8">
-        <v>-8.6965930811555456E-5</v>
+        <v>-3.4666916789438741E-5</v>
       </c>
       <c r="H8">
-        <v>2.6139754447995086E-3</v>
+        <v>7.783845584002629E-4</v>
       </c>
       <c r="I8">
-        <v>3.5723353331107003E-3</v>
+        <v>1.2204271694354525E-3</v>
       </c>
       <c r="J8">
-        <v>2.8484065459553772E-3</v>
+        <v>9.403108338159234E-4</v>
       </c>
       <c r="K8">
-        <v>2.6343104554747525E-7</v>
+        <v>3.5746240090737974E-5</v>
       </c>
       <c r="L8">
-        <v>-4.9888088172475283E-5</v>
+        <v>2.6942821806874444E-5</v>
       </c>
       <c r="M8">
-        <v>1.9537938671737934E-4</v>
+        <v>1.4700267585633287E-4</v>
       </c>
       <c r="N8">
-        <v>1.6431240731438554E-4</v>
+        <v>1.4321903528313298E-5</v>
       </c>
       <c r="O8">
-        <v>3.1452716917271728E-4</v>
+        <v>7.4384529647562243E-5</v>
       </c>
       <c r="P8">
-        <v>-1.6091380724919148E-4</v>
+        <v>6.9461158303949855E-5</v>
       </c>
       <c r="Q8">
-        <v>2.8127441826961109E-6</v>
+        <v>2.4042621231590747E-5</v>
       </c>
       <c r="R8">
-        <v>-1.8320079918309872E-5</v>
+        <v>8.0721235577946787E-5</v>
       </c>
       <c r="S8">
-        <v>1.4138133922669848E-4</v>
+        <v>-3.216752376598364E-5</v>
       </c>
       <c r="T8">
-        <v>3.8490274803550052E-5</v>
+        <v>-4.5569162773807654E-5</v>
       </c>
       <c r="U8">
-        <v>9.6289252865628446E-5</v>
+        <v>1.2178248447282174E-5</v>
       </c>
       <c r="V8">
-        <v>1.3900598378666258E-4</v>
+        <v>-6.0959269094791992E-6</v>
       </c>
       <c r="W8">
-        <v>-7.5662564888910545E-6</v>
+        <v>8.8441793355109447E-6</v>
       </c>
       <c r="X8">
-        <v>2.2587214035028392E-4</v>
+        <v>-1.888943224783563E-6</v>
       </c>
       <c r="Y8">
-        <v>-1.0579345123202947E-5</v>
+        <v>-5.5732285670051214E-5</v>
       </c>
       <c r="Z8">
-        <v>-3.8211822754501551E-3</v>
+        <v>-1.117218974136736E-3</v>
       </c>
     </row>
     <row r="9" spans="1:26" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>29</v>
-      </c>
-      <c r="B9" s="4">
-        <v>2.9366873380837444E-4</v>
+        <v>28</v>
+      </c>
+      <c r="B9">
+        <v>0.10968939957665261</v>
       </c>
       <c r="C9">
-        <v>1.887448996251969E-5</v>
+        <v>-7.9115478582439389E-5</v>
       </c>
       <c r="D9">
-        <v>1.2900836432948041E-4</v>
+        <v>1.6460168904879119E-5</v>
       </c>
       <c r="E9">
-        <v>-1.8824850879085174E-6</v>
+        <v>-3.1151430558223389E-7</v>
       </c>
       <c r="F9">
-        <v>1.0183353506414827E-4</v>
+        <v>-1.1777852052196017E-5</v>
       </c>
       <c r="G9">
-        <v>3.8119956888355401E-4</v>
+        <v>4.2797264586790347E-5</v>
       </c>
       <c r="H9">
-        <v>2.4428434018274455E-3</v>
+        <v>6.7997067697083595E-4</v>
       </c>
       <c r="I9">
-        <v>2.8484065459553772E-3</v>
+        <v>9.403108338159234E-4</v>
       </c>
       <c r="J9">
-        <v>6.1399011340624978E-3</v>
+        <v>1.739180246286323E-3</v>
       </c>
       <c r="K9">
-        <v>-6.5415241314201135E-6</v>
+        <v>6.8357298159902268E-5</v>
       </c>
       <c r="L9">
-        <v>1.4995769916045342E-4</v>
+        <v>4.3624119611568738E-5</v>
       </c>
       <c r="M9">
-        <v>2.3451643719028695E-4</v>
+        <v>8.0759724715267619E-5</v>
       </c>
       <c r="N9">
-        <v>7.4764605206404581E-5</v>
+        <v>2.6262958782437518E-6</v>
       </c>
       <c r="O9">
-        <v>3.1898232102219308E-4</v>
+        <v>7.7429648024753562E-5</v>
       </c>
       <c r="P9">
-        <v>-1.3256968413288654E-4</v>
+        <v>7.5609536548485465E-6</v>
       </c>
       <c r="Q9">
-        <v>4.4338415922231214E-5</v>
+        <v>2.7664803361350155E-5</v>
       </c>
       <c r="R9">
-        <v>1.3519401382955116E-5</v>
+        <v>6.5730285269400938E-5</v>
       </c>
       <c r="S9">
-        <v>8.2205096612161539E-5</v>
+        <v>3.8751328748586658E-5</v>
       </c>
       <c r="T9">
-        <v>3.8445495437119731E-5</v>
+        <v>4.2449390250190466E-5</v>
       </c>
       <c r="U9">
-        <v>1.3896181743156119E-4</v>
+        <v>2.2637990413158218E-6</v>
       </c>
       <c r="V9">
-        <v>5.9705543709869403E-5</v>
+        <v>1.030997400570618E-5</v>
       </c>
       <c r="W9">
-        <v>-2.0500938939573997E-5</v>
+        <v>1.0397140634715532E-5</v>
       </c>
       <c r="X9">
-        <v>1.4146172198566641E-4</v>
+        <v>-2.095688771491821E-5</v>
       </c>
       <c r="Y9">
-        <v>-2.3070630088995337E-5</v>
+        <v>-6.8064820096482264E-5</v>
       </c>
       <c r="Z9">
-        <v>-4.9137828341010818E-3</v>
+        <v>-1.2854775460974575E-3</v>
       </c>
     </row>
     <row r="10" spans="1:26" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>30</v>
-      </c>
-      <c r="B10" s="4">
-        <v>0.24492975476427298</v>
+        <v>29</v>
+      </c>
+      <c r="B10">
+        <v>-0.27313852937476568</v>
       </c>
       <c r="C10">
-        <v>1.3590582542531791E-4</v>
+        <v>2.9820009923332686E-5</v>
       </c>
       <c r="D10">
-        <v>4.8081521995091279E-5</v>
+        <v>3.3325472488515283E-6</v>
       </c>
       <c r="E10">
-        <v>-1.8396240802711042E-7</v>
+        <v>3.4841219568333261E-8</v>
       </c>
       <c r="F10">
-        <v>2.1040434921762853E-4</v>
+        <v>5.2822750145486313E-5</v>
       </c>
       <c r="G10">
-        <v>8.7360787852286534E-5</v>
+        <v>5.5896402061482735E-5</v>
       </c>
       <c r="H10">
-        <v>7.7478156417348613E-4</v>
+        <v>1.9290301091471446E-4</v>
       </c>
       <c r="I10">
-        <v>2.6343104554747525E-7</v>
+        <v>3.5746240090737974E-5</v>
       </c>
       <c r="J10">
-        <v>-6.5415241314201135E-6</v>
+        <v>6.8357298159902268E-5</v>
       </c>
       <c r="K10">
-        <v>2.558653816506828E-3</v>
+        <v>9.4040668950626878E-4</v>
       </c>
       <c r="L10">
-        <v>1.1315204574886295E-3</v>
+        <v>2.9772070142855447E-4</v>
       </c>
       <c r="M10">
-        <v>1.4444696640919033E-3</v>
+        <v>4.4465297248217272E-4</v>
       </c>
       <c r="N10">
-        <v>-7.9968446126236922E-6</v>
+        <v>4.7654815957605202E-6</v>
       </c>
       <c r="O10">
-        <v>9.4470998932977872E-6</v>
+        <v>-6.1521050240706776E-7</v>
       </c>
       <c r="P10">
-        <v>-2.7221906913465956E-4</v>
+        <v>4.5359652573374404E-5</v>
       </c>
       <c r="Q10">
-        <v>-3.7153096475986611E-5</v>
+        <v>-3.7917966161784464E-6</v>
       </c>
       <c r="R10">
-        <v>9.8458759243898056E-5</v>
+        <v>3.3716772293056045E-5</v>
       </c>
       <c r="S10">
-        <v>6.4229959810783869E-5</v>
+        <v>9.2243470161533517E-7</v>
       </c>
       <c r="T10">
-        <v>-1.6859652177268303E-4</v>
+        <v>8.1086051981943451E-6</v>
       </c>
       <c r="U10">
-        <v>-1.089832686853795E-5</v>
+        <v>-2.7569900902447498E-5</v>
       </c>
       <c r="V10">
-        <v>-4.5036032423920679E-6</v>
+        <v>-6.8501801556726917E-6</v>
       </c>
       <c r="W10">
-        <v>-7.8548086608421695E-6</v>
+        <v>2.0660026916604154E-6</v>
       </c>
       <c r="X10">
-        <v>1.9946283460452836E-4</v>
+        <v>2.6783808046612482E-5</v>
       </c>
       <c r="Y10">
-        <v>2.9082759658217126E-5</v>
+        <v>3.5392038102567599E-5</v>
       </c>
       <c r="Z10">
-        <v>-2.9915155472920204E-3</v>
+        <v>-7.4348718491287497E-4</v>
       </c>
     </row>
     <row r="11" spans="1:26" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>31</v>
-      </c>
-      <c r="B11" s="4">
-        <v>1.759073037574994E-2</v>
+        <v>30</v>
+      </c>
+      <c r="B11">
+        <v>-0.37101516875764901</v>
       </c>
       <c r="C11">
-        <v>3.6241522555972974E-5</v>
+        <v>4.6929438273914845E-5</v>
       </c>
       <c r="D11">
-        <v>1.4151240801527263E-4</v>
+        <v>3.5656654246877152E-5</v>
       </c>
       <c r="E11">
-        <v>-1.2642399934480773E-6</v>
+        <v>-2.9865803768461393E-7</v>
       </c>
       <c r="F11">
-        <v>1.2962097761670769E-4</v>
+        <v>3.7273946456482469E-5</v>
       </c>
       <c r="G11">
-        <v>-5.260542536790247E-5</v>
+        <v>4.2508433973970421E-5</v>
       </c>
       <c r="H11">
-        <v>1.8542320371499593E-5</v>
+        <v>2.0912506006810792E-5</v>
       </c>
       <c r="I11">
-        <v>-4.9888088172475283E-5</v>
+        <v>2.6942821806874444E-5</v>
       </c>
       <c r="J11">
-        <v>1.4995769916045342E-4</v>
+        <v>4.3624119611568738E-5</v>
       </c>
       <c r="K11">
-        <v>1.1315204574886295E-3</v>
+        <v>2.9772070142855447E-4</v>
       </c>
       <c r="L11">
-        <v>2.195019759054802E-3</v>
+        <v>5.8502613089024861E-4</v>
       </c>
       <c r="M11">
-        <v>1.0205180816306022E-3</v>
+        <v>3.4087231351431768E-4</v>
       </c>
       <c r="N11">
-        <v>4.2994522351615252E-5</v>
+        <v>8.8699150272470363E-6</v>
       </c>
       <c r="O11">
-        <v>8.8620550228148473E-6</v>
+        <v>-1.4319515040121239E-6</v>
       </c>
       <c r="P11">
-        <v>-3.5757492036081126E-4</v>
+        <v>9.4497646402913482E-5</v>
       </c>
       <c r="Q11">
-        <v>2.4279502873301989E-6</v>
+        <v>-3.036308746923627E-6</v>
       </c>
       <c r="R11">
-        <v>-3.4883103597178411E-4</v>
+        <v>-1.0620491329578697E-5</v>
       </c>
       <c r="S11">
-        <v>1.3503534828820723E-4</v>
+        <v>-1.8347087561049861E-6</v>
       </c>
       <c r="T11">
-        <v>-1.0882491131549408E-4</v>
+        <v>1.4944553644565006E-5</v>
       </c>
       <c r="U11">
-        <v>-9.2163317404511235E-6</v>
+        <v>5.1801573562477434E-6</v>
       </c>
       <c r="V11">
-        <v>1.7176405853380565E-5</v>
+        <v>-3.7738828733000678E-6</v>
       </c>
       <c r="W11">
-        <v>-3.0300902384266246E-6</v>
+        <v>-4.7276878218005709E-6</v>
       </c>
       <c r="X11">
-        <v>1.2214719370816124E-4</v>
+        <v>1.1827356287629452E-5</v>
       </c>
       <c r="Y11">
-        <v>3.7959409527624222E-5</v>
+        <v>1.3316517232298447E-5</v>
       </c>
       <c r="Z11">
-        <v>-4.8929371409059917E-3</v>
+        <v>-1.282965961914256E-3</v>
       </c>
     </row>
     <row r="12" spans="1:26" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>32</v>
-      </c>
-      <c r="B12" s="4">
-        <v>1.4612497094042312</v>
+        <v>31</v>
+      </c>
+      <c r="B12">
+        <v>-0.88839977863824615</v>
       </c>
       <c r="C12">
-        <v>5.767836060510637E-4</v>
+        <v>1.9667008938907692E-4</v>
       </c>
       <c r="D12">
-        <v>3.3295278434521559E-6</v>
+        <v>1.4527837837640295E-5</v>
       </c>
       <c r="E12">
-        <v>2.2305133179276629E-7</v>
+        <v>-5.3429518114519352E-8</v>
       </c>
       <c r="F12">
-        <v>2.6872124933042803E-5</v>
+        <v>3.4492006967320168E-5</v>
       </c>
       <c r="G12">
-        <v>2.3828626514347823E-5</v>
+        <v>5.9053499909431984E-5</v>
       </c>
       <c r="H12">
-        <v>4.7998057282696259E-4</v>
+        <v>2.9414484745343906E-4</v>
       </c>
       <c r="I12">
-        <v>1.9537938671737934E-4</v>
+        <v>1.4700267585633287E-4</v>
       </c>
       <c r="J12">
-        <v>2.3451643719028695E-4</v>
+        <v>8.0759724715267619E-5</v>
       </c>
       <c r="K12">
-        <v>1.4444696640919033E-3</v>
+        <v>4.4465297248217272E-4</v>
       </c>
       <c r="L12">
-        <v>1.0205180816306022E-3</v>
+        <v>3.4087231351431768E-4</v>
       </c>
       <c r="M12">
-        <v>1.2382466905696497E-2</v>
+        <v>6.9705051825409477E-3</v>
       </c>
       <c r="N12">
-        <v>6.9586036812538973E-5</v>
+        <v>1.7318849403136683E-5</v>
       </c>
       <c r="O12">
-        <v>-1.1627332219492377E-5</v>
+        <v>2.261562895939198E-7</v>
       </c>
       <c r="P12">
-        <v>-1.494286632164147E-3</v>
+        <v>1.5246466342378165E-4</v>
       </c>
       <c r="Q12">
-        <v>2.3954078196485482E-7</v>
+        <v>-6.4523032225885779E-6</v>
       </c>
       <c r="R12">
-        <v>-4.0761168211876967E-4</v>
+        <v>-6.3389826700670308E-5</v>
       </c>
       <c r="S12">
-        <v>-3.3336865053150227E-5</v>
+        <v>-1.3580742055550174E-5</v>
       </c>
       <c r="T12">
-        <v>-2.7870820580016306E-5</v>
+        <v>5.866075390490271E-5</v>
       </c>
       <c r="U12">
-        <v>-3.9616323218604897E-5</v>
+        <v>2.13351099667649E-5</v>
       </c>
       <c r="V12">
-        <v>-1.7736314328391901E-4</v>
+        <v>9.0980437235087274E-6</v>
       </c>
       <c r="W12">
-        <v>3.0628907788204219E-6</v>
+        <v>-9.82249850680291E-6</v>
       </c>
       <c r="X12">
-        <v>-4.5002205489233456E-4</v>
+        <v>-1.1972997822525574E-5</v>
       </c>
       <c r="Y12">
-        <v>-2.5629639932315434E-4</v>
+        <v>4.8764172564989448E-5</v>
       </c>
       <c r="Z12">
-        <v>-2.3289291197963963E-3</v>
+        <v>-1.0357465045762325E-3</v>
       </c>
     </row>
     <row r="13" spans="1:26" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>18</v>
-      </c>
-      <c r="B13" s="4">
-        <v>-3.462219818086322E-2</v>
+        <v>17</v>
+      </c>
+      <c r="B13">
+        <v>9.4976073226262309E-2</v>
       </c>
       <c r="C13">
-        <v>2.8338898545950185E-5</v>
+        <v>-1.1288063187715515E-5</v>
       </c>
       <c r="D13">
-        <v>2.0583332736663366E-5</v>
+        <v>2.2586019995947908E-7</v>
       </c>
       <c r="E13">
-        <v>-7.1265447348865531E-8</v>
+        <v>2.5757752110308993E-8</v>
       </c>
       <c r="F13">
-        <v>1.7924379537528074E-5</v>
+        <v>2.8797280961390582E-6</v>
       </c>
       <c r="G13">
-        <v>1.3107041374988757E-4</v>
+        <v>2.5214192856986362E-5</v>
       </c>
       <c r="H13">
-        <v>-3.0518826448337332E-5</v>
+        <v>7.6955121308407734E-6</v>
       </c>
       <c r="I13">
-        <v>1.6431240731438554E-4</v>
+        <v>1.4321903528313298E-5</v>
       </c>
       <c r="J13">
-        <v>7.4764605206404581E-5</v>
+        <v>2.6262958782437518E-6</v>
       </c>
       <c r="K13">
-        <v>-7.9968446126236922E-6</v>
+        <v>4.7654815957605202E-6</v>
       </c>
       <c r="L13">
-        <v>4.2994522351615252E-5</v>
+        <v>8.8699150272470363E-6</v>
       </c>
       <c r="M13">
-        <v>6.9586036812538973E-5</v>
+        <v>1.7318849403136683E-5</v>
       </c>
       <c r="N13">
-        <v>4.9592489206346825E-4</v>
+        <v>1.192345687109374E-4</v>
       </c>
       <c r="O13">
-        <v>-2.6246099474191212E-6</v>
+        <v>5.6114523690611667E-7</v>
       </c>
       <c r="P13">
-        <v>5.8118703391004528E-5</v>
+        <v>-1.7564294960533886E-5</v>
       </c>
       <c r="Q13">
-        <v>-9.9559191873397179E-6</v>
+        <v>-4.5518787523706891E-7</v>
       </c>
       <c r="R13">
-        <v>-2.4799050599614821E-5</v>
+        <v>2.2886214958567613E-7</v>
       </c>
       <c r="S13">
-        <v>3.0391854924508087E-5</v>
+        <v>6.4915830477918469E-6</v>
       </c>
       <c r="T13">
-        <v>4.3886044009500613E-5</v>
+        <v>1.4722583875249919E-5</v>
       </c>
       <c r="U13">
-        <v>8.9992017319033037E-6</v>
+        <v>1.2190679436379693E-6</v>
       </c>
       <c r="V13">
-        <v>-6.3358881642926537E-6</v>
+        <v>7.0919145752898266E-6</v>
       </c>
       <c r="W13">
-        <v>-7.4402925825339214E-6</v>
+        <v>-4.0619398426883213E-6</v>
       </c>
       <c r="X13">
-        <v>5.7388108143108197E-5</v>
+        <v>8.7700092162105439E-6</v>
       </c>
       <c r="Y13">
-        <v>-1.010376771855173E-5</v>
+        <v>3.8228483101774771E-5</v>
       </c>
       <c r="Z13">
-        <v>-2.545142494712441E-3</v>
+        <v>-4.8722965387099819E-4</v>
       </c>
     </row>
     <row r="14" spans="1:26" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>19</v>
-      </c>
-      <c r="B14" s="4">
-        <v>2.2527491693505666E-2</v>
+        <v>18</v>
+      </c>
+      <c r="B14">
+        <v>7.3188692975232105E-3</v>
       </c>
       <c r="C14">
-        <v>-1.6106877841293591E-5</v>
+        <v>-5.6422966327218777E-6</v>
       </c>
       <c r="D14">
-        <v>4.7850681222955064E-6</v>
+        <v>-1.6360224643778689E-6</v>
       </c>
       <c r="E14">
-        <v>-3.7662758621914361E-8</v>
+        <v>1.9179329431223549E-8</v>
       </c>
       <c r="F14">
-        <v>-3.7507574787564714E-6</v>
+        <v>3.6962994519418209E-6</v>
       </c>
       <c r="G14">
-        <v>1.5242450349293475E-5</v>
+        <v>9.9134665784640035E-6</v>
       </c>
       <c r="H14">
-        <v>3.5933627439942167E-4</v>
+        <v>7.7692966621244094E-5</v>
       </c>
       <c r="I14">
-        <v>3.1452716917271728E-4</v>
+        <v>7.4384529647562243E-5</v>
       </c>
       <c r="J14">
-        <v>3.1898232102219308E-4</v>
+        <v>7.7429648024753562E-5</v>
       </c>
       <c r="K14">
-        <v>9.4470998932977872E-6</v>
+        <v>-6.1521050240706776E-7</v>
       </c>
       <c r="L14">
-        <v>8.8620550228148473E-6</v>
+        <v>-1.4319515040121239E-6</v>
       </c>
       <c r="M14">
-        <v>-1.1627332219492377E-5</v>
+        <v>2.261562895939198E-7</v>
       </c>
       <c r="N14">
-        <v>-2.6246099474191212E-6</v>
+        <v>5.6114523690611667E-7</v>
       </c>
       <c r="O14">
-        <v>1.1883968083991577E-4</v>
+        <v>2.1151950334758696E-5</v>
       </c>
       <c r="P14">
-        <v>1.6398495087742979E-5</v>
+        <v>-2.9958852945358345E-6</v>
       </c>
       <c r="Q14">
-        <v>-6.7652116701053262E-5</v>
+        <v>-8.1113908351357792E-6</v>
       </c>
       <c r="R14">
-        <v>-6.6410590162537339E-5</v>
+        <v>7.1916328340362583E-6</v>
       </c>
       <c r="S14">
-        <v>8.5367800234729919E-6</v>
+        <v>4.3294146512942621E-6</v>
       </c>
       <c r="T14">
-        <v>-1.4613606207607675E-5</v>
+        <v>4.3645387060079595E-6</v>
       </c>
       <c r="U14">
-        <v>-6.5743544327962313E-8</v>
+        <v>6.8973323817475985E-7</v>
       </c>
       <c r="V14">
-        <v>-2.8408037548809497E-6</v>
+        <v>7.0397756707939917E-7</v>
       </c>
       <c r="W14">
-        <v>7.4759129479839401E-7</v>
+        <v>5.814047318459991E-7</v>
       </c>
       <c r="X14">
-        <v>2.0814173024050837E-6</v>
+        <v>-3.6810017569154283E-6</v>
       </c>
       <c r="Y14">
-        <v>-1.9067396904003884E-5</v>
+        <v>-4.9925851062191675E-6</v>
       </c>
       <c r="Z14">
-        <v>-4.8582126792973254E-4</v>
+        <v>-8.7132612874398128E-5</v>
       </c>
     </row>
     <row r="15" spans="1:26" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>20</v>
-      </c>
-      <c r="B15" s="4">
-        <v>4.2834043052942015</v>
+        <v>19</v>
+      </c>
+      <c r="B15">
+        <v>2.1245909372469165</v>
       </c>
       <c r="C15">
-        <v>-6.1616736195303518E-6</v>
+        <v>-9.3537273746559663E-6</v>
       </c>
       <c r="D15">
-        <v>1.7990167347663785E-5</v>
+        <v>-7.2866488159888207E-6</v>
       </c>
       <c r="E15">
-        <v>-2.3914809880062036E-7</v>
+        <v>2.2592922394968238E-8</v>
       </c>
       <c r="F15">
-        <v>4.5893494467773993E-5</v>
+        <v>1.2124547755947625E-4</v>
       </c>
       <c r="G15">
-        <v>3.5326185515899017E-4</v>
+        <v>3.0212510917043136E-4</v>
       </c>
       <c r="H15">
-        <v>3.5269211232810682E-4</v>
+        <v>1.3157415212642991E-5</v>
       </c>
       <c r="I15">
-        <v>-1.6091380724919148E-4</v>
+        <v>6.9461158303949855E-5</v>
       </c>
       <c r="J15">
-        <v>-1.3256968413288654E-4</v>
+        <v>7.5609536548485465E-6</v>
       </c>
       <c r="K15">
-        <v>-2.7221906913465956E-4</v>
+        <v>4.5359652573374404E-5</v>
       </c>
       <c r="L15">
-        <v>-3.5757492036081126E-4</v>
+        <v>9.4497646402913482E-5</v>
       </c>
       <c r="M15">
-        <v>-1.494286632164147E-3</v>
+        <v>1.5246466342378165E-4</v>
       </c>
       <c r="N15">
-        <v>5.8118703391004528E-5</v>
+        <v>-1.7564294960533886E-5</v>
       </c>
       <c r="O15">
-        <v>1.6398495087742979E-5</v>
+        <v>-2.9958852945358345E-6</v>
       </c>
       <c r="P15">
-        <v>1.8674224853223391E-2</v>
+        <v>4.5852756680706533E-3</v>
       </c>
       <c r="Q15">
-        <v>-2.1379873176476958E-5</v>
+        <v>4.4414391228305266E-6</v>
       </c>
       <c r="R15">
-        <v>-2.0497027268732968E-3</v>
+        <v>-2.2953889924514159E-4</v>
       </c>
       <c r="S15">
-        <v>-3.5298490546370074E-4</v>
+        <v>1.3316562541317383E-4</v>
       </c>
       <c r="T15">
-        <v>-3.0721872127827707E-4</v>
+        <v>1.1967139053201939E-4</v>
       </c>
       <c r="U15">
-        <v>-4.5934633212122008E-4</v>
+        <v>1.6430287287001771E-5</v>
       </c>
       <c r="V15">
-        <v>-1.0936687984682683E-4</v>
+        <v>2.6763705269150932E-5</v>
       </c>
       <c r="W15">
-        <v>2.0165841262187761E-5</v>
+        <v>1.4198746234983588E-5</v>
       </c>
       <c r="X15">
-        <v>1.2790729798383975E-3</v>
+        <v>1.3743158740737122E-5</v>
       </c>
       <c r="Y15">
-        <v>-4.4773165627762148E-4</v>
+        <v>-1.1474694682946428E-4</v>
       </c>
       <c r="Z15">
-        <v>-1.0742443691731485E-3</v>
+        <v>-5.5095491206692934E-4</v>
       </c>
     </row>
     <row r="16" spans="1:26" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>33</v>
-      </c>
-      <c r="B16" s="4">
-        <v>-1.048984960227076E-2</v>
+        <v>32</v>
+      </c>
+      <c r="B16">
+        <v>1.1174981745491013E-2</v>
       </c>
       <c r="C16">
-        <v>-2.974110074611576E-5</v>
+        <v>-7.9105966988647611E-6</v>
       </c>
       <c r="D16">
-        <v>-1.0838488077256601E-5</v>
+        <v>-3.562346585378855E-6</v>
       </c>
       <c r="E16">
-        <v>9.5820471223792519E-8</v>
+        <v>3.5552566295484652E-8</v>
       </c>
       <c r="F16">
-        <v>6.6773799459460647E-5</v>
+        <v>3.9416742180503504E-6</v>
       </c>
       <c r="G16">
-        <v>7.599701265936589E-5</v>
+        <v>9.9456229460841791E-6</v>
       </c>
       <c r="H16">
-        <v>3.5848321969282154E-6</v>
+        <v>2.2619823318768655E-5</v>
       </c>
       <c r="I16">
-        <v>2.8127441826961109E-6</v>
+        <v>2.4042621231590747E-5</v>
       </c>
       <c r="J16">
-        <v>4.4338415922231214E-5</v>
+        <v>2.7664803361350155E-5</v>
       </c>
       <c r="K16">
-        <v>-3.7153096475986611E-5</v>
+        <v>-3.7917966161784464E-6</v>
       </c>
       <c r="L16">
-        <v>2.4279502873301989E-6</v>
+        <v>-3.036308746923627E-6</v>
       </c>
       <c r="M16">
-        <v>2.3954078196485482E-7</v>
+        <v>-6.4523032225885779E-6</v>
       </c>
       <c r="N16">
-        <v>-9.9559191873397179E-6</v>
+        <v>-4.5518787523706891E-7</v>
       </c>
       <c r="O16">
-        <v>-6.7652116701053262E-5</v>
+        <v>-8.1113908351357792E-6</v>
       </c>
       <c r="P16">
-        <v>-2.1379873176476958E-5</v>
+        <v>4.4414391228305266E-6</v>
       </c>
       <c r="Q16">
-        <v>8.9615795632895805E-5</v>
+        <v>1.6179715054559891E-5</v>
       </c>
       <c r="R16">
-        <v>4.107602134735563E-5</v>
+        <v>1.1962960234478225E-6</v>
       </c>
       <c r="S16">
-        <v>-9.2538073233173839E-7</v>
+        <v>3.2140290321605563E-6</v>
       </c>
       <c r="T16">
-        <v>5.2997385310260865E-6</v>
+        <v>2.4535957961481216E-6</v>
       </c>
       <c r="U16">
-        <v>5.4438029899058459E-6</v>
+        <v>-2.4030500342602184E-6</v>
       </c>
       <c r="V16">
-        <v>8.5281436049276899E-6</v>
+        <v>-7.6683534285440012E-7</v>
       </c>
       <c r="W16">
-        <v>-1.1575118984314643E-6</v>
+        <v>1.0965818277581962E-7</v>
       </c>
       <c r="X16">
-        <v>-1.44640776023036E-5</v>
+        <v>6.6590267729446182E-7</v>
       </c>
       <c r="Y16">
-        <v>7.7598119044286755E-6</v>
+        <v>-2.0188572123193387E-6</v>
       </c>
       <c r="Z16">
-        <v>2.0599611265711387E-4</v>
+        <v>2.7800062831695899E-5</v>
       </c>
     </row>
     <row r="17" spans="1:26" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>34</v>
-      </c>
-      <c r="B17" s="4">
-        <v>2.6491452669883668</v>
+        <v>33</v>
+      </c>
+      <c r="B17">
+        <v>0.53603310650276847</v>
       </c>
       <c r="C17">
-        <v>1.1317409883911767E-4</v>
+        <v>9.9113807268979255E-6</v>
       </c>
       <c r="D17">
-        <v>-4.3551902623353085E-5</v>
+        <v>-6.5427626084489708E-6</v>
       </c>
       <c r="E17">
-        <v>3.8938360788607817E-7</v>
+        <v>4.1936601399230843E-8</v>
       </c>
       <c r="F17">
-        <v>5.1875941152168515E-5</v>
+        <v>3.2747887556468198E-5</v>
       </c>
       <c r="G17">
-        <v>8.2620771070478346E-5</v>
+        <v>9.9605645950698915E-5</v>
       </c>
       <c r="H17">
-        <v>-2.1835425973305757E-4</v>
+        <v>3.9129726335896536E-5</v>
       </c>
       <c r="I17">
-        <v>-1.8320079918309872E-5</v>
+        <v>8.0721235577946787E-5</v>
       </c>
       <c r="J17">
-        <v>1.3519401382955116E-5</v>
+        <v>6.5730285269400938E-5</v>
       </c>
       <c r="K17">
-        <v>9.8458759243898056E-5</v>
+        <v>3.3716772293056045E-5</v>
       </c>
       <c r="L17">
-        <v>-3.4883103597178411E-4</v>
+        <v>-1.0620491329578697E-5</v>
       </c>
       <c r="M17">
-        <v>-4.0761168211876967E-4</v>
+        <v>-6.3389826700670308E-5</v>
       </c>
       <c r="N17">
-        <v>-2.4799050599614821E-5</v>
+        <v>2.2886214958567613E-7</v>
       </c>
       <c r="O17">
-        <v>-6.6410590162537339E-5</v>
+        <v>7.1916328340362583E-6</v>
       </c>
       <c r="P17">
-        <v>-2.0497027268732968E-3</v>
+        <v>-2.2953889924514159E-4</v>
       </c>
       <c r="Q17">
-        <v>4.107602134735563E-5</v>
+        <v>1.1962960234478225E-6</v>
       </c>
       <c r="R17">
-        <v>9.7864901892834484E-3</v>
+        <v>1.256849031048056E-3</v>
       </c>
       <c r="S17">
-        <v>-1.5592365356163862E-4</v>
+        <v>9.1705349180599627E-5</v>
       </c>
       <c r="T17">
-        <v>-2.1631710320102988E-4</v>
+        <v>5.0899574474323745E-5</v>
       </c>
       <c r="U17">
-        <v>-1.6548053702964452E-4</v>
+        <v>6.5505306577585493E-6</v>
       </c>
       <c r="V17">
-        <v>-1.6197620198304117E-4</v>
+        <v>1.5529412593238282E-5</v>
       </c>
       <c r="W17">
-        <v>-1.9104016726998E-5</v>
+        <v>2.3120388220933762E-5</v>
       </c>
       <c r="X17">
-        <v>-1.0357543255889339E-4</v>
+        <v>-4.4011452889410269E-5</v>
       </c>
       <c r="Y17">
-        <v>-1.4182065293793597E-4</v>
+        <v>2.1097745748410912E-5</v>
       </c>
       <c r="Z17">
-        <v>1.3332604625859018E-3</v>
+        <v>-4.917801327568688E-4</v>
       </c>
     </row>
     <row r="18" spans="1:26" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>35</v>
       </c>
-      <c r="B18" s="4">
-        <v>7.0777923492592917E-2</v>
+      <c r="B18">
+        <v>-0.36947128334618357</v>
       </c>
       <c r="C18">
-        <v>-3.1930597001795954E-5</v>
+        <v>-2.4760968515378431E-5</v>
       </c>
       <c r="D18">
-        <v>1.9280583675494105E-5</v>
+        <v>-2.7724845509853414E-6</v>
       </c>
       <c r="E18">
-        <v>-1.8016041331657672E-7</v>
+        <v>3.2226335729336566E-8</v>
       </c>
       <c r="F18">
-        <v>-8.9427230875303138E-5</v>
+        <v>1.8538703766488876E-5</v>
       </c>
       <c r="G18">
-        <v>-2.5749285919079404E-4</v>
+        <v>-1.0242658971515465E-5</v>
       </c>
       <c r="H18">
-        <v>2.0584464399172817E-4</v>
+        <v>-1.5642980307411727E-5</v>
       </c>
       <c r="I18">
-        <v>1.4138133922669848E-4</v>
+        <v>-3.216752376598364E-5</v>
       </c>
       <c r="J18">
-        <v>8.2205096612161539E-5</v>
+        <v>3.8751328748586658E-5</v>
       </c>
       <c r="K18">
-        <v>6.4229959810783869E-5</v>
+        <v>9.2243470161533517E-7</v>
       </c>
       <c r="L18">
-        <v>1.3503534828820723E-4</v>
+        <v>-1.8347087561049861E-6</v>
       </c>
       <c r="M18">
-        <v>-3.3336865053150227E-5</v>
+        <v>-1.3580742055550174E-5</v>
       </c>
       <c r="N18">
-        <v>3.0391854924508087E-5</v>
+        <v>6.4915830477918469E-6</v>
       </c>
       <c r="O18">
-        <v>8.5367800234729919E-6</v>
+        <v>4.3294146512942621E-6</v>
       </c>
       <c r="P18">
-        <v>-3.5298490546370074E-4</v>
+        <v>1.3316562541317383E-4</v>
       </c>
       <c r="Q18">
-        <v>-9.2538073233173839E-7</v>
+        <v>3.2140290321605563E-6</v>
       </c>
       <c r="R18">
-        <v>-1.5592365356163862E-4</v>
+        <v>9.1705349180599627E-5</v>
       </c>
       <c r="S18">
-        <v>3.5981193214918794E-3</v>
+        <v>9.3252100533236179E-4</v>
       </c>
       <c r="T18">
-        <v>1.9373963085506938E-3</v>
+        <v>4.5948658945329363E-4</v>
       </c>
       <c r="U18">
-        <v>1.9308094190586039E-3</v>
+        <v>4.3567454357778688E-4</v>
       </c>
       <c r="V18">
-        <v>1.9410766389405993E-3</v>
+        <v>4.3994765594981025E-4</v>
       </c>
       <c r="W18">
-        <v>-5.7304002856855302E-5</v>
+        <v>-3.1773859793348248E-6</v>
       </c>
       <c r="X18">
-        <v>-1.3307224466582669E-4</v>
+        <v>2.559622617504838E-5</v>
       </c>
       <c r="Y18">
-        <v>2.6827644528989395E-4</v>
+        <v>2.9341575672740979E-5</v>
       </c>
       <c r="Z18">
-        <v>-1.5439685437287393E-3</v>
+        <v>-4.2186910526187133E-4</v>
       </c>
     </row>
     <row r="19" spans="1:26" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>36</v>
       </c>
-      <c r="B19" s="4">
-        <v>0.34073087210179648</v>
+      <c r="B19">
+        <v>-0.54903298360136532</v>
       </c>
       <c r="C19">
-        <v>1.5787656139973656E-5</v>
+        <v>-2.0349882290950109E-5</v>
       </c>
       <c r="D19">
-        <v>1.2070308675688482E-5</v>
+        <v>-1.4194491696989541E-6</v>
       </c>
       <c r="E19">
-        <v>-1.7012423833868518E-7</v>
+        <v>2.199054723841206E-8</v>
       </c>
       <c r="F19">
-        <v>-1.4944370075172048E-4</v>
+        <v>1.7307204965050522E-5</v>
       </c>
       <c r="G19">
-        <v>-9.0989792033858833E-5</v>
+        <v>-8.3988302436985892E-6</v>
       </c>
       <c r="H19">
-        <v>-4.8157230896755986E-5</v>
+        <v>3.4430845437848968E-6</v>
       </c>
       <c r="I19">
-        <v>3.8490274803550052E-5</v>
+        <v>-4.5569162773807654E-5</v>
       </c>
       <c r="J19">
-        <v>3.8445495437119731E-5</v>
+        <v>4.2449390250190466E-5</v>
       </c>
       <c r="K19">
-        <v>-1.6859652177268303E-4</v>
+        <v>8.1086051981943451E-6</v>
       </c>
       <c r="L19">
-        <v>-1.0882491131549408E-4</v>
+        <v>1.4944553644565006E-5</v>
       </c>
       <c r="M19">
-        <v>-2.7870820580016306E-5</v>
+        <v>5.866075390490271E-5</v>
       </c>
       <c r="N19">
-        <v>4.3886044009500613E-5</v>
+        <v>1.4722583875249919E-5</v>
       </c>
       <c r="O19">
-        <v>-1.4613606207607675E-5</v>
+        <v>4.3645387060079595E-6</v>
       </c>
       <c r="P19">
-        <v>-3.0721872127827707E-4</v>
+        <v>1.1967139053201939E-4</v>
       </c>
       <c r="Q19">
-        <v>5.2997385310260865E-6</v>
+        <v>2.4535957961481216E-6</v>
       </c>
       <c r="R19">
-        <v>-2.1631710320102988E-4</v>
+        <v>5.0899574474323745E-5</v>
       </c>
       <c r="S19">
-        <v>1.9373963085506938E-3</v>
+        <v>4.5948658945329363E-4</v>
       </c>
       <c r="T19">
-        <v>4.4700106496537596E-3</v>
+        <v>1.518570929735035E-3</v>
       </c>
       <c r="U19">
-        <v>1.9385638211049895E-3</v>
+        <v>4.3473999289606323E-4</v>
       </c>
       <c r="V19">
-        <v>1.9422909549137294E-3</v>
+        <v>4.3916602514898018E-4</v>
       </c>
       <c r="W19">
-        <v>-5.9695659533411686E-5</v>
+        <v>-4.2815977099313897E-6</v>
       </c>
       <c r="X19">
-        <v>-4.175097813983856E-5</v>
+        <v>1.7334410261212949E-5</v>
       </c>
       <c r="Y19">
-        <v>2.2727092413333096E-4</v>
+        <v>3.5843439536892657E-5</v>
       </c>
       <c r="Z19">
-        <v>-9.912376939941812E-4</v>
+        <v>-4.721877810310796E-4</v>
       </c>
     </row>
     <row r="20" spans="1:26" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>37</v>
       </c>
-      <c r="B20" s="4">
-        <v>0.1473893944873047</v>
+      <c r="B20">
+        <v>9.5925366234143508E-2</v>
       </c>
       <c r="C20">
-        <v>-4.303234360877463E-5</v>
+        <v>1.930230554874688E-6</v>
       </c>
       <c r="D20">
-        <v>9.1289300966917878E-6</v>
+        <v>1.4540266569357089E-6</v>
       </c>
       <c r="E20">
-        <v>-1.1490490676355463E-7</v>
+        <v>-7.7228336994951326E-9</v>
       </c>
       <c r="F20">
-        <v>1.225885141637839E-5</v>
+        <v>-1.437643463629817E-5</v>
       </c>
       <c r="G20">
-        <v>-8.3710056878112974E-5</v>
+        <v>-3.333255961533103E-5</v>
       </c>
       <c r="H20">
-        <v>1.2341537077314611E-4</v>
+        <v>3.426924458995481E-5</v>
       </c>
       <c r="I20">
-        <v>9.6289252865628446E-5</v>
+        <v>1.2178248447282174E-5</v>
       </c>
       <c r="J20">
-        <v>1.3896181743156119E-4</v>
+        <v>2.2637990413158218E-6</v>
       </c>
       <c r="K20">
-        <v>-1.089832686853795E-5</v>
+        <v>-2.7569900902447498E-5</v>
       </c>
       <c r="L20">
-        <v>-9.2163317404511235E-6</v>
+        <v>5.1801573562477434E-6</v>
       </c>
       <c r="M20">
-        <v>-3.9616323218604897E-5</v>
+        <v>2.13351099667649E-5</v>
       </c>
       <c r="N20">
-        <v>8.9992017319033037E-6</v>
+        <v>1.2190679436379693E-6</v>
       </c>
       <c r="O20">
-        <v>-6.5743544327962313E-8</v>
+        <v>6.8973323817475985E-7</v>
       </c>
       <c r="P20">
-        <v>-4.5934633212122008E-4</v>
+        <v>1.6430287287001771E-5</v>
       </c>
       <c r="Q20">
-        <v>5.4438029899058459E-6</v>
+        <v>-2.4030500342602184E-6</v>
       </c>
       <c r="R20">
-        <v>-1.6548053702964452E-4</v>
+        <v>6.5505306577585493E-6</v>
       </c>
       <c r="S20">
-        <v>1.9308094190586039E-3</v>
+        <v>4.3567454357778688E-4</v>
       </c>
       <c r="T20">
-        <v>1.9385638211049895E-3</v>
+        <v>4.3473999289606323E-4</v>
       </c>
       <c r="U20">
-        <v>3.4453687608547237E-3</v>
+        <v>8.35185764858482E-4</v>
       </c>
       <c r="V20">
-        <v>1.9433143873317878E-3</v>
+        <v>4.337499263055405E-4</v>
       </c>
       <c r="W20">
-        <v>-6.0126414419292787E-5</v>
+        <v>-7.1584093287477309E-6</v>
       </c>
       <c r="X20">
-        <v>-2.406400711238616E-4</v>
+        <v>-1.4561829000816654E-5</v>
       </c>
       <c r="Y20">
-        <v>1.6286987944488698E-4</v>
+        <v>8.83098171604565E-6</v>
       </c>
       <c r="Z20">
-        <v>-1.08000187558999E-3</v>
+        <v>-3.3824007416907557E-4</v>
       </c>
     </row>
     <row r="21" spans="1:26" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>38</v>
       </c>
-      <c r="B21" s="4">
-        <v>6.9638471794936138E-2</v>
+      <c r="B21">
+        <v>-0.10179778463791038</v>
       </c>
       <c r="C21">
-        <v>-4.03622165785195E-5</v>
+        <v>-5.3357055333429459E-6</v>
       </c>
       <c r="D21">
-        <v>1.5433213691023887E-5</v>
+        <v>-1.5238299107893068E-6</v>
       </c>
       <c r="E21">
-        <v>-1.7527874688059326E-7</v>
+        <v>1.6931698647129571E-8</v>
       </c>
       <c r="F21">
-        <v>3.492604323026313E-6</v>
+        <v>-3.4271122623108496E-6</v>
       </c>
       <c r="G21">
-        <v>-1.2486684619019382E-4</v>
+        <v>-1.2428230972393267E-5</v>
       </c>
       <c r="H21">
-        <v>2.7585135416178792E-4</v>
+        <v>4.6894016633811531E-6</v>
       </c>
       <c r="I21">
-        <v>1.3900598378666258E-4</v>
+        <v>-6.0959269094791992E-6</v>
       </c>
       <c r="J21">
-        <v>5.9705543709869403E-5</v>
+        <v>1.030997400570618E-5</v>
       </c>
       <c r="K21">
-        <v>-4.5036032423920679E-6</v>
+        <v>-6.8501801556726917E-6</v>
       </c>
       <c r="L21">
-        <v>1.7176405853380565E-5</v>
+        <v>-3.7738828733000678E-6</v>
       </c>
       <c r="M21">
-        <v>-1.7736314328391901E-4</v>
+        <v>9.0980437235087274E-6</v>
       </c>
       <c r="N21">
-        <v>-6.3358881642926537E-6</v>
+        <v>7.0919145752898266E-6</v>
       </c>
       <c r="O21">
-        <v>-2.8408037548809497E-6</v>
+        <v>7.0397756707939917E-7</v>
       </c>
       <c r="P21">
-        <v>-1.0936687984682683E-4</v>
+        <v>2.6763705269150932E-5</v>
       </c>
       <c r="Q21">
-        <v>8.5281436049276899E-6</v>
+        <v>-7.6683534285440012E-7</v>
       </c>
       <c r="R21">
-        <v>-1.6197620198304117E-4</v>
+        <v>1.5529412593238282E-5</v>
       </c>
       <c r="S21">
-        <v>1.9410766389405993E-3</v>
+        <v>4.3994765594981025E-4</v>
       </c>
       <c r="T21">
-        <v>1.9422909549137294E-3</v>
+        <v>4.3916602514898018E-4</v>
       </c>
       <c r="U21">
-        <v>1.9433143873317878E-3</v>
+        <v>4.337499263055405E-4</v>
       </c>
       <c r="V21">
-        <v>2.7525533154353242E-3</v>
+        <v>8.1079918488258771E-4</v>
       </c>
       <c r="W21">
-        <v>-5.31416522502238E-5</v>
+        <v>-8.1791027450360483E-6</v>
       </c>
       <c r="X21">
-        <v>-1.5499141738962139E-4</v>
+        <v>-1.7875582525885616E-5</v>
       </c>
       <c r="Y21">
-        <v>7.2766200978291559E-5</v>
+        <v>4.6100139059255358E-6</v>
       </c>
       <c r="Z21">
-        <v>-1.3212830075310126E-3</v>
+        <v>-2.7933902934915562E-4</v>
       </c>
     </row>
     <row r="22" spans="1:26" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
-        <v>21</v>
-      </c>
-      <c r="B22" s="4">
-        <v>-3.6948423892811111E-2</v>
+        <v>20</v>
+      </c>
+      <c r="B22">
+        <v>7.2362490179358099E-2</v>
       </c>
       <c r="C22">
-        <v>-1.8489065971462965E-6</v>
+        <v>6.4241140035134486E-7</v>
       </c>
       <c r="D22">
-        <v>-3.3377470949820688E-6</v>
+        <v>-4.8675910751175543E-7</v>
       </c>
       <c r="E22">
-        <v>3.0340105741843263E-8</v>
+        <v>-1.2233309193638598E-9</v>
       </c>
       <c r="F22">
-        <v>1.7220990881987147E-5</v>
+        <v>5.2239805422033144E-6</v>
       </c>
       <c r="G22">
-        <v>2.0251400453035254E-5</v>
+        <v>1.198603318790024E-5</v>
       </c>
       <c r="H22">
-        <v>-2.5757842459753981E-5</v>
+        <v>-3.2590277028666701E-6</v>
       </c>
       <c r="I22">
-        <v>-7.5662564888910545E-6</v>
+        <v>8.8441793355109447E-6</v>
       </c>
       <c r="J22">
-        <v>-2.0500938939573997E-5</v>
+        <v>1.0397140634715532E-5</v>
       </c>
       <c r="K22">
-        <v>-7.8548086608421695E-6</v>
+        <v>2.0660026916604154E-6</v>
       </c>
       <c r="L22">
-        <v>-3.0300902384266246E-6</v>
+        <v>-4.7276878218005709E-6</v>
       </c>
       <c r="M22">
-        <v>3.0628907788204219E-6</v>
+        <v>-9.82249850680291E-6</v>
       </c>
       <c r="N22">
-        <v>-7.4402925825339214E-6</v>
+        <v>-4.0619398426883213E-6</v>
       </c>
       <c r="O22">
-        <v>7.4759129479839401E-7</v>
+        <v>5.814047318459991E-7</v>
       </c>
       <c r="P22">
-        <v>2.0165841262187761E-5</v>
+        <v>1.4198746234983588E-5</v>
       </c>
       <c r="Q22">
-        <v>-1.1575118984314643E-6</v>
+        <v>1.0965818277581962E-7</v>
       </c>
       <c r="R22">
-        <v>-1.9104016726998E-5</v>
+        <v>2.3120388220933762E-5</v>
       </c>
       <c r="S22">
-        <v>-5.7304002856855302E-5</v>
+        <v>-3.1773859793348248E-6</v>
       </c>
       <c r="T22">
-        <v>-5.9695659533411686E-5</v>
+        <v>-4.2815977099313897E-6</v>
       </c>
       <c r="U22">
-        <v>-6.0126414419292787E-5</v>
+        <v>-7.1584093287477309E-6</v>
       </c>
       <c r="V22">
-        <v>-5.31416522502238E-5</v>
+        <v>-8.1791027450360483E-6</v>
       </c>
       <c r="W22">
-        <v>2.9795200121711498E-5</v>
+        <v>9.2375493497284672E-6</v>
       </c>
       <c r="X22">
-        <v>-1.0832512201968902E-4</v>
+        <v>-1.6744585501023872E-5</v>
       </c>
       <c r="Y22">
-        <v>-1.2479886174834951E-4</v>
+        <v>-2.295071278862993E-5</v>
       </c>
       <c r="Z22">
-        <v>-3.2913715363322638E-4</v>
+        <v>-1.2006996828146523E-4</v>
       </c>
     </row>
     <row r="23" spans="1:26" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
-        <v>22</v>
-      </c>
-      <c r="B23" s="4">
-        <v>-0.46497500611767489</v>
+        <v>21</v>
+      </c>
+      <c r="B23">
+        <v>0.16450799719733214</v>
       </c>
       <c r="C23">
-        <v>3.8758169007535272E-5</v>
+        <v>7.3211005194813629E-6</v>
       </c>
       <c r="D23">
-        <v>4.7456284863945449E-5</v>
+        <v>-2.9953078859712694E-6</v>
       </c>
       <c r="E23">
-        <v>-4.3748824523357364E-7</v>
+        <v>2.8424050159782826E-8</v>
       </c>
       <c r="F23">
-        <v>-1.2103884618969542E-4</v>
+        <v>5.4441691505076307E-6</v>
       </c>
       <c r="G23">
-        <v>-4.2580763047944019E-5</v>
+        <v>-1.4523466102543182E-6</v>
       </c>
       <c r="H23">
-        <v>5.2895724822177607E-4</v>
+        <v>-6.9115614778209261E-5</v>
       </c>
       <c r="I23">
-        <v>2.2587214035028392E-4</v>
+        <v>-1.888943224783563E-6</v>
       </c>
       <c r="J23">
-        <v>1.4146172198566641E-4</v>
+        <v>-2.095688771491821E-5</v>
       </c>
       <c r="K23">
-        <v>1.9946283460452836E-4</v>
+        <v>2.6783808046612482E-5</v>
       </c>
       <c r="L23">
-        <v>1.2214719370816124E-4</v>
+        <v>1.1827356287629452E-5</v>
       </c>
       <c r="M23">
-        <v>-4.5002205489233456E-4</v>
+        <v>-1.1972997822525574E-5</v>
       </c>
       <c r="N23">
-        <v>5.7388108143108197E-5</v>
+        <v>8.7700092162105439E-6</v>
       </c>
       <c r="O23">
-        <v>2.0814173024050837E-6</v>
+        <v>-3.6810017569154283E-6</v>
       </c>
       <c r="P23">
-        <v>1.2790729798383975E-3</v>
+        <v>1.3743158740737122E-5</v>
       </c>
       <c r="Q23">
-        <v>-1.44640776023036E-5</v>
+        <v>6.6590267729446182E-7</v>
       </c>
       <c r="R23">
-        <v>-1.0357543255889339E-4</v>
+        <v>-4.4011452889410269E-5</v>
       </c>
       <c r="S23">
-        <v>-1.3307224466582669E-4</v>
+        <v>2.559622617504838E-5</v>
       </c>
       <c r="T23">
-        <v>-4.175097813983856E-5</v>
+        <v>1.7334410261212949E-5</v>
       </c>
       <c r="U23">
-        <v>-2.406400711238616E-4</v>
+        <v>-1.4561829000816654E-5</v>
       </c>
       <c r="V23">
-        <v>-1.5499141738962139E-4</v>
+        <v>-1.7875582525885616E-5</v>
       </c>
       <c r="W23">
-        <v>-1.0832512201968902E-4</v>
+        <v>-1.6744585501023872E-5</v>
       </c>
       <c r="X23">
-        <v>6.4292795434908916E-3</v>
+        <v>7.6444460374600911E-4</v>
       </c>
       <c r="Y23">
-        <v>1.1281446579347871E-3</v>
+        <v>4.4137506245900063E-4</v>
       </c>
       <c r="Z23">
-        <v>3.6661003420565596E-5</v>
+        <v>2.7569184283633729E-4</v>
       </c>
     </row>
     <row r="24" spans="1:26" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
-        <v>23</v>
-      </c>
-      <c r="B24" s="4">
-        <v>-0.41258663436045423</v>
+        <v>22</v>
+      </c>
+      <c r="B24">
+        <v>-9.013073683748804E-3</v>
       </c>
       <c r="C24">
-        <v>1.8506060607368518E-5</v>
+        <v>6.0687961971312324E-6</v>
       </c>
       <c r="D24">
-        <v>1.7790854707234191E-5</v>
+        <v>4.4958746874400215E-8</v>
       </c>
       <c r="E24">
-        <v>-1.9351885592057598E-7</v>
+        <v>1.6509860258172627E-8</v>
       </c>
       <c r="F24">
-        <v>-1.0175761089266844E-4</v>
+        <v>-7.8852760226817448E-6</v>
       </c>
       <c r="G24">
-        <v>2.5806581809090234E-5</v>
+        <v>-1.9324393009367298E-5</v>
       </c>
       <c r="H24">
-        <v>-1.0039890202066457E-4</v>
+        <v>-9.2507556571743473E-6</v>
       </c>
       <c r="I24">
-        <v>-1.0579345123202947E-5</v>
+        <v>-5.5732285670051214E-5</v>
       </c>
       <c r="J24">
-        <v>-2.3070630088995337E-5</v>
+        <v>-6.8064820096482264E-5</v>
       </c>
       <c r="K24">
-        <v>2.9082759658217126E-5</v>
+        <v>3.5392038102567599E-5</v>
       </c>
       <c r="L24">
-        <v>3.7959409527624222E-5</v>
+        <v>1.3316517232298447E-5</v>
       </c>
       <c r="M24">
-        <v>-2.5629639932315434E-4</v>
+        <v>4.8764172564989448E-5</v>
       </c>
       <c r="N24">
-        <v>-1.010376771855173E-5</v>
+        <v>3.8228483101774771E-5</v>
       </c>
       <c r="O24">
-        <v>-1.9067396904003884E-5</v>
+        <v>-4.9925851062191675E-6</v>
       </c>
       <c r="P24">
-        <v>-4.4773165627762148E-4</v>
+        <v>-1.1474694682946428E-4</v>
       </c>
       <c r="Q24">
-        <v>7.7598119044286755E-6</v>
+        <v>-2.0188572123193387E-6</v>
       </c>
       <c r="R24">
-        <v>-1.4182065293793597E-4</v>
+        <v>2.1097745748410912E-5</v>
       </c>
       <c r="S24">
-        <v>2.6827644528989395E-4</v>
+        <v>2.9341575672740979E-5</v>
       </c>
       <c r="T24">
-        <v>2.2727092413333096E-4</v>
+        <v>3.5843439536892657E-5</v>
       </c>
       <c r="U24">
-        <v>1.6286987944488698E-4</v>
+        <v>8.83098171604565E-6</v>
       </c>
       <c r="V24">
-        <v>7.2766200978291559E-5</v>
+        <v>4.6100139059255358E-6</v>
       </c>
       <c r="W24">
-        <v>-1.2479886174834951E-4</v>
+        <v>-2.295071278862993E-5</v>
       </c>
       <c r="X24">
-        <v>1.1281446579347871E-3</v>
+        <v>4.4137506245900063E-4</v>
       </c>
       <c r="Y24">
-        <v>3.0333125801310186E-3</v>
+        <v>5.5501454774548422E-4</v>
       </c>
       <c r="Z24">
-        <v>1.3948128600288795E-3</v>
+        <v>1.8528884912339297E-4</v>
       </c>
     </row>
     <row r="25" spans="1:26" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
-        <v>24</v>
-      </c>
-      <c r="B25" s="4">
-        <v>-2.0725060798096253</v>
+        <v>23</v>
+      </c>
+      <c r="B25">
+        <v>-1.1592708404516181</v>
       </c>
       <c r="C25">
-        <v>-7.3127166886379001E-4</v>
+        <v>-2.6750172737660915E-4</v>
       </c>
       <c r="D25">
-        <v>-1.5703476312509779E-3</v>
+        <v>-5.1291744315841382E-4</v>
       </c>
       <c r="E25">
-        <v>1.4296387363460427E-5</v>
+        <v>4.4794366207618664E-6</v>
       </c>
       <c r="F25">
-        <v>-1.2966174938875807E-3</v>
+        <v>-1.0201047048666947E-3</v>
       </c>
       <c r="G25">
-        <v>-2.9021676809827097E-3</v>
+        <v>-1.0606612310304104E-3</v>
       </c>
       <c r="H25">
-        <v>-9.1895501848544611E-3</v>
+        <v>-3.4918434793624773E-3</v>
       </c>
       <c r="I25">
-        <v>-3.8211822754501551E-3</v>
+        <v>-1.117218974136736E-3</v>
       </c>
       <c r="J25">
-        <v>-4.9137828341010818E-3</v>
+        <v>-1.2854775460974575E-3</v>
       </c>
       <c r="K25">
-        <v>-2.9915155472920204E-3</v>
+        <v>-7.4348718491287497E-4</v>
       </c>
       <c r="L25">
-        <v>-4.8929371409059917E-3</v>
+        <v>-1.282965961914256E-3</v>
       </c>
       <c r="M25">
-        <v>-2.3289291197963963E-3</v>
+        <v>-1.0357465045762325E-3</v>
       </c>
       <c r="N25">
-        <v>-2.545142494712441E-3</v>
+        <v>-4.8722965387099819E-4</v>
       </c>
       <c r="O25">
-        <v>-4.8582126792973254E-4</v>
+        <v>-8.7132612874398128E-5</v>
       </c>
       <c r="P25">
-        <v>-1.0742443691731485E-3</v>
+        <v>-5.5095491206692934E-4</v>
       </c>
       <c r="Q25">
-        <v>2.0599611265711387E-4</v>
+        <v>2.7800062831695899E-5</v>
       </c>
       <c r="R25">
-        <v>1.3332604625859018E-3</v>
+        <v>-4.917801327568688E-4</v>
       </c>
       <c r="S25">
-        <v>-1.5439685437287393E-3</v>
+        <v>-4.2186910526187133E-4</v>
       </c>
       <c r="T25">
-        <v>-9.912376939941812E-4</v>
+        <v>-4.721877810310796E-4</v>
       </c>
       <c r="U25">
-        <v>-1.08000187558999E-3</v>
+        <v>-3.3824007416907557E-4</v>
       </c>
       <c r="V25">
-        <v>-1.3212830075310126E-3</v>
+        <v>-2.7933902934915562E-4</v>
       </c>
       <c r="W25">
-        <v>-3.2913715363322638E-4</v>
+        <v>-1.2006996828146523E-4</v>
       </c>
       <c r="X25">
-        <v>3.6661003420565596E-5</v>
+        <v>2.7569184283633729E-4</v>
       </c>
       <c r="Y25">
-        <v>1.3948128600288795E-3</v>
+        <v>1.8528884912339297E-4</v>
       </c>
       <c r="Z25">
-        <v>6.1924249902459427E-2</v>
+        <v>2.0259045631680128E-2</v>
       </c>
     </row>
   </sheetData>
@@ -3411,28 +3377,28 @@
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" t="s">
         <v>13</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>14</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>15</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>16</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>17</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>18</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>19</v>
-      </c>
-      <c r="H1" t="s">
-        <v>20</v>
       </c>
       <c r="I1" t="s">
         <v>35</v>
@@ -3447,716 +3413,716 @@
         <v>38</v>
       </c>
       <c r="M1" t="s">
+        <v>20</v>
+      </c>
+      <c r="N1" t="s">
         <v>21</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>22</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>23</v>
-      </c>
-      <c r="P1" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2" s="4">
-        <v>0.12319420025411058</v>
+        <v>14</v>
+      </c>
+      <c r="B2">
+        <v>-8.0031862168541842E-2</v>
       </c>
       <c r="C2">
-        <v>5.0195282325361801E-3</v>
+        <v>3.3541050378593103E-3</v>
       </c>
       <c r="D2">
-        <v>-1.1252605851151789E-3</v>
+        <v>-7.4448296551565818E-4</v>
       </c>
       <c r="E2">
-        <v>2.7207528922078958E-5</v>
+        <v>1.9337930593156755E-5</v>
       </c>
       <c r="F2">
-        <v>-2.9057946088258493E-4</v>
+        <v>-4.4126044919863311E-5</v>
       </c>
       <c r="G2">
-        <v>2.3169774070266414E-4</v>
+        <v>-4.5748112136919348E-5</v>
       </c>
       <c r="H2">
-        <v>1.3843346208248404E-3</v>
+        <v>-2.1041225617311494E-4</v>
       </c>
       <c r="I2">
-        <v>1.22992819960481E-3</v>
+        <v>6.737888380704618E-4</v>
       </c>
       <c r="J2">
-        <v>-2.4736610286243835E-4</v>
+        <v>4.9220733254687083E-4</v>
       </c>
       <c r="K2">
-        <v>1.23506838494092E-3</v>
+        <v>1.5765125018504648E-4</v>
       </c>
       <c r="L2">
-        <v>1.3219394753812303E-3</v>
+        <v>1.0973402013506875E-4</v>
       </c>
       <c r="M2">
-        <v>-2.0669883189212545E-4</v>
+        <v>-1.0174975793236091E-5</v>
       </c>
       <c r="N2">
-        <v>1.1135141558624578E-3</v>
+        <v>5.1516370329221734E-4</v>
       </c>
       <c r="O2">
-        <v>1.3596766944184713E-3</v>
+        <v>2.8528512257399189E-4</v>
       </c>
       <c r="P2">
-        <v>1.1800140215829216E-2</v>
+        <v>5.6462228461383046E-3</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" s="4">
-        <v>-1.1526274440216122</v>
+        <v>15</v>
+      </c>
+      <c r="B3">
+        <v>-1.1016067510995129</v>
       </c>
       <c r="C3">
-        <v>-1.1252605851151789E-3</v>
+        <v>-7.4448296551565818E-4</v>
       </c>
       <c r="D3">
-        <v>0.11382906973580703</v>
+        <v>3.9600104137418324E-2</v>
       </c>
       <c r="E3">
-        <v>-2.6746014776572657E-3</v>
+        <v>-9.0918792296049589E-4</v>
       </c>
       <c r="F3">
-        <v>-1.7554362139046986E-3</v>
+        <v>-5.2536985937378169E-4</v>
       </c>
       <c r="G3">
-        <v>-2.3433645321509072E-3</v>
+        <v>-1.4153391873213106E-4</v>
       </c>
       <c r="H3">
-        <v>-1.1197888601447215E-2</v>
+        <v>-4.5890234440099098E-4</v>
       </c>
       <c r="I3">
-        <v>8.0043786157224517E-4</v>
+        <v>-9.8344213348908194E-4</v>
       </c>
       <c r="J3">
-        <v>-5.6185426881895373E-3</v>
+        <v>1.3317152253580211E-3</v>
       </c>
       <c r="K3">
-        <v>-2.3673205086899296E-3</v>
+        <v>9.5864209889925944E-4</v>
       </c>
       <c r="L3">
-        <v>-5.1838683665106355E-3</v>
+        <v>8.1599359991203768E-4</v>
       </c>
       <c r="M3">
-        <v>2.657933204922025E-5</v>
+        <v>-2.3023808209551855E-4</v>
       </c>
       <c r="N3">
-        <v>-6.4714649724706419E-4</v>
+        <v>-3.0171525863692539E-4</v>
       </c>
       <c r="O3">
-        <v>1.6212045003851649E-3</v>
+        <v>5.011014410160608E-4</v>
       </c>
       <c r="P3">
-        <v>-1.1818694378680359</v>
+        <v>-0.4185270447493683</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B4" s="4">
-        <v>2.6326382510832691E-2</v>
+        <v>16</v>
+      </c>
+      <c r="B4">
+        <v>2.3714752259823134E-2</v>
       </c>
       <c r="C4">
-        <v>2.7207528922078958E-5</v>
+        <v>1.9337930593156755E-5</v>
       </c>
       <c r="D4">
-        <v>-2.6746014776572657E-3</v>
+        <v>-9.0918792296049589E-4</v>
       </c>
       <c r="E4">
-        <v>6.3071912756288405E-5</v>
+        <v>2.0952923211004632E-5</v>
       </c>
       <c r="F4">
-        <v>4.3989813547445043E-5</v>
+        <v>1.3586821547763956E-5</v>
       </c>
       <c r="G4">
-        <v>5.2379212139450071E-5</v>
+        <v>2.7158299071251047E-6</v>
       </c>
       <c r="H4">
-        <v>2.4211597486782643E-4</v>
+        <v>7.984600369327112E-6</v>
       </c>
       <c r="I4">
-        <v>-3.2047592142248754E-5</v>
+        <v>2.2984281576036991E-5</v>
       </c>
       <c r="J4">
-        <v>1.2572296763127631E-4</v>
+        <v>-3.7397895073953101E-5</v>
       </c>
       <c r="K4">
-        <v>5.0569477060290885E-5</v>
+        <v>-2.1596748820682139E-5</v>
       </c>
       <c r="L4">
-        <v>1.2190841548789105E-4</v>
+        <v>-1.9148968912972939E-5</v>
       </c>
       <c r="M4">
-        <v>2.6058318862301824E-7</v>
+        <v>5.3285524412709792E-6</v>
       </c>
       <c r="N4">
-        <v>7.4613889960509217E-6</v>
+        <v>8.9519006272191677E-6</v>
       </c>
       <c r="O4">
-        <v>-3.7975802741879033E-5</v>
+        <v>-1.2565301891906411E-5</v>
       </c>
       <c r="P4">
-        <v>2.766296587348438E-2</v>
+        <v>9.5665320114287078E-3</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" s="4">
-        <v>5.3308697031061704E-2</v>
+        <v>17</v>
+      </c>
+      <c r="B5">
+        <v>3.0018362872930703E-2</v>
       </c>
       <c r="C5">
-        <v>-2.9057946088258493E-4</v>
+        <v>-4.4126044919863311E-5</v>
       </c>
       <c r="D5">
-        <v>-1.7554362139046986E-3</v>
+        <v>-5.2536985937378169E-4</v>
       </c>
       <c r="E5">
-        <v>4.3989813547445043E-5</v>
+        <v>1.3586821547763956E-5</v>
       </c>
       <c r="F5">
-        <v>2.2706831400724154E-3</v>
+        <v>1.8468363891396707E-3</v>
       </c>
       <c r="G5">
-        <v>5.354546410503121E-5</v>
+        <v>4.1210557177562911E-5</v>
       </c>
       <c r="H5">
-        <v>-2.280017075353552E-4</v>
+        <v>-1.1915299694196038E-4</v>
       </c>
       <c r="I5">
-        <v>6.6446112980107427E-4</v>
+        <v>6.7006779213668946E-5</v>
       </c>
       <c r="J5">
-        <v>1.4565834611942954E-3</v>
+        <v>-3.5527798149956845E-4</v>
       </c>
       <c r="K5">
-        <v>4.6274793327923461E-4</v>
+        <v>2.7094587692695236E-4</v>
       </c>
       <c r="L5">
-        <v>1.090800571213333E-3</v>
+        <v>2.0245739169760628E-4</v>
       </c>
       <c r="M5">
-        <v>1.6526992286030467E-5</v>
+        <v>3.1161184943816807E-6</v>
       </c>
       <c r="N5">
-        <v>-1.4270717679869954E-4</v>
+        <v>1.9075818077087404E-4</v>
       </c>
       <c r="O5">
-        <v>-5.1547254115068969E-4</v>
+        <v>2.7139749861332645E-4</v>
       </c>
       <c r="P5">
-        <v>6.4851542851403071E-3</v>
+        <v>-3.2566067647884639E-3</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>19</v>
-      </c>
-      <c r="B6" s="4">
-        <v>1.1890812931562274E-2</v>
+        <v>18</v>
+      </c>
+      <c r="B6">
+        <v>2.7326906709935144E-4</v>
       </c>
       <c r="C6">
-        <v>2.3169774070266414E-4</v>
+        <v>-4.5748112136919348E-5</v>
       </c>
       <c r="D6">
-        <v>-2.3433645321509072E-3</v>
+        <v>-1.4153391873213106E-4</v>
       </c>
       <c r="E6">
-        <v>5.2379212139450071E-5</v>
+        <v>2.7158299071251047E-6</v>
       </c>
       <c r="F6">
-        <v>5.354546410503121E-5</v>
+        <v>4.1210557177562911E-5</v>
       </c>
       <c r="G6">
-        <v>1.3934164198531646E-3</v>
+        <v>1.9177549002910005E-4</v>
       </c>
       <c r="H6">
-        <v>5.9148698650419995E-4</v>
+        <v>-3.3820139195250756E-5</v>
       </c>
       <c r="I6">
-        <v>5.565000081345535E-4</v>
+        <v>-1.0532797334682166E-5</v>
       </c>
       <c r="J6">
-        <v>-9.6644541236533352E-6</v>
+        <v>1.5113661094045844E-4</v>
       </c>
       <c r="K6">
-        <v>9.7785644261284485E-5</v>
+        <v>-1.7174097733021879E-5</v>
       </c>
       <c r="L6">
-        <v>4.5739009683734826E-4</v>
+        <v>-3.1365705214942211E-5</v>
       </c>
       <c r="M6">
-        <v>-4.5534866582593514E-5</v>
+        <v>1.0477768236645985E-5</v>
       </c>
       <c r="N6">
-        <v>1.1464250876590601E-4</v>
+        <v>-1.1880370469209028E-4</v>
       </c>
       <c r="O6">
-        <v>-3.0082824316213577E-4</v>
+        <v>-3.4848779927307717E-5</v>
       </c>
       <c r="P6">
-        <v>2.5293738091566466E-2</v>
+        <v>1.3562582116268679E-3</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>20</v>
-      </c>
-      <c r="B7" s="4">
-        <v>1.9646408870008256</v>
+        <v>19</v>
+      </c>
+      <c r="B7">
+        <v>1.8528399954410915</v>
       </c>
       <c r="C7">
-        <v>1.3843346208248404E-3</v>
+        <v>-2.1041225617311494E-4</v>
       </c>
       <c r="D7">
-        <v>-1.1197888601447215E-2</v>
+        <v>-4.5890234440099098E-4</v>
       </c>
       <c r="E7">
-        <v>2.4211597486782643E-4</v>
+        <v>7.984600369327112E-6</v>
       </c>
       <c r="F7">
-        <v>-2.280017075353552E-4</v>
+        <v>-1.1915299694196038E-4</v>
       </c>
       <c r="G7">
-        <v>5.9148698650419995E-4</v>
+        <v>-3.3820139195250756E-5</v>
       </c>
       <c r="H7">
-        <v>1.1294126352228845E-2</v>
+        <v>1.210351550903899E-3</v>
       </c>
       <c r="I7">
-        <v>2.1498735493796356E-3</v>
+        <v>-1.1976272373672055E-4</v>
       </c>
       <c r="J7">
-        <v>-7.7674203696138401E-4</v>
+        <v>5.4423297703512508E-7</v>
       </c>
       <c r="K7">
-        <v>9.8575014910289027E-4</v>
+        <v>1.5098902475966375E-4</v>
       </c>
       <c r="L7">
-        <v>2.0363851534511979E-4</v>
+        <v>8.5690112081428585E-5</v>
       </c>
       <c r="M7">
-        <v>-4.549144309909034E-4</v>
+        <v>-3.7076144257025849E-5</v>
       </c>
       <c r="N7">
-        <v>2.5672419735162377E-3</v>
+        <v>-5.9440249645177114E-4</v>
       </c>
       <c r="O7">
-        <v>3.1645858352313261E-3</v>
+        <v>-4.2186510665438975E-4</v>
       </c>
       <c r="P7">
-        <v>0.1282299973674339</v>
+        <v>6.4501597645320319E-3</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>35</v>
       </c>
-      <c r="B8" s="4">
-        <v>0.24676065035211078</v>
+      <c r="B8">
+        <v>-0.34952103854599376</v>
       </c>
       <c r="C8">
-        <v>1.22992819960481E-3</v>
+        <v>6.737888380704618E-4</v>
       </c>
       <c r="D8">
-        <v>8.0043786157224517E-4</v>
+        <v>-9.8344213348908194E-4</v>
       </c>
       <c r="E8">
-        <v>-3.2047592142248754E-5</v>
+        <v>2.2984281576036991E-5</v>
       </c>
       <c r="F8">
-        <v>6.6446112980107427E-4</v>
+        <v>6.7006779213668946E-5</v>
       </c>
       <c r="G8">
-        <v>5.565000081345535E-4</v>
+        <v>-1.0532797334682166E-5</v>
       </c>
       <c r="H8">
-        <v>2.1498735493796356E-3</v>
+        <v>-1.1976272373672055E-4</v>
       </c>
       <c r="I8">
-        <v>2.3622077387497529E-2</v>
+        <v>8.0438549895216083E-3</v>
       </c>
       <c r="J8">
-        <v>1.894883084470695E-2</v>
+        <v>2.4518476895423694E-3</v>
       </c>
       <c r="K8">
-        <v>1.8470408843994611E-2</v>
+        <v>2.4982010008271628E-3</v>
       </c>
       <c r="L8">
-        <v>1.8687751272662857E-2</v>
+        <v>2.4919561518118669E-3</v>
       </c>
       <c r="M8">
-        <v>-2.7027870232842945E-4</v>
+        <v>1.0299569759283954E-4</v>
       </c>
       <c r="N8">
-        <v>1.8932994781061946E-3</v>
+        <v>4.4048264797431967E-4</v>
       </c>
       <c r="O8">
-        <v>7.8638256617918206E-4</v>
+        <v>3.0647906831390663E-4</v>
       </c>
       <c r="P8">
-        <v>-2.1635764729056095E-2</v>
+        <v>5.4509100273559888E-3</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>36</v>
       </c>
-      <c r="B9" s="4">
-        <v>0.16469994912358724</v>
+      <c r="B9">
+        <v>-0.35554135007226012</v>
       </c>
       <c r="C9">
-        <v>-2.4736610286243835E-4</v>
+        <v>4.9220733254687083E-4</v>
       </c>
       <c r="D9">
-        <v>-5.6185426881895373E-3</v>
+        <v>1.3317152253580211E-3</v>
       </c>
       <c r="E9">
-        <v>1.2572296763127631E-4</v>
+        <v>-3.7397895073953101E-5</v>
       </c>
       <c r="F9">
-        <v>1.4565834611942954E-3</v>
+        <v>-3.5527798149956845E-4</v>
       </c>
       <c r="G9">
-        <v>-9.6644541236533352E-6</v>
+        <v>1.5113661094045844E-4</v>
       </c>
       <c r="H9">
-        <v>-7.7674203696138401E-4</v>
+        <v>5.4423297703512508E-7</v>
       </c>
       <c r="I9">
-        <v>1.894883084470695E-2</v>
+        <v>2.4518476895423694E-3</v>
       </c>
       <c r="J9">
-        <v>3.4726450814474813E-2</v>
+        <v>1.7790435354001169E-2</v>
       </c>
       <c r="K9">
-        <v>1.9023048342741496E-2</v>
+        <v>2.4512287840872996E-3</v>
       </c>
       <c r="L9">
-        <v>1.9058813677783216E-2</v>
+        <v>2.5462921999915558E-3</v>
       </c>
       <c r="M9">
-        <v>1.8006094498874319E-4</v>
+        <v>1.3475270495859706E-4</v>
       </c>
       <c r="N9">
-        <v>-1.6911947769313596E-3</v>
+        <v>-6.571548740600024E-4</v>
       </c>
       <c r="O9">
-        <v>-3.0155073382366129E-3</v>
+        <v>5.9843721436692379E-4</v>
       </c>
       <c r="P9">
-        <v>3.3873743835035268E-2</v>
+        <v>-1.4886530345461779E-2</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="4">
-        <v>0.14480378851144068</v>
+      <c r="B10">
+        <v>-9.6559513463215493E-2</v>
       </c>
       <c r="C10">
-        <v>1.23506838494092E-3</v>
+        <v>1.5765125018504648E-4</v>
       </c>
       <c r="D10">
-        <v>-2.3673205086899296E-3</v>
+        <v>9.5864209889925944E-4</v>
       </c>
       <c r="E10">
-        <v>5.0569477060290885E-5</v>
+        <v>-2.1596748820682139E-5</v>
       </c>
       <c r="F10">
-        <v>4.6274793327923461E-4</v>
+        <v>2.7094587692695236E-4</v>
       </c>
       <c r="G10">
-        <v>9.7785644261284485E-5</v>
+        <v>-1.7174097733021879E-5</v>
       </c>
       <c r="H10">
-        <v>9.8575014910289027E-4</v>
+        <v>1.5098902475966375E-4</v>
       </c>
       <c r="I10">
-        <v>1.8470408843994611E-2</v>
+        <v>2.4982010008271628E-3</v>
       </c>
       <c r="J10">
-        <v>1.9023048342741496E-2</v>
+        <v>2.4512287840872996E-3</v>
       </c>
       <c r="K10">
-        <v>2.3775840579355861E-2</v>
+        <v>4.9791821174333169E-3</v>
       </c>
       <c r="L10">
-        <v>1.8539191987915378E-2</v>
+        <v>2.5051082366599297E-3</v>
       </c>
       <c r="M10">
-        <v>-1.2296816655995094E-4</v>
+        <v>-2.6526047982114941E-5</v>
       </c>
       <c r="N10">
-        <v>1.6220238936531933E-3</v>
+        <v>-1.8342949901992579E-4</v>
       </c>
       <c r="O10">
-        <v>8.2022740902427255E-5</v>
+        <v>-2.5277219356978527E-5</v>
       </c>
       <c r="P10">
-        <v>7.6308813809943254E-3</v>
+        <v>-1.3790990179723531E-2</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="4">
-        <v>0.18776929739002465</v>
+      <c r="B11">
+        <v>2.7025954280804565E-2</v>
       </c>
       <c r="C11">
-        <v>1.3219394753812303E-3</v>
+        <v>1.0973402013506875E-4</v>
       </c>
       <c r="D11">
-        <v>-5.1838683665106355E-3</v>
+        <v>8.1599359991203768E-4</v>
       </c>
       <c r="E11">
-        <v>1.2190841548789105E-4</v>
+        <v>-1.9148968912972939E-5</v>
       </c>
       <c r="F11">
-        <v>1.090800571213333E-3</v>
+        <v>2.0245739169760628E-4</v>
       </c>
       <c r="G11">
-        <v>4.5739009683734826E-4</v>
+        <v>-3.1365705214942211E-5</v>
       </c>
       <c r="H11">
-        <v>2.0363851534511979E-4</v>
+        <v>8.5690112081428585E-5</v>
       </c>
       <c r="I11">
-        <v>1.8687751272662857E-2</v>
+        <v>2.4919561518118669E-3</v>
       </c>
       <c r="J11">
-        <v>1.9058813677783216E-2</v>
+        <v>2.5462921999915558E-3</v>
       </c>
       <c r="K11">
-        <v>1.8539191987915378E-2</v>
+        <v>2.5051082366599297E-3</v>
       </c>
       <c r="L11">
-        <v>2.1418512058959178E-2</v>
+        <v>4.7901666106245156E-3</v>
       </c>
       <c r="M11">
-        <v>-1.4712561356783295E-4</v>
+        <v>-3.085244155139001E-5</v>
       </c>
       <c r="N11">
-        <v>4.9878461699426335E-4</v>
+        <v>-3.114621143207126E-4</v>
       </c>
       <c r="O11">
-        <v>-3.6648383292658265E-5</v>
+        <v>-1.0185387915782299E-4</v>
       </c>
       <c r="P11">
-        <v>3.2542808979383088E-2</v>
+        <v>-1.1441132512972921E-2</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>21</v>
-      </c>
-      <c r="B12" s="4">
-        <v>1.723373731460139E-4</v>
+        <v>20</v>
+      </c>
+      <c r="B12">
+        <v>-1.8684732123456713E-2</v>
       </c>
       <c r="C12">
-        <v>-2.0669883189212545E-4</v>
+        <v>-1.0174975793236091E-5</v>
       </c>
       <c r="D12">
-        <v>2.657933204922025E-5</v>
+        <v>-2.3023808209551855E-4</v>
       </c>
       <c r="E12">
-        <v>2.6058318862301824E-7</v>
+        <v>5.3285524412709792E-6</v>
       </c>
       <c r="F12">
-        <v>1.6526992286030467E-5</v>
+        <v>3.1161184943816807E-6</v>
       </c>
       <c r="G12">
-        <v>-4.5534866582593514E-5</v>
+        <v>1.0477768236645985E-5</v>
       </c>
       <c r="H12">
-        <v>-4.549144309909034E-4</v>
+        <v>-3.7076144257025849E-5</v>
       </c>
       <c r="I12">
-        <v>-2.7027870232842945E-4</v>
+        <v>1.0299569759283954E-4</v>
       </c>
       <c r="J12">
-        <v>1.8006094498874319E-4</v>
+        <v>1.3475270495859706E-4</v>
       </c>
       <c r="K12">
-        <v>-1.2296816655995094E-4</v>
+        <v>-2.6526047982114941E-5</v>
       </c>
       <c r="L12">
-        <v>-1.4712561356783295E-4</v>
+        <v>-3.085244155139001E-5</v>
       </c>
       <c r="M12">
-        <v>1.3957275320010089E-4</v>
+        <v>6.4396832264686975E-5</v>
       </c>
       <c r="N12">
-        <v>-7.8466856244705733E-4</v>
+        <v>-2.2410720580221129E-4</v>
       </c>
       <c r="O12">
-        <v>-8.6984134895892046E-4</v>
+        <v>-2.4847814002912198E-4</v>
       </c>
       <c r="P12">
-        <v>-2.4045286104206424E-3</v>
+        <v>1.4244680409090243E-3</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>22</v>
-      </c>
-      <c r="B13" s="4">
-        <v>0.37387111698028147</v>
+        <v>21</v>
+      </c>
+      <c r="B13">
+        <v>4.2916592674815984E-2</v>
       </c>
       <c r="C13">
-        <v>1.1135141558624578E-3</v>
+        <v>5.1516370329221734E-4</v>
       </c>
       <c r="D13">
-        <v>-6.4714649724706419E-4</v>
+        <v>-3.0171525863692539E-4</v>
       </c>
       <c r="E13">
-        <v>7.4613889960509217E-6</v>
+        <v>8.9519006272191677E-6</v>
       </c>
       <c r="F13">
-        <v>-1.4270717679869954E-4</v>
+        <v>1.9075818077087404E-4</v>
       </c>
       <c r="G13">
-        <v>1.1464250876590601E-4</v>
+        <v>-1.1880370469209028E-4</v>
       </c>
       <c r="H13">
-        <v>2.5672419735162377E-3</v>
+        <v>-5.9440249645177114E-4</v>
       </c>
       <c r="I13">
-        <v>1.8932994781061946E-3</v>
+        <v>4.4048264797431967E-4</v>
       </c>
       <c r="J13">
-        <v>-1.6911947769313596E-3</v>
+        <v>-6.571548740600024E-4</v>
       </c>
       <c r="K13">
-        <v>1.6220238936531933E-3</v>
+        <v>-1.8342949901992579E-4</v>
       </c>
       <c r="L13">
-        <v>4.9878461699426335E-4</v>
+        <v>-3.114621143207126E-4</v>
       </c>
       <c r="M13">
-        <v>-7.8466856244705733E-4</v>
+        <v>-2.2410720580221129E-4</v>
       </c>
       <c r="N13">
-        <v>1.8778063265822459E-2</v>
+        <v>1.0549859299675083E-2</v>
       </c>
       <c r="O13">
-        <v>5.9044829463552294E-3</v>
+        <v>5.4685298274083083E-3</v>
       </c>
       <c r="P13">
-        <v>1.8976903857132403E-2</v>
+        <v>4.5830610487753998E-3</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>23</v>
-      </c>
-      <c r="B14" s="4">
-        <v>0.1959586069288192</v>
+        <v>22</v>
+      </c>
+      <c r="B14">
+        <v>-0.17991278178567746</v>
       </c>
       <c r="C14">
-        <v>1.3596766944184713E-3</v>
+        <v>2.8528512257399189E-4</v>
       </c>
       <c r="D14">
-        <v>1.6212045003851649E-3</v>
+        <v>5.011014410160608E-4</v>
       </c>
       <c r="E14">
-        <v>-3.7975802741879033E-5</v>
+        <v>-1.2565301891906411E-5</v>
       </c>
       <c r="F14">
-        <v>-5.1547254115068969E-4</v>
+        <v>2.7139749861332645E-4</v>
       </c>
       <c r="G14">
-        <v>-3.0082824316213577E-4</v>
+        <v>-3.4848779927307717E-5</v>
       </c>
       <c r="H14">
-        <v>3.1645858352313261E-3</v>
+        <v>-4.2186510665438975E-4</v>
       </c>
       <c r="I14">
-        <v>7.8638256617918206E-4</v>
+        <v>3.0647906831390663E-4</v>
       </c>
       <c r="J14">
-        <v>-3.0155073382366129E-3</v>
+        <v>5.9843721436692379E-4</v>
       </c>
       <c r="K14">
-        <v>8.2022740902427255E-5</v>
+        <v>-2.5277219356978527E-5</v>
       </c>
       <c r="L14">
-        <v>-3.6648383292658265E-5</v>
+        <v>-1.0185387915782299E-4</v>
       </c>
       <c r="M14">
-        <v>-8.6984134895892046E-4</v>
+        <v>-2.4847814002912198E-4</v>
       </c>
       <c r="N14">
-        <v>5.9044829463552294E-3</v>
+        <v>5.4685298274083083E-3</v>
       </c>
       <c r="O14">
-        <v>2.5279861736286643E-2</v>
+        <v>9.3877981583088081E-3</v>
       </c>
       <c r="P14">
-        <v>-4.4414507035290679E-3</v>
+        <v>-2.735299099196415E-3</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>24</v>
-      </c>
-      <c r="B15" s="4">
-        <v>10.10606926980193</v>
+        <v>23</v>
+      </c>
+      <c r="B15">
+        <v>10.51940806348582</v>
       </c>
       <c r="C15">
-        <v>1.1800140215829216E-2</v>
+        <v>5.6462228461383046E-3</v>
       </c>
       <c r="D15">
-        <v>-1.1818694378680359</v>
+        <v>-0.4185270447493683</v>
       </c>
       <c r="E15">
-        <v>2.766296587348438E-2</v>
+        <v>9.5665320114287078E-3</v>
       </c>
       <c r="F15">
-        <v>6.4851542851403071E-3</v>
+        <v>-3.2566067647884639E-3</v>
       </c>
       <c r="G15">
-        <v>2.5293738091566466E-2</v>
+        <v>1.3562582116268679E-3</v>
       </c>
       <c r="H15">
-        <v>0.1282299973674339</v>
+        <v>6.4501597645320319E-3</v>
       </c>
       <c r="I15">
-        <v>-2.1635764729056095E-2</v>
+        <v>5.4509100273559888E-3</v>
       </c>
       <c r="J15">
-        <v>3.3873743835035268E-2</v>
+        <v>-1.4886530345461779E-2</v>
       </c>
       <c r="K15">
-        <v>7.6308813809943254E-3</v>
+        <v>-1.3790990179723531E-2</v>
       </c>
       <c r="L15">
-        <v>3.2542808979383088E-2</v>
+        <v>-1.1441132512972921E-2</v>
       </c>
       <c r="M15">
-        <v>-2.4045286104206424E-3</v>
+        <v>1.4244680409090243E-3</v>
       </c>
       <c r="N15">
-        <v>1.8976903857132403E-2</v>
+        <v>4.5830610487753998E-3</v>
       </c>
       <c r="O15">
-        <v>-4.4414507035290679E-3</v>
+        <v>-2.735299099196415E-3</v>
       </c>
       <c r="P15">
-        <v>12.412622335513817</v>
+        <v>4.5009288998298302</v>
       </c>
     </row>
   </sheetData>
@@ -4174,58 +4140,58 @@
   <sheetData>
     <row r="1" spans="1:26" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" t="s">
         <v>13</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>14</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>15</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>16</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I1" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" t="s">
+        <v>28</v>
+      </c>
+      <c r="K1" t="s">
+        <v>29</v>
+      </c>
+      <c r="L1" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1" t="s">
+        <v>31</v>
+      </c>
+      <c r="N1" t="s">
         <v>17</v>
       </c>
-      <c r="F1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G1" t="s">
-        <v>26</v>
-      </c>
-      <c r="H1" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" t="s">
-        <v>28</v>
-      </c>
-      <c r="J1" t="s">
-        <v>29</v>
-      </c>
-      <c r="K1" t="s">
-        <v>30</v>
-      </c>
-      <c r="L1" t="s">
-        <v>31</v>
-      </c>
-      <c r="M1" t="s">
+      <c r="O1" t="s">
+        <v>18</v>
+      </c>
+      <c r="P1" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q1" t="s">
         <v>32</v>
       </c>
-      <c r="N1" t="s">
-        <v>18</v>
-      </c>
-      <c r="O1" t="s">
-        <v>19</v>
-      </c>
-      <c r="P1" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>33</v>
-      </c>
-      <c r="R1" t="s">
-        <v>34</v>
       </c>
       <c r="S1" t="s">
         <v>35</v>
@@ -4240,1936 +4206,1936 @@
         <v>38</v>
       </c>
       <c r="W1" t="s">
+        <v>20</v>
+      </c>
+      <c r="X1" t="s">
         <v>21</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Y1" t="s">
         <v>22</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Z1" t="s">
         <v>23</v>
-      </c>
-      <c r="Z1" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2" s="4">
-        <v>-5.8244337439533299E-2</v>
+        <v>14</v>
+      </c>
+      <c r="B2">
+        <v>-2.4296226378618238E-2</v>
       </c>
       <c r="C2">
-        <v>8.6129790233819463E-4</v>
+        <v>2.3230418703808472E-4</v>
       </c>
       <c r="D2">
-        <v>1.1537759783117645E-5</v>
+        <v>6.0590986505325357E-6</v>
       </c>
       <c r="E2">
-        <v>-1.3832432375897174E-7</v>
+        <v>-4.9879817171001908E-8</v>
       </c>
       <c r="F2">
-        <v>-6.5821776464585857E-5</v>
+        <v>-1.3901842258290877E-5</v>
       </c>
       <c r="G2">
-        <v>-1.1041942892118178E-4</v>
+        <v>-9.597813122328458E-6</v>
       </c>
       <c r="H2">
-        <v>2.3926617753739894E-5</v>
+        <v>-2.6478409920186573E-5</v>
       </c>
       <c r="I2">
-        <v>4.1345360460427807E-5</v>
+        <v>4.020762171304243E-6</v>
       </c>
       <c r="J2">
-        <v>1.1812306491909035E-4</v>
+        <v>-6.5351464051536813E-5</v>
       </c>
       <c r="K2">
-        <v>2.1290690263527561E-5</v>
+        <v>1.7352902364988686E-5</v>
       </c>
       <c r="L2">
-        <v>1.4136078321906563E-4</v>
+        <v>2.1380422688521254E-5</v>
       </c>
       <c r="M2">
-        <v>3.9559334507008163E-4</v>
+        <v>9.3408167998449554E-5</v>
       </c>
       <c r="N2">
-        <v>8.263790303207261E-6</v>
+        <v>-7.4713184851774906E-6</v>
       </c>
       <c r="O2">
-        <v>-3.4810703238267465E-5</v>
+        <v>-4.5434251341367233E-6</v>
       </c>
       <c r="P2">
-        <v>3.4253593797670524E-5</v>
+        <v>-5.3018050143326489E-6</v>
       </c>
       <c r="Q2">
-        <v>7.0746500088472745E-6</v>
+        <v>-4.4326794273329E-6</v>
       </c>
       <c r="R2">
-        <v>2.9219204551918839E-5</v>
+        <v>2.2095690865363979E-6</v>
       </c>
       <c r="S2">
-        <v>-6.8740754487054616E-5</v>
+        <v>8.9947307677456752E-6</v>
       </c>
       <c r="T2">
-        <v>-2.5049520889910439E-5</v>
+        <v>6.12897660920804E-6</v>
       </c>
       <c r="U2">
-        <v>-2.210067863526545E-5</v>
+        <v>4.0177292178696675E-6</v>
       </c>
       <c r="V2">
-        <v>-5.2814065858668799E-5</v>
+        <v>-3.9273454822358285E-7</v>
       </c>
       <c r="W2">
-        <v>2.531492062338568E-6</v>
+        <v>6.0034505429399852E-7</v>
       </c>
       <c r="X2">
-        <v>-7.3838360348885991E-5</v>
+        <v>7.8824776593289909E-6</v>
       </c>
       <c r="Y2">
-        <v>-1.2361335127915279E-5</v>
+        <v>-1.1388777788190706E-6</v>
       </c>
       <c r="Z2">
-        <v>-5.4097457861786245E-4</v>
+        <v>-2.052694353893756E-4</v>
       </c>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" s="4">
-        <v>-3.1191217533901206E-3</v>
+        <v>15</v>
+      </c>
+      <c r="B3">
+        <v>2.3262285990547329E-2</v>
       </c>
       <c r="C3">
-        <v>1.1537759783117645E-5</v>
+        <v>6.0590986505325357E-6</v>
       </c>
       <c r="D3">
-        <v>3.9269203907667287E-5</v>
+        <v>1.3320685174518696E-5</v>
       </c>
       <c r="E3">
-        <v>-4.0318523265743496E-7</v>
+        <v>-1.2179015056284664E-7</v>
       </c>
       <c r="F3">
-        <v>3.097747956421924E-6</v>
+        <v>-2.613205145728994E-6</v>
       </c>
       <c r="G3">
-        <v>2.0896688269028533E-5</v>
+        <v>-4.2604330610438563E-6</v>
       </c>
       <c r="H3">
-        <v>1.2532664492259226E-4</v>
+        <v>4.3106878982547857E-5</v>
       </c>
       <c r="I3">
-        <v>2.7210431392616574E-5</v>
+        <v>-1.5767788282585176E-6</v>
       </c>
       <c r="J3">
-        <v>1.4538950345677318E-4</v>
+        <v>4.6048409507209911E-6</v>
       </c>
       <c r="K3">
-        <v>8.7815220380825715E-6</v>
+        <v>2.1638555039413422E-6</v>
       </c>
       <c r="L3">
-        <v>9.6829355437907016E-5</v>
+        <v>1.8430983023351977E-5</v>
       </c>
       <c r="M3">
-        <v>8.1038298294644484E-6</v>
+        <v>3.7046615812273459E-6</v>
       </c>
       <c r="N3">
-        <v>1.9440038454409223E-5</v>
+        <v>-6.0586291069508023E-7</v>
       </c>
       <c r="O3">
-        <v>4.3904665657726409E-6</v>
+        <v>-5.5322703420250999E-7</v>
       </c>
       <c r="P3">
-        <v>2.1875134260745076E-6</v>
+        <v>-3.9441584444811019E-6</v>
       </c>
       <c r="Q3">
-        <v>-7.1366978749782726E-6</v>
+        <v>-2.6338406783097621E-6</v>
       </c>
       <c r="R3">
-        <v>-1.1912993313841652E-5</v>
+        <v>2.318414674662867E-6</v>
       </c>
       <c r="S3">
-        <v>-3.7250098793184365E-5</v>
+        <v>2.7607705692786672E-6</v>
       </c>
       <c r="T3">
-        <v>-2.8046201873132789E-5</v>
+        <v>1.7132150989396114E-6</v>
       </c>
       <c r="U3">
-        <v>-1.1754883711324031E-5</v>
+        <v>1.8305068884135411E-6</v>
       </c>
       <c r="V3">
-        <v>-4.6111083192621025E-6</v>
+        <v>1.447232824922551E-6</v>
       </c>
       <c r="W3">
-        <v>-4.0329785101902516E-8</v>
+        <v>3.3183568241448074E-7</v>
       </c>
       <c r="X3">
-        <v>3.2091389183514342E-7</v>
+        <v>-1.0678991882215978E-6</v>
       </c>
       <c r="Y3">
-        <v>-1.899410615235473E-5</v>
+        <v>-1.6968097017025426E-6</v>
       </c>
       <c r="Z3">
-        <v>-9.7190515930184744E-4</v>
+        <v>-3.288898409886566E-4</v>
       </c>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B4" s="4">
-        <v>2.1458686554868058E-5</v>
+        <v>16</v>
+      </c>
+      <c r="B4">
+        <v>-1.5658021899878343E-4</v>
       </c>
       <c r="C4">
-        <v>-1.3832432375897174E-7</v>
+        <v>-4.9879817171001908E-8</v>
       </c>
       <c r="D4">
-        <v>-4.0318523265743496E-7</v>
+        <v>-1.2179015056284664E-7</v>
       </c>
       <c r="E4">
-        <v>4.3256818085386898E-9</v>
+        <v>1.1625420897029464E-9</v>
       </c>
       <c r="F4">
-        <v>-4.2284407424664498E-8</v>
+        <v>2.3008893454322691E-8</v>
       </c>
       <c r="G4">
-        <v>-2.6082323092895617E-7</v>
+        <v>1.0284165938616245E-8</v>
       </c>
       <c r="H4">
-        <v>-1.0542185214877344E-6</v>
+        <v>-3.0643102239210047E-7</v>
       </c>
       <c r="I4">
-        <v>-2.4625110527586493E-7</v>
+        <v>3.2528299305907866E-9</v>
       </c>
       <c r="J4">
-        <v>-1.9126147150741681E-6</v>
+        <v>-1.3022831994831984E-7</v>
       </c>
       <c r="K4">
-        <v>7.4340317162795604E-8</v>
+        <v>9.6805066140436183E-9</v>
       </c>
       <c r="L4">
-        <v>-8.8391568942679372E-7</v>
+        <v>-1.5145773318601679E-7</v>
       </c>
       <c r="M4">
-        <v>7.4115891119072505E-8</v>
+        <v>7.022253081E-9</v>
       </c>
       <c r="N4">
-        <v>-1.2270871511615015E-7</v>
+        <v>1.8569552925896075E-8</v>
       </c>
       <c r="O4">
-        <v>-3.5907709889012168E-8</v>
+        <v>7.1156786327649309E-9</v>
       </c>
       <c r="P4">
-        <v>-3.4445761935874338E-8</v>
+        <v>3.0517519950605474E-8</v>
       </c>
       <c r="Q4">
-        <v>6.6367420612143924E-8</v>
+        <v>2.6034399810427398E-8</v>
       </c>
       <c r="R4">
-        <v>7.9341648558189329E-8</v>
+        <v>-2.312981855302495E-8</v>
       </c>
       <c r="S4">
-        <v>3.6387185071771577E-7</v>
+        <v>-2.3095984567940335E-8</v>
       </c>
       <c r="T4">
-        <v>3.1138648873248127E-7</v>
+        <v>-1.4035384774121009E-8</v>
       </c>
       <c r="U4">
-        <v>1.1685853539109537E-7</v>
+        <v>-1.4724836446767245E-8</v>
       </c>
       <c r="V4">
-        <v>6.3122073051336974E-8</v>
+        <v>-1.7293325221811415E-8</v>
       </c>
       <c r="W4">
-        <v>-1.7091764456851345E-9</v>
+        <v>-5.1590226801820155E-9</v>
       </c>
       <c r="X4">
-        <v>-9.0277729582625478E-9</v>
+        <v>5.0910654532365833E-10</v>
       </c>
       <c r="Y4">
-        <v>1.8642845634098309E-7</v>
+        <v>1.7153634489465683E-8</v>
       </c>
       <c r="Z4">
-        <v>9.2542742162443259E-6</v>
+        <v>2.837904909877767E-6</v>
       </c>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>25</v>
-      </c>
-      <c r="B5" s="4">
-        <v>-2.6243066590943814E-2</v>
+        <v>24</v>
+      </c>
+      <c r="B5">
+        <v>-0.19160865107007224</v>
       </c>
       <c r="C5">
-        <v>-6.5821776464585857E-5</v>
+        <v>-1.3901842258290877E-5</v>
       </c>
       <c r="D5">
-        <v>3.097747956421924E-6</v>
+        <v>-2.613205145728994E-6</v>
       </c>
       <c r="E5">
-        <v>-4.2284407424664498E-8</v>
+        <v>2.3008893454322691E-8</v>
       </c>
       <c r="F5">
-        <v>1.2487632945239503E-3</v>
+        <v>3.5912284057389984E-4</v>
       </c>
       <c r="G5">
-        <v>1.0734375848985645E-3</v>
+        <v>2.4215546202781187E-4</v>
       </c>
       <c r="H5">
-        <v>2.480932595793346E-4</v>
+        <v>-1.952976663859173E-6</v>
       </c>
       <c r="I5">
-        <v>2.5341839490375978E-5</v>
+        <v>-6.3477558574498811E-6</v>
       </c>
       <c r="J5">
-        <v>1.4191679568151014E-4</v>
+        <v>7.8735653036820092E-6</v>
       </c>
       <c r="K5">
-        <v>3.6738752805370016E-5</v>
+        <v>1.6371287435893985E-5</v>
       </c>
       <c r="L5">
-        <v>6.5765629929144266E-6</v>
+        <v>1.514311019954198E-6</v>
       </c>
       <c r="M5">
-        <v>-1.1030112446794803E-5</v>
+        <v>-7.6256782466381832E-6</v>
       </c>
       <c r="N5">
-        <v>2.5615280217365409E-5</v>
+        <v>-8.8762188333170642E-7</v>
       </c>
       <c r="O5">
-        <v>2.2371872422610123E-5</v>
+        <v>3.1236057827847439E-6</v>
       </c>
       <c r="P5">
-        <v>2.7209221914715662E-4</v>
+        <v>1.9109104482408385E-5</v>
       </c>
       <c r="Q5">
-        <v>1.2313494079948957E-5</v>
+        <v>2.2553347162354603E-6</v>
       </c>
       <c r="R5">
-        <v>1.2269489782068251E-4</v>
+        <v>-5.1602215853656616E-6</v>
       </c>
       <c r="S5">
-        <v>-1.8714320074651077E-4</v>
+        <v>4.7672448034131944E-6</v>
       </c>
       <c r="T5">
-        <v>-9.8241641799995036E-5</v>
+        <v>2.7157191047452039E-5</v>
       </c>
       <c r="U5">
-        <v>-5.9523634846229831E-5</v>
+        <v>-1.5004625773108157E-5</v>
       </c>
       <c r="V5">
-        <v>2.1986294995192217E-5</v>
+        <v>2.4240899710838761E-6</v>
       </c>
       <c r="W5">
-        <v>3.8236620791673429E-6</v>
+        <v>3.7235906919433749E-6</v>
       </c>
       <c r="X5">
-        <v>-8.6505127803494254E-5</v>
+        <v>-1.8979050568965271E-5</v>
       </c>
       <c r="Y5">
-        <v>-1.3023542989722944E-4</v>
+        <v>-1.5638874454195498E-5</v>
       </c>
       <c r="Z5">
-        <v>-1.3882889392827877E-3</v>
+        <v>-2.5494856565214758E-4</v>
       </c>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>26</v>
-      </c>
-      <c r="B6" s="4">
-        <v>-0.12870404310936376</v>
+        <v>25</v>
+      </c>
+      <c r="B6">
+        <v>-0.46054914714897688</v>
       </c>
       <c r="C6">
-        <v>-1.1041942892118178E-4</v>
+        <v>-9.597813122328458E-6</v>
       </c>
       <c r="D6">
-        <v>2.0896688269028533E-5</v>
+        <v>-4.2604330610438563E-6</v>
       </c>
       <c r="E6">
-        <v>-2.6082323092895617E-7</v>
+        <v>1.0284165938616245E-8</v>
       </c>
       <c r="F6">
-        <v>1.0734375848985645E-3</v>
+        <v>2.4215546202781187E-4</v>
       </c>
       <c r="G6">
-        <v>2.1129750788040132E-3</v>
+        <v>4.7731045057716856E-4</v>
       </c>
       <c r="H6">
-        <v>-6.7964394361190515E-6</v>
+        <v>1.171458200359006E-5</v>
       </c>
       <c r="I6">
-        <v>-1.7380737716333794E-5</v>
+        <v>-2.2624623537587949E-5</v>
       </c>
       <c r="J6">
-        <v>1.8072184171006369E-4</v>
+        <v>3.56012419329715E-5</v>
       </c>
       <c r="K6">
-        <v>1.8673146809732125E-5</v>
+        <v>2.325952821965816E-5</v>
       </c>
       <c r="L6">
-        <v>-1.5282205461530376E-4</v>
+        <v>-7.294162620517399E-6</v>
       </c>
       <c r="M6">
-        <v>-7.6703185975858209E-5</v>
+        <v>-2.1893803838591788E-6</v>
       </c>
       <c r="N6">
-        <v>2.0355774682455118E-5</v>
+        <v>1.7852674436351518E-5</v>
       </c>
       <c r="O6">
-        <v>1.8214459153904922E-5</v>
+        <v>7.258188002743172E-6</v>
       </c>
       <c r="P6">
-        <v>2.9571721484926926E-4</v>
+        <v>3.2937451203749724E-5</v>
       </c>
       <c r="Q6">
-        <v>2.1281815203028334E-5</v>
+        <v>4.2167095559251978E-6</v>
       </c>
       <c r="R6">
-        <v>1.7415127400607845E-4</v>
+        <v>1.9280716547261242E-6</v>
       </c>
       <c r="S6">
-        <v>-1.780855412694877E-4</v>
+        <v>-6.3352104005031447E-6</v>
       </c>
       <c r="T6">
-        <v>-1.4103473078683497E-4</v>
+        <v>1.0664882092616877E-5</v>
       </c>
       <c r="U6">
-        <v>-1.1157675396371362E-4</v>
+        <v>-2.9678212976187843E-5</v>
       </c>
       <c r="V6">
-        <v>6.7610349847862605E-5</v>
+        <v>8.1225176297103905E-6</v>
       </c>
       <c r="W6">
-        <v>8.6731768599810364E-6</v>
+        <v>6.6855247055917278E-6</v>
       </c>
       <c r="X6">
-        <v>-1.4161359383604117E-4</v>
+        <v>4.3379863333244323E-6</v>
       </c>
       <c r="Y6">
-        <v>-1.2300805045074105E-4</v>
+        <v>3.6965918365123473E-6</v>
       </c>
       <c r="Z6">
-        <v>-1.7516767670310801E-3</v>
+        <v>-3.2518717977771095E-4</v>
       </c>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>27</v>
-      </c>
-      <c r="B7" s="4">
-        <v>-9.8061738900925167E-3</v>
+        <v>26</v>
+      </c>
+      <c r="B7">
+        <v>0.31929121243778219</v>
       </c>
       <c r="C7">
-        <v>2.3926617753739894E-5</v>
+        <v>-2.6478409920186573E-5</v>
       </c>
       <c r="D7">
-        <v>1.2532664492259226E-4</v>
+        <v>4.3106878982547857E-5</v>
       </c>
       <c r="E7">
-        <v>-1.0542185214877344E-6</v>
+        <v>-3.0643102239210047E-7</v>
       </c>
       <c r="F7">
-        <v>2.480932595793346E-4</v>
+        <v>-1.952976663859173E-6</v>
       </c>
       <c r="G7">
-        <v>-6.7964394361190515E-6</v>
+        <v>1.171458200359006E-5</v>
       </c>
       <c r="H7">
-        <v>7.7388528488616919E-3</v>
+        <v>3.6660996088805631E-3</v>
       </c>
       <c r="I7">
-        <v>1.6203312486933364E-3</v>
+        <v>4.0110842108957961E-4</v>
       </c>
       <c r="J7">
-        <v>1.5924081783739484E-3</v>
+        <v>3.1646614058764092E-4</v>
       </c>
       <c r="K7">
-        <v>4.4819071621424769E-4</v>
+        <v>1.0602646418700665E-4</v>
       </c>
       <c r="L7">
-        <v>1.0461928419654767E-4</v>
+        <v>1.7909588040549923E-6</v>
       </c>
       <c r="M7">
-        <v>3.6682615579711328E-4</v>
+        <v>1.5394003251831365E-4</v>
       </c>
       <c r="N7">
-        <v>8.9569415133233157E-6</v>
+        <v>-1.8690582271492191E-6</v>
       </c>
       <c r="O7">
-        <v>2.5729302500337168E-4</v>
+        <v>3.7708234103006476E-5</v>
       </c>
       <c r="P7">
-        <v>3.8243050074444028E-5</v>
+        <v>-3.8117145037284267E-5</v>
       </c>
       <c r="Q7">
-        <v>-4.389228717709255E-5</v>
+        <v>1.4560022957984698E-5</v>
       </c>
       <c r="R7">
-        <v>1.0957274743964886E-4</v>
+        <v>-1.3364368590208136E-5</v>
       </c>
       <c r="S7">
-        <v>-1.8674932461552169E-4</v>
+        <v>-9.0924029602153884E-5</v>
       </c>
       <c r="T7">
-        <v>-2.8735762084782478E-4</v>
+        <v>-1.3540478251042386E-4</v>
       </c>
       <c r="U7">
-        <v>-1.2146006919084207E-4</v>
+        <v>-7.9777646237705769E-5</v>
       </c>
       <c r="V7">
-        <v>1.7266588027294548E-5</v>
+        <v>-1.215617897776548E-4</v>
       </c>
       <c r="W7">
-        <v>5.7238100108621354E-6</v>
+        <v>4.4544904443447042E-6</v>
       </c>
       <c r="X7">
-        <v>-2.0487191327827996E-4</v>
+        <v>-6.2919010088083186E-5</v>
       </c>
       <c r="Y7">
-        <v>-1.7041217826349315E-4</v>
+        <v>-3.6819404043739331E-5</v>
       </c>
       <c r="Z7">
-        <v>-5.4677183572386127E-3</v>
+        <v>-1.8388406350030445E-3</v>
       </c>
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>28</v>
-      </c>
-      <c r="B8" s="4">
-        <v>8.5251364722751341E-2</v>
+        <v>27</v>
+      </c>
+      <c r="B8">
+        <v>5.4571868434479899E-2</v>
       </c>
       <c r="C8">
-        <v>4.1345360460427807E-5</v>
+        <v>4.020762171304243E-6</v>
       </c>
       <c r="D8">
-        <v>2.7210431392616574E-5</v>
+        <v>-1.5767788282585176E-6</v>
       </c>
       <c r="E8">
-        <v>-2.4625110527586493E-7</v>
+        <v>3.2528299305907866E-9</v>
       </c>
       <c r="F8">
-        <v>2.5341839490375978E-5</v>
+        <v>-6.3477558574498811E-6</v>
       </c>
       <c r="G8">
-        <v>-1.7380737716333794E-5</v>
+        <v>-2.2624623537587949E-5</v>
       </c>
       <c r="H8">
-        <v>1.6203312486933364E-3</v>
+        <v>4.0110842108957961E-4</v>
       </c>
       <c r="I8">
-        <v>1.8493293060547126E-3</v>
+        <v>7.9028308985543149E-4</v>
       </c>
       <c r="J8">
-        <v>1.5452388929371645E-3</v>
+        <v>5.3393204174408571E-4</v>
       </c>
       <c r="K8">
-        <v>2.2190614749332117E-5</v>
+        <v>3.5849768457517985E-5</v>
       </c>
       <c r="L8">
-        <v>8.4168894894211439E-5</v>
+        <v>2.2163517369200827E-5</v>
       </c>
       <c r="M8">
-        <v>1.1086297911880815E-4</v>
+        <v>5.171597621960155E-5</v>
       </c>
       <c r="N8">
-        <v>1.2640233518600844E-4</v>
+        <v>2.730596434654627E-6</v>
       </c>
       <c r="O8">
-        <v>1.9361214300540549E-4</v>
+        <v>4.0611073912800584E-5</v>
       </c>
       <c r="P8">
-        <v>1.904642038395854E-5</v>
+        <v>-9.227311115639434E-6</v>
       </c>
       <c r="Q8">
-        <v>-1.2476127105941895E-5</v>
+        <v>1.2525970276300819E-5</v>
       </c>
       <c r="R8">
-        <v>-1.563756334544092E-5</v>
+        <v>-5.0469434790101337E-6</v>
       </c>
       <c r="S8">
-        <v>-1.2564809291153308E-4</v>
+        <v>-8.3049760382235418E-5</v>
       </c>
       <c r="T8">
-        <v>-1.8833404912447105E-4</v>
+        <v>-5.2284120763103445E-5</v>
       </c>
       <c r="U8">
-        <v>-8.9018456995237016E-5</v>
+        <v>-1.3792891991894023E-5</v>
       </c>
       <c r="V8">
-        <v>5.0609610093509095E-6</v>
+        <v>-3.8299450313766711E-5</v>
       </c>
       <c r="W8">
-        <v>3.9283034091352527E-7</v>
+        <v>1.1635940812401434E-6</v>
       </c>
       <c r="X8">
-        <v>-1.4779442285337572E-4</v>
+        <v>1.0142510176636436E-5</v>
       </c>
       <c r="Y8">
-        <v>-8.2491207183308345E-5</v>
+        <v>-4.4142509780008353E-6</v>
       </c>
       <c r="Z8">
-        <v>-2.6610883106909845E-3</v>
+        <v>-4.895820767468205E-4</v>
       </c>
     </row>
     <row r="9" spans="1:26" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>29</v>
-      </c>
-      <c r="B9" s="4">
-        <v>2.1324978870012629E-2</v>
+        <v>28</v>
+      </c>
+      <c r="B9">
+        <v>0.15457709618727533</v>
       </c>
       <c r="C9">
-        <v>1.1812306491909035E-4</v>
+        <v>-6.5351464051536813E-5</v>
       </c>
       <c r="D9">
-        <v>1.4538950345677318E-4</v>
+        <v>4.6048409507209911E-6</v>
       </c>
       <c r="E9">
-        <v>-1.9126147150741681E-6</v>
+        <v>-1.3022831994831984E-7</v>
       </c>
       <c r="F9">
-        <v>1.4191679568151014E-4</v>
+        <v>7.8735653036820092E-6</v>
       </c>
       <c r="G9">
-        <v>1.8072184171006369E-4</v>
+        <v>3.56012419329715E-5</v>
       </c>
       <c r="H9">
-        <v>1.5924081783739484E-3</v>
+        <v>3.1646614058764092E-4</v>
       </c>
       <c r="I9">
-        <v>1.5452388929371645E-3</v>
+        <v>5.3393204174408571E-4</v>
       </c>
       <c r="J9">
-        <v>4.5006192393169725E-3</v>
+        <v>8.8842999599979299E-4</v>
       </c>
       <c r="K9">
-        <v>8.9944985331068478E-5</v>
+        <v>7.2866580181396432E-5</v>
       </c>
       <c r="L9">
-        <v>2.8384233521615905E-4</v>
+        <v>4.2944451227327917E-5</v>
       </c>
       <c r="M9">
-        <v>1.4607422224815125E-4</v>
+        <v>6.0366541645943142E-5</v>
       </c>
       <c r="N9">
-        <v>9.7407784196778217E-5</v>
+        <v>-1.8673498190741961E-7</v>
       </c>
       <c r="O9">
-        <v>2.0300420819357678E-4</v>
+        <v>4.3841213741730758E-5</v>
       </c>
       <c r="P9">
-        <v>2.7483153931976995E-5</v>
+        <v>-4.7127598030577151E-6</v>
       </c>
       <c r="Q9">
-        <v>-1.1003625606446275E-5</v>
+        <v>1.0657923773134315E-5</v>
       </c>
       <c r="R9">
-        <v>-1.0976841387612575E-5</v>
+        <v>6.3885588759638118E-6</v>
       </c>
       <c r="S9">
-        <v>-4.2312371119459244E-5</v>
+        <v>-2.8770885992555754E-5</v>
       </c>
       <c r="T9">
-        <v>-3.9263538518019916E-4</v>
+        <v>-8.946415101226035E-6</v>
       </c>
       <c r="U9">
-        <v>-1.2445994927460385E-4</v>
+        <v>-3.8003857750089267E-6</v>
       </c>
       <c r="V9">
-        <v>-4.6618273654365613E-5</v>
+        <v>-1.042660303580964E-5</v>
       </c>
       <c r="W9">
-        <v>-1.0407116605641399E-5</v>
+        <v>7.3784239535592123E-7</v>
       </c>
       <c r="X9">
-        <v>7.4400115263890303E-5</v>
+        <v>3.5239996712606064E-6</v>
       </c>
       <c r="Y9">
-        <v>-2.4825393044161474E-5</v>
+        <v>-5.8867787595129621E-6</v>
       </c>
       <c r="Z9">
-        <v>-4.4637914327299915E-3</v>
+        <v>-4.8248553596203848E-4</v>
       </c>
     </row>
     <row r="10" spans="1:26" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>30</v>
-      </c>
-      <c r="B10" s="4">
-        <v>-9.6034372623850131E-2</v>
+        <v>29</v>
+      </c>
+      <c r="B10">
+        <v>9.288740528995091E-3</v>
       </c>
       <c r="C10">
-        <v>2.1290690263527561E-5</v>
+        <v>1.7352902364988686E-5</v>
       </c>
       <c r="D10">
-        <v>8.7815220380825715E-6</v>
+        <v>2.1638555039413422E-6</v>
       </c>
       <c r="E10">
-        <v>7.4340317162795604E-8</v>
+        <v>9.6805066140436183E-9</v>
       </c>
       <c r="F10">
-        <v>3.6738752805370016E-5</v>
+        <v>1.6371287435893985E-5</v>
       </c>
       <c r="G10">
-        <v>1.8673146809732125E-5</v>
+        <v>2.325952821965816E-5</v>
       </c>
       <c r="H10">
-        <v>4.4819071621424769E-4</v>
+        <v>1.0602646418700665E-4</v>
       </c>
       <c r="I10">
-        <v>2.2190614749332117E-5</v>
+        <v>3.5849768457517985E-5</v>
       </c>
       <c r="J10">
-        <v>8.9944985331068478E-5</v>
+        <v>7.2866580181396432E-5</v>
       </c>
       <c r="K10">
-        <v>1.5677376201955568E-3</v>
+        <v>5.3202474407568223E-4</v>
       </c>
       <c r="L10">
-        <v>8.1901905611024952E-4</v>
+        <v>1.416057579804629E-4</v>
       </c>
       <c r="M10">
-        <v>9.7344139533651441E-4</v>
+        <v>2.2873676240028011E-4</v>
       </c>
       <c r="N10">
-        <v>-1.9240833091113939E-5</v>
+        <v>3.7032576328265409E-7</v>
       </c>
       <c r="O10">
-        <v>1.2935998733076218E-5</v>
+        <v>1.1075025425434518E-6</v>
       </c>
       <c r="P10">
-        <v>-4.7986906572309055E-5</v>
+        <v>-7.269451496015692E-6</v>
       </c>
       <c r="Q10">
-        <v>-5.8719200983573051E-6</v>
+        <v>-3.0704882394088135E-6</v>
       </c>
       <c r="R10">
-        <v>-5.9817895815331406E-5</v>
+        <v>5.0586784719691902E-6</v>
       </c>
       <c r="S10">
-        <v>1.0175382215642199E-4</v>
+        <v>2.0139724151731897E-5</v>
       </c>
       <c r="T10">
-        <v>-7.4097733710036214E-5</v>
+        <v>3.7953935838534291E-6</v>
       </c>
       <c r="U10">
-        <v>-4.5904528581284685E-5</v>
+        <v>-1.3108287156991691E-5</v>
       </c>
       <c r="V10">
-        <v>-5.9798794095122801E-5</v>
+        <v>-8.8345035922361259E-6</v>
       </c>
       <c r="W10">
-        <v>-3.7525721659891321E-6</v>
+        <v>3.5266717129359311E-7</v>
       </c>
       <c r="X10">
-        <v>2.0010662561979991E-4</v>
+        <v>4.0265629473044051E-5</v>
       </c>
       <c r="Y10">
-        <v>1.8473476141887287E-4</v>
+        <v>1.9517675162887373E-5</v>
       </c>
       <c r="Z10">
-        <v>-1.3611217807710451E-3</v>
+        <v>-3.6376838557618761E-4</v>
       </c>
     </row>
     <row r="11" spans="1:26" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>31</v>
-      </c>
-      <c r="B11" s="4">
-        <v>2.280846900442721E-2</v>
+        <v>30</v>
+      </c>
+      <c r="B11">
+        <v>5.7208771229707779E-2</v>
       </c>
       <c r="C11">
-        <v>1.4136078321906563E-4</v>
+        <v>2.1380422688521254E-5</v>
       </c>
       <c r="D11">
-        <v>9.6829355437907016E-5</v>
+        <v>1.8430983023351977E-5</v>
       </c>
       <c r="E11">
-        <v>-8.8391568942679372E-7</v>
+        <v>-1.5145773318601679E-7</v>
       </c>
       <c r="F11">
-        <v>6.5765629929144266E-6</v>
+        <v>1.514311019954198E-6</v>
       </c>
       <c r="G11">
-        <v>-1.5282205461530376E-4</v>
+        <v>-7.294162620517399E-6</v>
       </c>
       <c r="H11">
-        <v>1.0461928419654767E-4</v>
+        <v>1.7909588040549923E-6</v>
       </c>
       <c r="I11">
-        <v>8.4168894894211439E-5</v>
+        <v>2.2163517369200827E-5</v>
       </c>
       <c r="J11">
-        <v>2.8384233521615905E-4</v>
+        <v>4.2944451227327917E-5</v>
       </c>
       <c r="K11">
-        <v>8.1901905611024952E-4</v>
+        <v>1.416057579804629E-4</v>
       </c>
       <c r="L11">
-        <v>1.6219684454342549E-3</v>
+        <v>2.98605076330692E-4</v>
       </c>
       <c r="M11">
-        <v>8.6240133115083099E-4</v>
+        <v>1.5897188280794428E-4</v>
       </c>
       <c r="N11">
-        <v>-5.2403165446465889E-6</v>
+        <v>4.0249384334069529E-6</v>
       </c>
       <c r="O11">
-        <v>1.2626907106087651E-5</v>
+        <v>9.3497848502063556E-7</v>
       </c>
       <c r="P11">
-        <v>-1.0012264019466921E-4</v>
+        <v>-1.1794238899907915E-5</v>
       </c>
       <c r="Q11">
-        <v>6.5845791926000732E-6</v>
+        <v>-1.166371621226632E-6</v>
       </c>
       <c r="R11">
-        <v>-5.463948481952371E-5</v>
+        <v>1.2212824910302349E-5</v>
       </c>
       <c r="S11">
-        <v>-4.1055095720955595E-5</v>
+        <v>4.7274162984353371E-7</v>
       </c>
       <c r="T11">
-        <v>-1.8903502955310014E-5</v>
+        <v>2.0264800048956644E-6</v>
       </c>
       <c r="U11">
-        <v>3.2915190851703262E-5</v>
+        <v>4.7910188245123991E-6</v>
       </c>
       <c r="V11">
-        <v>8.590314213695121E-5</v>
+        <v>-5.0043481363612593E-6</v>
       </c>
       <c r="W11">
-        <v>-5.002102684185811E-6</v>
+        <v>-2.2064054999403602E-6</v>
       </c>
       <c r="X11">
-        <v>1.4630818488771077E-4</v>
+        <v>-5.2722229684035193E-6</v>
       </c>
       <c r="Y11">
-        <v>6.6350580178099668E-5</v>
+        <v>5.9386948000614346E-6</v>
       </c>
       <c r="Z11">
-        <v>-3.2882069727189294E-3</v>
+        <v>-6.5081675067867289E-4</v>
       </c>
     </row>
     <row r="12" spans="1:26" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>32</v>
-      </c>
-      <c r="B12" s="4">
-        <v>0.26741494989146103</v>
+        <v>31</v>
+      </c>
+      <c r="B12">
+        <v>0.45676506448444026</v>
       </c>
       <c r="C12">
-        <v>3.9559334507008163E-4</v>
+        <v>9.3408167998449554E-5</v>
       </c>
       <c r="D12">
-        <v>8.1038298294644484E-6</v>
+        <v>3.7046615812273459E-6</v>
       </c>
       <c r="E12">
-        <v>7.4115891119072505E-8</v>
+        <v>7.022253081E-9</v>
       </c>
       <c r="F12">
-        <v>-1.1030112446794803E-5</v>
+        <v>-7.6256782466381832E-6</v>
       </c>
       <c r="G12">
-        <v>-7.6703185975858209E-5</v>
+        <v>-2.1893803838591788E-6</v>
       </c>
       <c r="H12">
-        <v>3.6682615579711328E-4</v>
+        <v>1.5394003251831365E-4</v>
       </c>
       <c r="I12">
-        <v>1.1086297911880815E-4</v>
+        <v>5.171597621960155E-5</v>
       </c>
       <c r="J12">
-        <v>1.4607422224815125E-4</v>
+        <v>6.0366541645943142E-5</v>
       </c>
       <c r="K12">
-        <v>9.7344139533651441E-4</v>
+        <v>2.2873676240028011E-4</v>
       </c>
       <c r="L12">
-        <v>8.6240133115083099E-4</v>
+        <v>1.5897188280794428E-4</v>
       </c>
       <c r="M12">
-        <v>1.9174979005975388E-3</v>
+        <v>3.8558872008436005E-3</v>
       </c>
       <c r="N12">
-        <v>3.5285687823458664E-6</v>
+        <v>-4.0609504063515022E-7</v>
       </c>
       <c r="O12">
-        <v>-1.1725244156528871E-5</v>
+        <v>-2.0496276987463907E-6</v>
       </c>
       <c r="P12">
-        <v>-1.5782965813853668E-4</v>
+        <v>-2.20796419504668E-5</v>
       </c>
       <c r="Q12">
-        <v>3.9970748210134486E-6</v>
+        <v>2.0234623745312128E-6</v>
       </c>
       <c r="R12">
-        <v>-1.4472670299373481E-5</v>
+        <v>7.1920855890320994E-6</v>
       </c>
       <c r="S12">
-        <v>6.221047669368446E-6</v>
+        <v>-1.8701848320600137E-5</v>
       </c>
       <c r="T12">
-        <v>3.3390118148220595E-6</v>
+        <v>-1.1458957765401003E-5</v>
       </c>
       <c r="U12">
-        <v>6.0961263863224647E-5</v>
+        <v>3.3637588899615206E-6</v>
       </c>
       <c r="V12">
-        <v>3.4232478111005194E-5</v>
+        <v>-3.9812254343785133E-5</v>
       </c>
       <c r="W12">
-        <v>-1.5425744178756167E-5</v>
+        <v>-1.8336964371445136E-6</v>
       </c>
       <c r="X12">
-        <v>1.1507275028427592E-4</v>
+        <v>-1.7521861695383284E-5</v>
       </c>
       <c r="Y12">
-        <v>9.2035613564749757E-5</v>
+        <v>-4.957584749059246E-5</v>
       </c>
       <c r="Z12">
-        <v>-1.2818561877108708E-3</v>
+        <v>-3.953389418885671E-4</v>
       </c>
     </row>
     <row r="13" spans="1:26" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>18</v>
-      </c>
-      <c r="B13" s="4">
-        <v>-7.7528342995605119E-3</v>
+        <v>17</v>
+      </c>
+      <c r="B13">
+        <v>1.2068556567329228E-2</v>
       </c>
       <c r="C13">
-        <v>8.263790303207261E-6</v>
+        <v>-7.4713184851774906E-6</v>
       </c>
       <c r="D13">
-        <v>1.9440038454409223E-5</v>
+        <v>-6.0586291069508023E-7</v>
       </c>
       <c r="E13">
-        <v>-1.2270871511615015E-7</v>
+        <v>1.8569552925896075E-8</v>
       </c>
       <c r="F13">
-        <v>2.5615280217365409E-5</v>
+        <v>-8.8762188333170642E-7</v>
       </c>
       <c r="G13">
-        <v>2.0355774682455118E-5</v>
+        <v>1.7852674436351518E-5</v>
       </c>
       <c r="H13">
-        <v>8.9569415133233157E-6</v>
+        <v>-1.8690582271492191E-6</v>
       </c>
       <c r="I13">
-        <v>1.2640233518600844E-4</v>
+        <v>2.730596434654627E-6</v>
       </c>
       <c r="J13">
-        <v>9.7407784196778217E-5</v>
+        <v>-1.8673498190741961E-7</v>
       </c>
       <c r="K13">
-        <v>-1.9240833091113939E-5</v>
+        <v>3.7032576328265409E-7</v>
       </c>
       <c r="L13">
-        <v>-5.2403165446465889E-6</v>
+        <v>4.0249384334069529E-6</v>
       </c>
       <c r="M13">
-        <v>3.5285687823458664E-6</v>
+        <v>-4.0609504063515022E-7</v>
       </c>
       <c r="N13">
-        <v>3.0659961120835938E-4</v>
+        <v>7.5956385138458292E-5</v>
       </c>
       <c r="O13">
-        <v>-1.1469035361401925E-7</v>
+        <v>-8.6083233923995043E-7</v>
       </c>
       <c r="P13">
-        <v>3.3870416484631802E-5</v>
+        <v>-1.8341704692856293E-6</v>
       </c>
       <c r="Q13">
-        <v>-1.0060791849923822E-5</v>
+        <v>6.0394927083183935E-8</v>
       </c>
       <c r="R13">
-        <v>-9.1027207010532449E-5</v>
+        <v>4.1564134615272824E-7</v>
       </c>
       <c r="S13">
-        <v>-2.4843403507190584E-5</v>
+        <v>-1.7666657750077118E-6</v>
       </c>
       <c r="T13">
-        <v>1.3084655330368108E-8</v>
+        <v>9.2376861697027288E-6</v>
       </c>
       <c r="U13">
-        <v>1.0258318133512287E-6</v>
+        <v>-6.0835156215599507E-6</v>
       </c>
       <c r="V13">
-        <v>1.3056585895025399E-5</v>
+        <v>-2.6916219119545843E-6</v>
       </c>
       <c r="W13">
-        <v>-3.7508758724344386E-6</v>
+        <v>-1.1648919099622115E-6</v>
       </c>
       <c r="X13">
-        <v>-1.2180728347892396E-5</v>
+        <v>3.2863141718789644E-6</v>
       </c>
       <c r="Y13">
-        <v>-5.0164733857542364E-5</v>
+        <v>3.0354886025044072E-5</v>
       </c>
       <c r="Z13">
-        <v>-1.6751956709370778E-3</v>
+        <v>-2.9142971269760113E-4</v>
       </c>
     </row>
     <row r="14" spans="1:26" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>19</v>
-      </c>
-      <c r="B14" s="4">
-        <v>1.7423236427559431E-2</v>
+        <v>18</v>
+      </c>
+      <c r="B14">
+        <v>8.6261798412987159E-3</v>
       </c>
       <c r="C14">
-        <v>-3.4810703238267465E-5</v>
+        <v>-4.5434251341367233E-6</v>
       </c>
       <c r="D14">
-        <v>4.3904665657726409E-6</v>
+        <v>-5.5322703420250999E-7</v>
       </c>
       <c r="E14">
-        <v>-3.5907709889012168E-8</v>
+        <v>7.1156786327649309E-9</v>
       </c>
       <c r="F14">
-        <v>2.2371872422610123E-5</v>
+        <v>3.1236057827847439E-6</v>
       </c>
       <c r="G14">
-        <v>1.8214459153904922E-5</v>
+        <v>7.258188002743172E-6</v>
       </c>
       <c r="H14">
-        <v>2.5729302500337168E-4</v>
+        <v>3.7708234103006476E-5</v>
       </c>
       <c r="I14">
-        <v>1.9361214300540549E-4</v>
+        <v>4.0611073912800584E-5</v>
       </c>
       <c r="J14">
-        <v>2.0300420819357678E-4</v>
+        <v>4.3841213741730758E-5</v>
       </c>
       <c r="K14">
-        <v>1.2935998733076218E-5</v>
+        <v>1.1075025425434518E-6</v>
       </c>
       <c r="L14">
-        <v>1.2626907106087651E-5</v>
+        <v>9.3497848502063556E-7</v>
       </c>
       <c r="M14">
-        <v>-1.1725244156528871E-5</v>
+        <v>-2.0496276987463907E-6</v>
       </c>
       <c r="N14">
-        <v>-1.1469035361401925E-7</v>
+        <v>-8.6083233923995043E-7</v>
       </c>
       <c r="O14">
-        <v>8.7235659233855981E-5</v>
+        <v>1.3958700372898041E-5</v>
       </c>
       <c r="P14">
-        <v>-2.8750510728788384E-6</v>
+        <v>-1.332313822314801E-7</v>
       </c>
       <c r="Q14">
-        <v>-5.5073276741396366E-5</v>
+        <v>-6.9366381727496841E-6</v>
       </c>
       <c r="R14">
-        <v>1.6528010135882261E-6</v>
+        <v>-2.3991980362991465E-7</v>
       </c>
       <c r="S14">
-        <v>-1.9623335413979399E-5</v>
+        <v>-4.3989348294575345E-6</v>
       </c>
       <c r="T14">
-        <v>-3.5543902289093974E-5</v>
+        <v>-6.0324429002672891E-7</v>
       </c>
       <c r="U14">
-        <v>-7.5716303166748302E-6</v>
+        <v>-3.6750950325146008E-6</v>
       </c>
       <c r="V14">
-        <v>9.6522063377708391E-6</v>
+        <v>-3.3017021870913987E-6</v>
       </c>
       <c r="W14">
-        <v>-9.2060685244680649E-8</v>
+        <v>1.1588106554259771E-7</v>
       </c>
       <c r="X14">
-        <v>-2.1939000935732639E-5</v>
+        <v>-2.3916006191006495E-8</v>
       </c>
       <c r="Y14">
-        <v>-1.4351757241395973E-5</v>
+        <v>-1.1758206044810254E-7</v>
       </c>
       <c r="Z14">
-        <v>-3.4124106226029896E-4</v>
+        <v>-4.5855470787625464E-5</v>
       </c>
     </row>
     <row r="15" spans="1:26" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>20</v>
-      </c>
-      <c r="B15" s="4">
-        <v>1.4831210733588338</v>
+        <v>19</v>
+      </c>
+      <c r="B15">
+        <v>1.540404311048917</v>
       </c>
       <c r="C15">
-        <v>3.4253593797670524E-5</v>
+        <v>-5.3018050143326489E-6</v>
       </c>
       <c r="D15">
-        <v>2.1875134260745076E-6</v>
+        <v>-3.9441584444811019E-6</v>
       </c>
       <c r="E15">
-        <v>-3.4445761935874338E-8</v>
+        <v>3.0517519950605474E-8</v>
       </c>
       <c r="F15">
-        <v>2.7209221914715662E-4</v>
+        <v>1.9109104482408385E-5</v>
       </c>
       <c r="G15">
-        <v>2.9571721484926926E-4</v>
+        <v>3.2937451203749724E-5</v>
       </c>
       <c r="H15">
-        <v>3.8243050074444028E-5</v>
+        <v>-3.8117145037284267E-5</v>
       </c>
       <c r="I15">
-        <v>1.904642038395854E-5</v>
+        <v>-9.227311115639434E-6</v>
       </c>
       <c r="J15">
-        <v>2.7483153931976995E-5</v>
+        <v>-4.7127598030577151E-6</v>
       </c>
       <c r="K15">
-        <v>-4.7986906572309055E-5</v>
+        <v>-7.269451496015692E-6</v>
       </c>
       <c r="L15">
-        <v>-1.0012264019466921E-4</v>
+        <v>-1.1794238899907915E-5</v>
       </c>
       <c r="M15">
-        <v>-1.5782965813853668E-4</v>
+        <v>-2.20796419504668E-5</v>
       </c>
       <c r="N15">
-        <v>3.3870416484631802E-5</v>
+        <v>-1.8341704692856293E-6</v>
       </c>
       <c r="O15">
-        <v>-2.8750510728788384E-6</v>
+        <v>-1.332313822314801E-7</v>
       </c>
       <c r="P15">
-        <v>2.2117457632896634E-3</v>
+        <v>2.7327067218493645E-4</v>
       </c>
       <c r="Q15">
-        <v>-1.1852022061469748E-5</v>
+        <v>4.3288063539600958E-7</v>
       </c>
       <c r="R15">
-        <v>-1.2422181125236818E-3</v>
+        <v>-2.2617647347189233E-4</v>
       </c>
       <c r="S15">
-        <v>-2.1227884036241251E-4</v>
+        <v>-6.2922755281169965E-7</v>
       </c>
       <c r="T15">
-        <v>-1.4067455843475759E-4</v>
+        <v>-1.639563847920086E-5</v>
       </c>
       <c r="U15">
-        <v>4.9552684978026816E-6</v>
+        <v>5.4056104605772705E-6</v>
       </c>
       <c r="V15">
-        <v>-1.3190455124847673E-4</v>
+        <v>5.8503664066349853E-6</v>
       </c>
       <c r="W15">
-        <v>-7.3438250366484364E-7</v>
+        <v>6.4482022512958328E-7</v>
       </c>
       <c r="X15">
-        <v>-2.8378356873044427E-4</v>
+        <v>-1.3119722814263319E-5</v>
       </c>
       <c r="Y15">
-        <v>-1.399591403825416E-4</v>
+        <v>-4.0293955958587885E-5</v>
       </c>
       <c r="Z15">
-        <v>-5.7394918700289638E-4</v>
+        <v>6.765497780212475E-5</v>
       </c>
     </row>
     <row r="16" spans="1:26" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>33</v>
-      </c>
-      <c r="B16" s="4">
-        <v>-2.6064242270854563E-3</v>
+        <v>32</v>
+      </c>
+      <c r="B16">
+        <v>9.9292150843671677E-3</v>
       </c>
       <c r="C16">
-        <v>7.0746500088472745E-6</v>
+        <v>-4.4326794273329E-6</v>
       </c>
       <c r="D16">
-        <v>-7.1366978749782726E-6</v>
+        <v>-2.6338406783097621E-6</v>
       </c>
       <c r="E16">
-        <v>6.6367420612143924E-8</v>
+        <v>2.6034399810427398E-8</v>
       </c>
       <c r="F16">
-        <v>1.2313494079948957E-5</v>
+        <v>2.2553347162354603E-6</v>
       </c>
       <c r="G16">
-        <v>2.1281815203028334E-5</v>
+        <v>4.2167095559251978E-6</v>
       </c>
       <c r="H16">
-        <v>-4.389228717709255E-5</v>
+        <v>1.4560022957984698E-5</v>
       </c>
       <c r="I16">
-        <v>-1.2476127105941895E-5</v>
+        <v>1.2525970276300819E-5</v>
       </c>
       <c r="J16">
-        <v>-1.1003625606446275E-5</v>
+        <v>1.0657923773134315E-5</v>
       </c>
       <c r="K16">
-        <v>-5.8719200983573051E-6</v>
+        <v>-3.0704882394088135E-6</v>
       </c>
       <c r="L16">
-        <v>6.5845791926000732E-6</v>
+        <v>-1.166371621226632E-6</v>
       </c>
       <c r="M16">
-        <v>3.9970748210134486E-6</v>
+        <v>2.0234623745312128E-6</v>
       </c>
       <c r="N16">
-        <v>-1.0060791849923822E-5</v>
+        <v>6.0394927083183935E-8</v>
       </c>
       <c r="O16">
-        <v>-5.5073276741396366E-5</v>
+        <v>-6.9366381727496841E-6</v>
       </c>
       <c r="P16">
-        <v>-1.1852022061469748E-5</v>
+        <v>4.3288063539600958E-7</v>
       </c>
       <c r="Q16">
-        <v>6.3107266582559349E-5</v>
+        <v>1.1087942844686311E-5</v>
       </c>
       <c r="R16">
-        <v>4.2169214247192953E-6</v>
+        <v>-4.222420066559246E-7</v>
       </c>
       <c r="S16">
-        <v>2.4209763341831993E-5</v>
+        <v>1.7760538452546029E-6</v>
       </c>
       <c r="T16">
-        <v>1.9571674622286446E-5</v>
+        <v>-4.7469728653608163E-7</v>
       </c>
       <c r="U16">
-        <v>7.662239660605457E-6</v>
+        <v>1.4154339307565149E-6</v>
       </c>
       <c r="V16">
-        <v>6.8438667247680469E-6</v>
+        <v>1.0676656748794851E-7</v>
       </c>
       <c r="W16">
-        <v>-8.6335968130657746E-7</v>
+        <v>-3.0174565132101841E-7</v>
       </c>
       <c r="X16">
-        <v>9.5471783148785304E-6</v>
+        <v>-2.4390233059814681E-6</v>
       </c>
       <c r="Y16">
-        <v>1.7298133638593463E-5</v>
+        <v>-9.355408110667264E-7</v>
       </c>
       <c r="Z16">
-        <v>1.793518952605416E-4</v>
+        <v>3.77365783741122E-5</v>
       </c>
     </row>
     <row r="17" spans="1:26" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>34</v>
-      </c>
-      <c r="B17" s="4">
-        <v>0.56112966802657149</v>
+        <v>33</v>
+      </c>
+      <c r="B17">
+        <v>0.42243099920451438</v>
       </c>
       <c r="C17">
-        <v>2.9219204551918839E-5</v>
+        <v>2.2095690865363979E-6</v>
       </c>
       <c r="D17">
-        <v>-1.1912993313841652E-5</v>
+        <v>2.318414674662867E-6</v>
       </c>
       <c r="E17">
-        <v>7.9341648558189329E-8</v>
+        <v>-2.312981855302495E-8</v>
       </c>
       <c r="F17">
-        <v>1.2269489782068251E-4</v>
+        <v>-5.1602215853656616E-6</v>
       </c>
       <c r="G17">
-        <v>1.7415127400607845E-4</v>
+        <v>1.9280716547261242E-6</v>
       </c>
       <c r="H17">
-        <v>1.0957274743964886E-4</v>
+        <v>-1.3364368590208136E-5</v>
       </c>
       <c r="I17">
-        <v>-1.563756334544092E-5</v>
+        <v>-5.0469434790101337E-6</v>
       </c>
       <c r="J17">
-        <v>-1.0976841387612575E-5</v>
+        <v>6.3885588759638118E-6</v>
       </c>
       <c r="K17">
-        <v>-5.9817895815331406E-5</v>
+        <v>5.0586784719691902E-6</v>
       </c>
       <c r="L17">
-        <v>-5.463948481952371E-5</v>
+        <v>1.2212824910302349E-5</v>
       </c>
       <c r="M17">
-        <v>-1.4472670299373481E-5</v>
+        <v>7.1920855890320994E-6</v>
       </c>
       <c r="N17">
-        <v>-9.1027207010532449E-5</v>
+        <v>4.1564134615272824E-7</v>
       </c>
       <c r="O17">
-        <v>1.6528010135882261E-6</v>
+        <v>-2.3991980362991465E-7</v>
       </c>
       <c r="P17">
-        <v>-1.2422181125236818E-3</v>
+        <v>-2.2617647347189233E-4</v>
       </c>
       <c r="Q17">
-        <v>4.2169214247192953E-6</v>
+        <v>-4.222420066559246E-7</v>
       </c>
       <c r="R17">
-        <v>2.1149364813453295E-3</v>
+        <v>2.599872144739026E-4</v>
       </c>
       <c r="S17">
-        <v>-2.0700161206325544E-4</v>
+        <v>5.0323494135107546E-6</v>
       </c>
       <c r="T17">
-        <v>-1.4674195481609491E-4</v>
+        <v>2.0233908496501384E-5</v>
       </c>
       <c r="U17">
-        <v>-1.2535112306990689E-4</v>
+        <v>5.76237354201937E-6</v>
       </c>
       <c r="V17">
-        <v>-7.1715201520077684E-5</v>
+        <v>3.8459986493859927E-6</v>
       </c>
       <c r="W17">
-        <v>-8.5031063138964898E-7</v>
+        <v>-1.7337109460746665E-6</v>
       </c>
       <c r="X17">
-        <v>-5.4982861974611273E-5</v>
+        <v>-3.9929853980878038E-6</v>
       </c>
       <c r="Y17">
-        <v>-2.9337592473541067E-5</v>
+        <v>3.7300932876295782E-5</v>
       </c>
       <c r="Z17">
-        <v>4.9883554667337474E-4</v>
+        <v>-5.01300987493845E-5</v>
       </c>
     </row>
     <row r="18" spans="1:26" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>35</v>
       </c>
-      <c r="B18" s="4">
-        <v>5.875962510135093E-2</v>
+      <c r="B18">
+        <v>-0.40133274226472071</v>
       </c>
       <c r="C18">
-        <v>-6.8740754487054616E-5</v>
+        <v>8.9947307677456752E-6</v>
       </c>
       <c r="D18">
-        <v>-3.7250098793184365E-5</v>
+        <v>2.7607705692786672E-6</v>
       </c>
       <c r="E18">
-        <v>3.6387185071771577E-7</v>
+        <v>-2.3095984567940335E-8</v>
       </c>
       <c r="F18">
-        <v>-1.8714320074651077E-4</v>
+        <v>4.7672448034131944E-6</v>
       </c>
       <c r="G18">
-        <v>-1.780855412694877E-4</v>
+        <v>-6.3352104005031447E-6</v>
       </c>
       <c r="H18">
-        <v>-1.8674932461552169E-4</v>
+        <v>-9.0924029602153884E-5</v>
       </c>
       <c r="I18">
-        <v>-1.2564809291153308E-4</v>
+        <v>-8.3049760382235418E-5</v>
       </c>
       <c r="J18">
-        <v>-4.2312371119459244E-5</v>
+        <v>-2.8770885992555754E-5</v>
       </c>
       <c r="K18">
-        <v>1.0175382215642199E-4</v>
+        <v>2.0139724151731897E-5</v>
       </c>
       <c r="L18">
-        <v>-4.1055095720955595E-5</v>
+        <v>4.7274162984353371E-7</v>
       </c>
       <c r="M18">
-        <v>6.221047669368446E-6</v>
+        <v>-1.8701848320600137E-5</v>
       </c>
       <c r="N18">
-        <v>-2.4843403507190584E-5</v>
+        <v>-1.7666657750077118E-6</v>
       </c>
       <c r="O18">
-        <v>-1.9623335413979399E-5</v>
+        <v>-4.3989348294575345E-6</v>
       </c>
       <c r="P18">
-        <v>-2.1227884036241251E-4</v>
+        <v>-6.2922755281169965E-7</v>
       </c>
       <c r="Q18">
-        <v>2.4209763341831993E-5</v>
+        <v>1.7760538452546029E-6</v>
       </c>
       <c r="R18">
-        <v>-2.0700161206325544E-4</v>
+        <v>5.0323494135107546E-6</v>
       </c>
       <c r="S18">
-        <v>2.3545326252836143E-3</v>
+        <v>6.0768414711411239E-4</v>
       </c>
       <c r="T18">
-        <v>1.0956230346302978E-3</v>
+        <v>1.8931483189660154E-4</v>
       </c>
       <c r="U18">
-        <v>1.1083314335363493E-3</v>
+        <v>1.8895202252084745E-4</v>
       </c>
       <c r="V18">
-        <v>1.0802909365509165E-3</v>
+        <v>1.8853987798384014E-4</v>
       </c>
       <c r="W18">
-        <v>-8.0417876519968477E-6</v>
+        <v>4.7163842292647585E-7</v>
       </c>
       <c r="X18">
-        <v>5.7620726639387009E-4</v>
+        <v>1.456835199313657E-5</v>
       </c>
       <c r="Y18">
-        <v>4.509097454734146E-4</v>
+        <v>1.4970669167837116E-5</v>
       </c>
       <c r="Z18">
-        <v>2.1127715446781024E-4</v>
+        <v>-2.474971275245782E-4</v>
       </c>
     </row>
     <row r="19" spans="1:26" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>36</v>
       </c>
-      <c r="B19" s="4">
-        <v>-6.3216961994548307E-2</v>
+      <c r="B19">
+        <v>-0.37154182150032794</v>
       </c>
       <c r="C19">
-        <v>-2.5049520889910439E-5</v>
+        <v>6.12897660920804E-6</v>
       </c>
       <c r="D19">
-        <v>-2.8046201873132789E-5</v>
+        <v>1.7132150989396114E-6</v>
       </c>
       <c r="E19">
-        <v>3.1138648873248127E-7</v>
+        <v>-1.4035384774121009E-8</v>
       </c>
       <c r="F19">
-        <v>-9.8241641799995036E-5</v>
+        <v>2.7157191047452039E-5</v>
       </c>
       <c r="G19">
-        <v>-1.4103473078683497E-4</v>
+        <v>1.0664882092616877E-5</v>
       </c>
       <c r="H19">
-        <v>-2.8735762084782478E-4</v>
+        <v>-1.3540478251042386E-4</v>
       </c>
       <c r="I19">
-        <v>-1.8833404912447105E-4</v>
+        <v>-5.2284120763103445E-5</v>
       </c>
       <c r="J19">
-        <v>-3.9263538518019916E-4</v>
+        <v>-8.946415101226035E-6</v>
       </c>
       <c r="K19">
-        <v>-7.4097733710036214E-5</v>
+        <v>3.7953935838534291E-6</v>
       </c>
       <c r="L19">
-        <v>-1.8903502955310014E-5</v>
+        <v>2.0264800048956644E-6</v>
       </c>
       <c r="M19">
-        <v>3.3390118148220595E-6</v>
+        <v>-1.1458957765401003E-5</v>
       </c>
       <c r="N19">
-        <v>1.3084655330368108E-8</v>
+        <v>9.2376861697027288E-6</v>
       </c>
       <c r="O19">
-        <v>-3.5543902289093974E-5</v>
+        <v>-6.0324429002672891E-7</v>
       </c>
       <c r="P19">
-        <v>-1.4067455843475759E-4</v>
+        <v>-1.639563847920086E-5</v>
       </c>
       <c r="Q19">
-        <v>1.9571674622286446E-5</v>
+        <v>-4.7469728653608163E-7</v>
       </c>
       <c r="R19">
-        <v>-1.4674195481609491E-4</v>
+        <v>2.0233908496501384E-5</v>
       </c>
       <c r="S19">
-        <v>1.0956230346302978E-3</v>
+        <v>1.8931483189660154E-4</v>
       </c>
       <c r="T19">
-        <v>2.9245407493332896E-3</v>
+        <v>1.1664669610353246E-3</v>
       </c>
       <c r="U19">
-        <v>1.0813498203628463E-3</v>
+        <v>1.8885023874164549E-4</v>
       </c>
       <c r="V19">
-        <v>1.0527060866017571E-3</v>
+        <v>1.8903439826692888E-4</v>
       </c>
       <c r="W19">
-        <v>5.6280560119915208E-7</v>
+        <v>-1.2479950202965631E-6</v>
       </c>
       <c r="X19">
-        <v>4.4271440204636818E-5</v>
+        <v>7.9582774915925236E-6</v>
       </c>
       <c r="Y19">
-        <v>1.1850122225729062E-4</v>
+        <v>4.2328731741212774E-6</v>
       </c>
       <c r="Z19">
-        <v>-1.6132516765447681E-4</v>
+        <v>-2.5654283831203916E-4</v>
       </c>
     </row>
     <row r="20" spans="1:26" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>37</v>
       </c>
-      <c r="B20" s="4">
-        <v>0.11409879160165518</v>
+      <c r="B20">
+        <v>-6.1143518105376243E-2</v>
       </c>
       <c r="C20">
-        <v>-2.210067863526545E-5</v>
+        <v>4.0177292178696675E-6</v>
       </c>
       <c r="D20">
-        <v>-1.1754883711324031E-5</v>
+        <v>1.8305068884135411E-6</v>
       </c>
       <c r="E20">
-        <v>1.1685853539109537E-7</v>
+        <v>-1.4724836446767245E-8</v>
       </c>
       <c r="F20">
-        <v>-5.9523634846229831E-5</v>
+        <v>-1.5004625773108157E-5</v>
       </c>
       <c r="G20">
-        <v>-1.1157675396371362E-4</v>
+        <v>-2.9678212976187843E-5</v>
       </c>
       <c r="H20">
-        <v>-1.2146006919084207E-4</v>
+        <v>-7.9777646237705769E-5</v>
       </c>
       <c r="I20">
-        <v>-8.9018456995237016E-5</v>
+        <v>-1.3792891991894023E-5</v>
       </c>
       <c r="J20">
-        <v>-1.2445994927460385E-4</v>
+        <v>-3.8003857750089267E-6</v>
       </c>
       <c r="K20">
-        <v>-4.5904528581284685E-5</v>
+        <v>-1.3108287156991691E-5</v>
       </c>
       <c r="L20">
-        <v>3.2915190851703262E-5</v>
+        <v>4.7910188245123991E-6</v>
       </c>
       <c r="M20">
-        <v>6.0961263863224647E-5</v>
+        <v>3.3637588899615206E-6</v>
       </c>
       <c r="N20">
-        <v>1.0258318133512287E-6</v>
+        <v>-6.0835156215599507E-6</v>
       </c>
       <c r="O20">
-        <v>-7.5716303166748302E-6</v>
+        <v>-3.6750950325146008E-6</v>
       </c>
       <c r="P20">
-        <v>4.9552684978026816E-6</v>
+        <v>5.4056104605772705E-6</v>
       </c>
       <c r="Q20">
-        <v>7.662239660605457E-6</v>
+        <v>1.4154339307565149E-6</v>
       </c>
       <c r="R20">
-        <v>-1.2535112306990689E-4</v>
+        <v>5.76237354201937E-6</v>
       </c>
       <c r="S20">
-        <v>1.1083314335363493E-3</v>
+        <v>1.8895202252084745E-4</v>
       </c>
       <c r="T20">
-        <v>1.0813498203628463E-3</v>
+        <v>1.8885023874164549E-4</v>
       </c>
       <c r="U20">
-        <v>1.7236799382494509E-3</v>
+        <v>3.1959763534585841E-4</v>
       </c>
       <c r="V20">
-        <v>1.0603915174576444E-3</v>
+        <v>1.8492441249281548E-4</v>
       </c>
       <c r="W20">
-        <v>-2.5756087371170881E-6</v>
+        <v>-3.4672381735125904E-6</v>
       </c>
       <c r="X20">
-        <v>1.1295150881726347E-4</v>
+        <v>-2.2804709030419047E-5</v>
       </c>
       <c r="Y20">
-        <v>1.0796865642086711E-4</v>
+        <v>-9.9661934778780051E-6</v>
       </c>
       <c r="Z20">
-        <v>-6.1456192242089467E-4</v>
+        <v>-1.2076168336568968E-4</v>
       </c>
     </row>
     <row r="21" spans="1:26" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>38</v>
       </c>
-      <c r="B21" s="4">
-        <v>-9.4710864514856129E-3</v>
+      <c r="B21">
+        <v>-0.1929539804481297</v>
       </c>
       <c r="C21">
-        <v>-5.2814065858668799E-5</v>
+        <v>-3.9273454822358285E-7</v>
       </c>
       <c r="D21">
-        <v>-4.6111083192621025E-6</v>
+        <v>1.447232824922551E-6</v>
       </c>
       <c r="E21">
-        <v>6.3122073051336974E-8</v>
+        <v>-1.7293325221811415E-8</v>
       </c>
       <c r="F21">
-        <v>2.1986294995192217E-5</v>
+        <v>2.4240899710838761E-6</v>
       </c>
       <c r="G21">
-        <v>6.7610349847862605E-5</v>
+        <v>8.1225176297103905E-6</v>
       </c>
       <c r="H21">
-        <v>1.7266588027294548E-5</v>
+        <v>-1.215617897776548E-4</v>
       </c>
       <c r="I21">
-        <v>5.0609610093509095E-6</v>
+        <v>-3.8299450313766711E-5</v>
       </c>
       <c r="J21">
-        <v>-4.6618273654365613E-5</v>
+        <v>-1.042660303580964E-5</v>
       </c>
       <c r="K21">
-        <v>-5.9798794095122801E-5</v>
+        <v>-8.8345035922361259E-6</v>
       </c>
       <c r="L21">
-        <v>8.590314213695121E-5</v>
+        <v>-5.0043481363612593E-6</v>
       </c>
       <c r="M21">
-        <v>3.4232478111005194E-5</v>
+        <v>-3.9812254343785133E-5</v>
       </c>
       <c r="N21">
-        <v>1.3056585895025399E-5</v>
+        <v>-2.6916219119545843E-6</v>
       </c>
       <c r="O21">
-        <v>9.6522063377708391E-6</v>
+        <v>-3.3017021870913987E-6</v>
       </c>
       <c r="P21">
-        <v>-1.3190455124847673E-4</v>
+        <v>5.8503664066349853E-6</v>
       </c>
       <c r="Q21">
-        <v>6.8438667247680469E-6</v>
+        <v>1.0676656748794851E-7</v>
       </c>
       <c r="R21">
-        <v>-7.1715201520077684E-5</v>
+        <v>3.8459986493859927E-6</v>
       </c>
       <c r="S21">
-        <v>1.0802909365509165E-3</v>
+        <v>1.8853987798384014E-4</v>
       </c>
       <c r="T21">
-        <v>1.0527060866017571E-3</v>
+        <v>1.8903439826692888E-4</v>
       </c>
       <c r="U21">
-        <v>1.0603915174576444E-3</v>
+        <v>1.8492441249281548E-4</v>
       </c>
       <c r="V21">
-        <v>1.5416761970843181E-3</v>
+        <v>3.9150384632997433E-4</v>
       </c>
       <c r="W21">
-        <v>-2.5152068866856586E-6</v>
+        <v>-1.9692630079253743E-6</v>
       </c>
       <c r="X21">
-        <v>2.947533416053713E-5</v>
+        <v>-1.1822515946030009E-5</v>
       </c>
       <c r="Y21">
-        <v>1.6014366203762233E-5</v>
+        <v>-9.1189245904745897E-6</v>
       </c>
       <c r="Z21">
-        <v>-1.0208579459922743E-3</v>
+        <v>-1.3766732932676202E-4</v>
       </c>
     </row>
     <row r="22" spans="1:26" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
-        <v>21</v>
-      </c>
-      <c r="B22" s="4">
-        <v>1.5097838322668224E-2</v>
+        <v>20</v>
+      </c>
+      <c r="B22">
+        <v>-3.163802392749962E-2</v>
       </c>
       <c r="C22">
-        <v>2.531492062338568E-6</v>
+        <v>6.0034505429399852E-7</v>
       </c>
       <c r="D22">
-        <v>-4.0329785101902516E-8</v>
+        <v>3.3183568241448074E-7</v>
       </c>
       <c r="E22">
-        <v>-1.7091764456851345E-9</v>
+        <v>-5.1590226801820155E-9</v>
       </c>
       <c r="F22">
-        <v>3.8236620791673429E-6</v>
+        <v>3.7235906919433749E-6</v>
       </c>
       <c r="G22">
-        <v>8.6731768599810364E-6</v>
+        <v>6.6855247055917278E-6</v>
       </c>
       <c r="H22">
-        <v>5.7238100108621354E-6</v>
+        <v>4.4544904443447042E-6</v>
       </c>
       <c r="I22">
-        <v>3.9283034091352527E-7</v>
+        <v>1.1635940812401434E-6</v>
       </c>
       <c r="J22">
-        <v>-1.0407116605641399E-5</v>
+        <v>7.3784239535592123E-7</v>
       </c>
       <c r="K22">
-        <v>-3.7525721659891321E-6</v>
+        <v>3.5266717129359311E-7</v>
       </c>
       <c r="L22">
-        <v>-5.002102684185811E-6</v>
+        <v>-2.2064054999403602E-6</v>
       </c>
       <c r="M22">
-        <v>-1.5425744178756167E-5</v>
+        <v>-1.8336964371445136E-6</v>
       </c>
       <c r="N22">
-        <v>-3.7508758724344386E-6</v>
+        <v>-1.1648919099622115E-6</v>
       </c>
       <c r="O22">
-        <v>-9.2060685244680649E-8</v>
+        <v>1.1588106554259771E-7</v>
       </c>
       <c r="P22">
-        <v>-7.3438250366484364E-7</v>
+        <v>6.4482022512958328E-7</v>
       </c>
       <c r="Q22">
-        <v>-8.6335968130657746E-7</v>
+        <v>-3.0174565132101841E-7</v>
       </c>
       <c r="R22">
-        <v>-8.5031063138964898E-7</v>
+        <v>-1.7337109460746665E-6</v>
       </c>
       <c r="S22">
-        <v>-8.0417876519968477E-6</v>
+        <v>4.7163842292647585E-7</v>
       </c>
       <c r="T22">
-        <v>5.6280560119915208E-7</v>
+        <v>-1.2479950202965631E-6</v>
       </c>
       <c r="U22">
-        <v>-2.5756087371170881E-6</v>
+        <v>-3.4672381735125904E-6</v>
       </c>
       <c r="V22">
-        <v>-2.5152068866856586E-6</v>
+        <v>-1.9692630079253743E-6</v>
       </c>
       <c r="W22">
-        <v>1.4923715562899379E-5</v>
+        <v>4.3887801367449529E-6</v>
       </c>
       <c r="X22">
-        <v>-5.6738986528005769E-5</v>
+        <v>-7.650901216713516E-6</v>
       </c>
       <c r="Y22">
-        <v>-7.2502395698087162E-5</v>
+        <v>-1.1027797524594714E-5</v>
       </c>
       <c r="Z22">
-        <v>-2.1330096781240764E-4</v>
+        <v>-7.2265396428641257E-5</v>
       </c>
     </row>
     <row r="23" spans="1:26" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
-        <v>22</v>
-      </c>
-      <c r="B23" s="4">
-        <v>4.916657481033445E-2</v>
+        <v>21</v>
+      </c>
+      <c r="B23">
+        <v>-2.8517285487333552E-4</v>
       </c>
       <c r="C23">
-        <v>-7.3838360348885991E-5</v>
+        <v>7.8824776593289909E-6</v>
       </c>
       <c r="D23">
-        <v>3.2091389183514342E-7</v>
+        <v>-1.0678991882215978E-6</v>
       </c>
       <c r="E23">
-        <v>-9.0277729582625478E-9</v>
+        <v>5.0910654532365833E-10</v>
       </c>
       <c r="F23">
-        <v>-8.6505127803494254E-5</v>
+        <v>-1.8979050568965271E-5</v>
       </c>
       <c r="G23">
-        <v>-1.4161359383604117E-4</v>
+        <v>4.3379863333244323E-6</v>
       </c>
       <c r="H23">
-        <v>-2.0487191327827996E-4</v>
+        <v>-6.2919010088083186E-5</v>
       </c>
       <c r="I23">
-        <v>-1.4779442285337572E-4</v>
+        <v>1.0142510176636436E-5</v>
       </c>
       <c r="J23">
-        <v>7.4400115263890303E-5</v>
+        <v>3.5239996712606064E-6</v>
       </c>
       <c r="K23">
-        <v>2.0010662561979991E-4</v>
+        <v>4.0265629473044051E-5</v>
       </c>
       <c r="L23">
-        <v>1.4630818488771077E-4</v>
+        <v>-5.2722229684035193E-6</v>
       </c>
       <c r="M23">
-        <v>1.1507275028427592E-4</v>
+        <v>-1.7521861695383284E-5</v>
       </c>
       <c r="N23">
-        <v>-1.2180728347892396E-5</v>
+        <v>3.2863141718789644E-6</v>
       </c>
       <c r="O23">
-        <v>-2.1939000935732639E-5</v>
+        <v>-2.3916006191006495E-8</v>
       </c>
       <c r="P23">
-        <v>-2.8378356873044427E-4</v>
+        <v>-1.3119722814263319E-5</v>
       </c>
       <c r="Q23">
-        <v>9.5471783148785304E-6</v>
+        <v>-2.4390233059814681E-6</v>
       </c>
       <c r="R23">
-        <v>-5.4982861974611273E-5</v>
+        <v>-3.9929853980878038E-6</v>
       </c>
       <c r="S23">
-        <v>5.7620726639387009E-4</v>
+        <v>1.456835199313657E-5</v>
       </c>
       <c r="T23">
-        <v>4.4271440204636818E-5</v>
+        <v>7.9582774915925236E-6</v>
       </c>
       <c r="U23">
-        <v>1.1295150881726347E-4</v>
+        <v>-2.2804709030419047E-5</v>
       </c>
       <c r="V23">
-        <v>2.947533416053713E-5</v>
+        <v>-1.1822515946030009E-5</v>
       </c>
       <c r="W23">
-        <v>-5.6738986528005769E-5</v>
+        <v>-7.650901216713516E-6</v>
       </c>
       <c r="X23">
-        <v>2.9814213297746977E-3</v>
+        <v>4.5483712677082667E-4</v>
       </c>
       <c r="Y23">
-        <v>9.6936395508520385E-4</v>
+        <v>2.0504146142818171E-4</v>
       </c>
       <c r="Z23">
-        <v>8.0830793647224141E-4</v>
+        <v>1.6075863818473983E-4</v>
       </c>
     </row>
     <row r="24" spans="1:26" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
-        <v>23</v>
-      </c>
-      <c r="B24" s="4">
-        <v>0.1012707683296683</v>
+        <v>22</v>
+      </c>
+      <c r="B24">
+        <v>-7.5643106657386869E-2</v>
       </c>
       <c r="C24">
-        <v>-1.2361335127915279E-5</v>
+        <v>-1.1388777788190706E-6</v>
       </c>
       <c r="D24">
-        <v>-1.899410615235473E-5</v>
+        <v>-1.6968097017025426E-6</v>
       </c>
       <c r="E24">
-        <v>1.8642845634098309E-7</v>
+        <v>1.7153634489465683E-8</v>
       </c>
       <c r="F24">
-        <v>-1.3023542989722944E-4</v>
+        <v>-1.5638874454195498E-5</v>
       </c>
       <c r="G24">
-        <v>-1.2300805045074105E-4</v>
+        <v>3.6965918365123473E-6</v>
       </c>
       <c r="H24">
-        <v>-1.7041217826349315E-4</v>
+        <v>-3.6819404043739331E-5</v>
       </c>
       <c r="I24">
-        <v>-8.2491207183308345E-5</v>
+        <v>-4.4142509780008353E-6</v>
       </c>
       <c r="J24">
-        <v>-2.4825393044161474E-5</v>
+        <v>-5.8867787595129621E-6</v>
       </c>
       <c r="K24">
-        <v>1.8473476141887287E-4</v>
+        <v>1.9517675162887373E-5</v>
       </c>
       <c r="L24">
-        <v>6.6350580178099668E-5</v>
+        <v>5.9386948000614346E-6</v>
       </c>
       <c r="M24">
-        <v>9.2035613564749757E-5</v>
+        <v>-4.957584749059246E-5</v>
       </c>
       <c r="N24">
-        <v>-5.0164733857542364E-5</v>
+        <v>3.0354886025044072E-5</v>
       </c>
       <c r="O24">
-        <v>-1.4351757241395973E-5</v>
+        <v>-1.1758206044810254E-7</v>
       </c>
       <c r="P24">
-        <v>-1.399591403825416E-4</v>
+        <v>-4.0293955958587885E-5</v>
       </c>
       <c r="Q24">
-        <v>1.7298133638593463E-5</v>
+        <v>-9.355408110667264E-7</v>
       </c>
       <c r="R24">
-        <v>-2.9337592473541067E-5</v>
+        <v>3.7300932876295782E-5</v>
       </c>
       <c r="S24">
-        <v>4.509097454734146E-4</v>
+        <v>1.4970669167837116E-5</v>
       </c>
       <c r="T24">
-        <v>1.1850122225729062E-4</v>
+        <v>4.2328731741212774E-6</v>
       </c>
       <c r="U24">
-        <v>1.0796865642086711E-4</v>
+        <v>-9.9661934778780051E-6</v>
       </c>
       <c r="V24">
-        <v>1.6014366203762233E-5</v>
+        <v>-9.1189245904745897E-6</v>
       </c>
       <c r="W24">
-        <v>-7.2502395698087162E-5</v>
+        <v>-1.1027797524594714E-5</v>
       </c>
       <c r="X24">
-        <v>9.6936395508520385E-4</v>
+        <v>2.0504146142818171E-4</v>
       </c>
       <c r="Y24">
-        <v>2.4102027571552146E-3</v>
+        <v>3.0210138634924458E-4</v>
       </c>
       <c r="Z24">
-        <v>1.550912911325623E-3</v>
+        <v>8.9870209641225161E-5</v>
       </c>
     </row>
     <row r="25" spans="1:26" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
-        <v>24</v>
-      </c>
-      <c r="B25" s="4">
-        <v>-2.1480988817062192</v>
+        <v>23</v>
+      </c>
+      <c r="B25">
+        <v>-2.5801142802868213</v>
       </c>
       <c r="C25">
-        <v>-5.4097457861786245E-4</v>
+        <v>-2.052694353893756E-4</v>
       </c>
       <c r="D25">
-        <v>-9.7190515930184744E-4</v>
+        <v>-3.288898409886566E-4</v>
       </c>
       <c r="E25">
-        <v>9.2542742162443259E-6</v>
+        <v>2.837904909877767E-6</v>
       </c>
       <c r="F25">
-        <v>-1.3882889392827877E-3</v>
+        <v>-2.5494856565214758E-4</v>
       </c>
       <c r="G25">
-        <v>-1.7516767670310801E-3</v>
+        <v>-3.2518717977771095E-4</v>
       </c>
       <c r="H25">
-        <v>-5.4677183572386127E-3</v>
+        <v>-1.8388406350030445E-3</v>
       </c>
       <c r="I25">
-        <v>-2.6610883106909845E-3</v>
+        <v>-4.895820767468205E-4</v>
       </c>
       <c r="J25">
-        <v>-4.4637914327299915E-3</v>
+        <v>-4.8248553596203848E-4</v>
       </c>
       <c r="K25">
-        <v>-1.3611217807710451E-3</v>
+        <v>-3.6376838557618761E-4</v>
       </c>
       <c r="L25">
-        <v>-3.2882069727189294E-3</v>
+        <v>-6.5081675067867289E-4</v>
       </c>
       <c r="M25">
-        <v>-1.2818561877108708E-3</v>
+        <v>-3.953389418885671E-4</v>
       </c>
       <c r="N25">
-        <v>-1.6751956709370778E-3</v>
+        <v>-2.9142971269760113E-4</v>
       </c>
       <c r="O25">
-        <v>-3.4124106226029896E-4</v>
+        <v>-4.5855470787625464E-5</v>
       </c>
       <c r="P25">
-        <v>-5.7394918700289638E-4</v>
+        <v>6.765497780212475E-5</v>
       </c>
       <c r="Q25">
-        <v>1.793518952605416E-4</v>
+        <v>3.77365783741122E-5</v>
       </c>
       <c r="R25">
-        <v>4.9883554667337474E-4</v>
+        <v>-5.01300987493845E-5</v>
       </c>
       <c r="S25">
-        <v>2.1127715446781024E-4</v>
+        <v>-2.474971275245782E-4</v>
       </c>
       <c r="T25">
-        <v>-1.6132516765447681E-4</v>
+        <v>-2.5654283831203916E-4</v>
       </c>
       <c r="U25">
-        <v>-6.1456192242089467E-4</v>
+        <v>-1.2076168336568968E-4</v>
       </c>
       <c r="V25">
-        <v>-1.0208579459922743E-3</v>
+        <v>-1.3766732932676202E-4</v>
       </c>
       <c r="W25">
-        <v>-2.1330096781240764E-4</v>
+        <v>-7.2265396428641257E-5</v>
       </c>
       <c r="X25">
-        <v>8.0830793647224141E-4</v>
+        <v>1.6075863818473983E-4</v>
       </c>
       <c r="Y25">
-        <v>1.550912911325623E-3</v>
+        <v>8.9870209641225161E-5</v>
       </c>
       <c r="Z25">
-        <v>3.824483816201954E-2</v>
+        <v>1.215660787165165E-2</v>
       </c>
     </row>
   </sheetData>
